--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -50354,7 +50354,11 @@
         <v>64682</v>
       </c>
       <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>1781971927933</t>
+        </is>
+      </c>
       <c r="O330" t="n">
         <v>0</v>
       </c>
@@ -50375,7 +50379,11 @@
         <v>0</v>
       </c>
       <c r="V330" t="inlineStr"/>
-      <c r="W330" t="inlineStr"/>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64592/ca674f52-37b1-4a0d-a48b-c84651b8575d.jpg</t>
+        </is>
+      </c>
       <c r="X330" t="n">
         <v>0</v>
       </c>
@@ -50809,7 +50817,11 @@
         <v>64684</v>
       </c>
       <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>1781971743495</t>
+        </is>
+      </c>
       <c r="O333" t="n">
         <v>0</v>
       </c>
@@ -50830,7 +50842,11 @@
         <v>0</v>
       </c>
       <c r="V333" t="inlineStr"/>
-      <c r="W333" t="inlineStr"/>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64594/7151839f-f186-4979-b8d3-0b19e89c5b76.jpg</t>
+        </is>
+      </c>
       <c r="X333" t="n">
         <v>0</v>
       </c>
@@ -51860,7 +51876,11 @@
         <v>151205</v>
       </c>
       <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>1781971929957</t>
+        </is>
+      </c>
       <c r="O340" t="n">
         <v>0</v>
       </c>
@@ -51881,7 +51901,11 @@
         <v>0</v>
       </c>
       <c r="V340" t="inlineStr"/>
-      <c r="W340" t="inlineStr"/>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/646492/1d9e2b82-fc01-420e-8951-c35c6cd31408.jpg</t>
+        </is>
+      </c>
       <c r="X340" t="n">
         <v>0</v>
       </c>
@@ -55240,7 +55264,11 @@
         <v>151207</v>
       </c>
       <c r="M362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>1781970842335</t>
+        </is>
+      </c>
       <c r="O362" t="n">
         <v>0</v>
       </c>
@@ -55261,7 +55289,11 @@
         <v>0</v>
       </c>
       <c r="V362" t="inlineStr"/>
-      <c r="W362" t="inlineStr"/>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646497/6e783e9c-36aa-4f09-8d51-aeaaa1873f50.jpg</t>
+        </is>
+      </c>
       <c r="X362" t="n">
         <v>0</v>
       </c>
@@ -57092,7 +57124,11 @@
         <v>64714</v>
       </c>
       <c r="M374" t="inlineStr"/>
-      <c r="N374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>1781970484687</t>
+        </is>
+      </c>
       <c r="O374" t="n">
         <v>0</v>
       </c>
@@ -57113,7 +57149,11 @@
         <v>0</v>
       </c>
       <c r="V374" t="inlineStr"/>
-      <c r="W374" t="inlineStr"/>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
+        </is>
+      </c>
       <c r="X374" t="n">
         <v>0</v>
       </c>
@@ -57241,7 +57281,11 @@
         <v>64715</v>
       </c>
       <c r="M375" t="inlineStr"/>
-      <c r="N375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>1781970664668</t>
+        </is>
+      </c>
       <c r="O375" t="n">
         <v>0</v>
       </c>
@@ -57262,7 +57306,11 @@
         <v>0</v>
       </c>
       <c r="V375" t="inlineStr"/>
-      <c r="W375" t="inlineStr"/>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
+        </is>
+      </c>
       <c r="X375" t="n">
         <v>0</v>
       </c>
@@ -59224,7 +59272,11 @@
         <v>64725</v>
       </c>
       <c r="M388" t="inlineStr"/>
-      <c r="N388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>1781971564529</t>
+        </is>
+      </c>
       <c r="O388" t="n">
         <v>0</v>
       </c>
@@ -59245,7 +59297,11 @@
         <v>0</v>
       </c>
       <c r="V388" t="inlineStr"/>
-      <c r="W388" t="inlineStr"/>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
+        </is>
+      </c>
       <c r="X388" t="n">
         <v>0</v>
       </c>
@@ -59373,7 +59429,11 @@
         <v>64726</v>
       </c>
       <c r="M389" t="inlineStr"/>
-      <c r="N389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>1781971929292</t>
+        </is>
+      </c>
       <c r="O389" t="n">
         <v>0</v>
       </c>
@@ -59394,7 +59454,11 @@
         <v>0</v>
       </c>
       <c r="V389" t="inlineStr"/>
-      <c r="W389" t="inlineStr"/>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
+        </is>
+      </c>
       <c r="X389" t="n">
         <v>0</v>
       </c>
@@ -59522,7 +59586,11 @@
         <v>64727</v>
       </c>
       <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>1781971930377</t>
+        </is>
+      </c>
       <c r="O390" t="n">
         <v>0</v>
       </c>
@@ -59543,7 +59611,11 @@
         <v>0</v>
       </c>
       <c r="V390" t="inlineStr"/>
-      <c r="W390" t="inlineStr"/>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
+        </is>
+      </c>
       <c r="X390" t="n">
         <v>0</v>
       </c>
@@ -59671,7 +59743,11 @@
         <v>64728</v>
       </c>
       <c r="M391" t="inlineStr"/>
-      <c r="N391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>1781971922925</t>
+        </is>
+      </c>
       <c r="O391" t="n">
         <v>0</v>
       </c>
@@ -59692,7 +59768,11 @@
         <v>0</v>
       </c>
       <c r="V391" t="inlineStr"/>
-      <c r="W391" t="inlineStr"/>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
+        </is>
+      </c>
       <c r="X391" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -19081,7 +19081,11 @@
         <v>58525</v>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>1781973209406</t>
+        </is>
+      </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
@@ -19102,7 +19106,11 @@
         <v>0</v>
       </c>
       <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58434/c69a8fdf-0591-46d7-8d9a-b52a91152a60.jpg</t>
+        </is>
+      </c>
       <c r="X123" t="n">
         <v>0</v>
       </c>
@@ -42959,7 +42967,11 @@
         <v>148718</v>
       </c>
       <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>1781973016521</t>
+        </is>
+      </c>
       <c r="O281" t="n">
         <v>0</v>
       </c>
@@ -42980,7 +42992,11 @@
         <v>0</v>
       </c>
       <c r="V281" t="inlineStr"/>
-      <c r="W281" t="inlineStr"/>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/644006/e9c83f38-18b2-4c30-a3a0-7bb10ffd1510.jpg</t>
+        </is>
+      </c>
       <c r="X281" t="n">
         <v>0</v>
       </c>
@@ -50205,7 +50221,11 @@
         <v>64681</v>
       </c>
       <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>1781972104104</t>
+        </is>
+      </c>
       <c r="O329" t="n">
         <v>0</v>
       </c>
@@ -50226,7 +50246,11 @@
         <v>0</v>
       </c>
       <c r="V329" t="inlineStr"/>
-      <c r="W329" t="inlineStr"/>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64591/670ec5c9-117c-4b27-a33c-ffde65397f76.jpg</t>
+        </is>
+      </c>
       <c r="X329" t="n">
         <v>0</v>
       </c>
@@ -50974,7 +50998,11 @@
         <v>64685</v>
       </c>
       <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>1781973205953</t>
+        </is>
+      </c>
       <c r="O334" t="n">
         <v>0</v>
       </c>
@@ -50995,7 +51023,11 @@
         <v>0</v>
       </c>
       <c r="V334" t="inlineStr"/>
-      <c r="W334" t="inlineStr"/>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64595/77179fd6-3eef-45c9-be42-c08e55b27d40.jpg</t>
+        </is>
+      </c>
       <c r="X334" t="n">
         <v>0</v>
       </c>
@@ -51272,7 +51304,11 @@
         <v>64687</v>
       </c>
       <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>1781973382923</t>
+        </is>
+      </c>
       <c r="O336" t="n">
         <v>0</v>
       </c>
@@ -51293,7 +51329,11 @@
         <v>0</v>
       </c>
       <c r="V336" t="inlineStr"/>
-      <c r="W336" t="inlineStr"/>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64597/6e3e07b3-6877-4111-9684-0d8acbf7a470.jpg</t>
+        </is>
+      </c>
       <c r="X336" t="n">
         <v>0</v>
       </c>
@@ -52182,7 +52222,11 @@
         <v>64705</v>
       </c>
       <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>1781972103673</t>
+        </is>
+      </c>
       <c r="O342" t="n">
         <v>0</v>
       </c>
@@ -52203,7 +52247,11 @@
         <v>0</v>
       </c>
       <c r="V342" t="inlineStr"/>
-      <c r="W342" t="inlineStr"/>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64615/a95a9781-55cf-4f3c-8ad0-e3cf04378620.jpg</t>
+        </is>
+      </c>
       <c r="X342" t="n">
         <v>0</v>
       </c>
@@ -52488,7 +52536,11 @@
         <v>64707</v>
       </c>
       <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>1781972285799</t>
+        </is>
+      </c>
       <c r="O344" t="n">
         <v>0</v>
       </c>
@@ -52509,7 +52561,11 @@
         <v>0</v>
       </c>
       <c r="V344" t="inlineStr"/>
-      <c r="W344" t="inlineStr"/>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64617/c4f5d63c-4af7-48dd-98ed-0a67c76ecc76.jpg</t>
+        </is>
+      </c>
       <c r="X344" t="n">
         <v>0</v>
       </c>
@@ -52637,7 +52693,11 @@
         <v>64708</v>
       </c>
       <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>1781972289321</t>
+        </is>
+      </c>
       <c r="O345" t="n">
         <v>0</v>
       </c>
@@ -52658,7 +52718,11 @@
         <v>0</v>
       </c>
       <c r="V345" t="inlineStr"/>
-      <c r="W345" t="inlineStr"/>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64618/72ad9035-c4c4-4006-b9f3-c20edc91c97d.jpg</t>
+        </is>
+      </c>
       <c r="X345" t="n">
         <v>0</v>
       </c>
@@ -52786,7 +52850,11 @@
         <v>64709</v>
       </c>
       <c r="M346" t="inlineStr"/>
-      <c r="N346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>1781972469858</t>
+        </is>
+      </c>
       <c r="O346" t="n">
         <v>0</v>
       </c>
@@ -52807,7 +52875,11 @@
         <v>0</v>
       </c>
       <c r="V346" t="inlineStr"/>
-      <c r="W346" t="inlineStr"/>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64619/702b3d56-62d9-4b66-8caa-7149c05e2b6f.jpg</t>
+        </is>
+      </c>
       <c r="X346" t="n">
         <v>0</v>
       </c>
@@ -52935,7 +53007,11 @@
         <v>64710</v>
       </c>
       <c r="M347" t="inlineStr"/>
-      <c r="N347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>1781972471092</t>
+        </is>
+      </c>
       <c r="O347" t="n">
         <v>0</v>
       </c>
@@ -52956,7 +53032,11 @@
         <v>0</v>
       </c>
       <c r="V347" t="inlineStr"/>
-      <c r="W347" t="inlineStr"/>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64620/6e2896ac-f65d-4d7d-a102-587a87a3a1a6.jpg</t>
+        </is>
+      </c>
       <c r="X347" t="n">
         <v>0</v>
       </c>
@@ -53547,7 +53627,11 @@
         <v>151212</v>
       </c>
       <c r="M351" t="inlineStr"/>
-      <c r="N351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>1781972468063</t>
+        </is>
+      </c>
       <c r="O351" t="n">
         <v>0</v>
       </c>
@@ -53568,7 +53652,11 @@
         <v>0</v>
       </c>
       <c r="V351" t="inlineStr"/>
-      <c r="W351" t="inlineStr"/>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/646494/97490551-aec4-4954-b67f-4d425ac1863f.jpg</t>
+        </is>
+      </c>
       <c r="X351" t="n">
         <v>0</v>
       </c>
@@ -56504,7 +56592,11 @@
         <v>64703</v>
       </c>
       <c r="M370" t="inlineStr"/>
-      <c r="N370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>1781972284783</t>
+        </is>
+      </c>
       <c r="O370" t="n">
         <v>0</v>
       </c>
@@ -56525,7 +56617,11 @@
         <v>0</v>
       </c>
       <c r="V370" t="inlineStr"/>
-      <c r="W370" t="inlineStr"/>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64613/bbf2dd97-9e62-4b41-a7bb-d2e629535220.jpg</t>
+        </is>
+      </c>
       <c r="X370" t="n">
         <v>0</v>
       </c>
@@ -60057,7 +60153,11 @@
         <v>151218</v>
       </c>
       <c r="M393" t="inlineStr"/>
-      <c r="N393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>1781972103434</t>
+        </is>
+      </c>
       <c r="O393" t="n">
         <v>0</v>
       </c>
@@ -60078,7 +60178,11 @@
         <v>0</v>
       </c>
       <c r="V393" t="inlineStr"/>
-      <c r="W393" t="inlineStr"/>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
+        </is>
+      </c>
       <c r="X393" t="n">
         <v>0</v>
       </c>
@@ -60206,7 +60310,11 @@
         <v>151219</v>
       </c>
       <c r="M394" t="inlineStr"/>
-      <c r="N394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>1781972285399</t>
+        </is>
+      </c>
       <c r="O394" t="n">
         <v>0</v>
       </c>
@@ -60227,7 +60335,11 @@
         <v>0</v>
       </c>
       <c r="V394" t="inlineStr"/>
-      <c r="W394" t="inlineStr"/>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
+        </is>
+      </c>
       <c r="X394" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -15912,7 +15912,11 @@
         <v>148654</v>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>1781973550353</t>
+        </is>
+      </c>
       <c r="O102" t="n">
         <v>0</v>
       </c>
@@ -15933,7 +15937,11 @@
         <v>0</v>
       </c>
       <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643942/2a4e5e43-3748-437a-b574-3f8acbff9286.jpg</t>
+        </is>
+      </c>
       <c r="X102" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -2977,7 +2977,11 @@
         <v>58451</v>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1781973555290</t>
+        </is>
+      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2998,7 +3002,11 @@
         <v>0</v>
       </c>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58360/dfb4289b-fed2-4527-82f5-8a8049feec61.jpg</t>
+        </is>
+      </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
@@ -4185,7 +4193,11 @@
         <v>58455</v>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1781973742525</t>
+        </is>
+      </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
@@ -4206,7 +4218,11 @@
         <v>0</v>
       </c>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58364/07dc3aae-4511-4e1b-bc4b-a2d2c46da04d.jpg</t>
+        </is>
+      </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
@@ -25129,7 +25145,11 @@
         <v>58553</v>
       </c>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>1781973544939</t>
+        </is>
+      </c>
       <c r="O163" t="n">
         <v>0</v>
       </c>
@@ -25150,7 +25170,11 @@
         <v>0</v>
       </c>
       <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58462/6516dd45-5c16-4956-95f2-48cc71f0555e.jpg</t>
+        </is>
+      </c>
       <c r="X163" t="n">
         <v>0</v>
       </c>
@@ -27686,7 +27710,11 @@
         <v>148683</v>
       </c>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>1781973740358</t>
+        </is>
+      </c>
       <c r="O180" t="n">
         <v>0</v>
       </c>
@@ -27707,7 +27735,11 @@
         <v>0</v>
       </c>
       <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/643971/f52dc953-a60a-4665-8b4f-ac5504de9041.jpg</t>
+        </is>
+      </c>
       <c r="X180" t="n">
         <v>0</v>
       </c>
@@ -35860,7 +35892,11 @@
         <v>58598</v>
       </c>
       <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>1781973688827</t>
+        </is>
+      </c>
       <c r="O234" t="n">
         <v>0</v>
       </c>
@@ -35881,7 +35917,11 @@
         <v>0</v>
       </c>
       <c r="V234" t="inlineStr"/>
-      <c r="W234" t="inlineStr"/>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58507/019d3f5c-3480-4540-bbd6-aa017e110586.jpg</t>
+        </is>
+      </c>
       <c r="X234" t="n">
         <v>0</v>
       </c>
@@ -49029,7 +49069,11 @@
         <v>64674</v>
       </c>
       <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>1781973933925</t>
+        </is>
+      </c>
       <c r="O321" t="n">
         <v>0</v>
       </c>
@@ -49050,7 +49094,11 @@
         <v>0</v>
       </c>
       <c r="V321" t="inlineStr"/>
-      <c r="W321" t="inlineStr"/>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4718/64584/fbd03aa7-e746-4070-9129-9979e84d8036.jpg</t>
+        </is>
+      </c>
       <c r="X321" t="n">
         <v>0</v>
       </c>
@@ -58309,7 +58357,11 @@
         <v>64721</v>
       </c>
       <c r="M381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>1781973924024</t>
+        </is>
+      </c>
       <c r="O381" t="n">
         <v>0</v>
       </c>
@@ -58330,7 +58382,11 @@
         <v>0</v>
       </c>
       <c r="V381" t="inlineStr"/>
-      <c r="W381" t="inlineStr"/>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
+        </is>
+      </c>
       <c r="X381" t="n">
         <v>0</v>
       </c>
@@ -58607,7 +58663,11 @@
         <v>151216</v>
       </c>
       <c r="M383" t="inlineStr"/>
-      <c r="N383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>1781973731518</t>
+        </is>
+      </c>
       <c r="O383" t="n">
         <v>0</v>
       </c>
@@ -58628,7 +58688,11 @@
         <v>0</v>
       </c>
       <c r="V383" t="inlineStr"/>
-      <c r="W383" t="inlineStr"/>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
+        </is>
+      </c>
       <c r="X383" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -1471,7 +1471,11 @@
         <v>58441</v>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1781974451377</t>
+        </is>
+      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -1492,7 +1496,11 @@
         <v>0</v>
       </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58350/d5bbb9f7-bf7a-4f30-a5b6-d6d7de510331.jpg</t>
+        </is>
+      </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
@@ -23325,7 +23333,11 @@
         <v>148670</v>
       </c>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>1781974451315</t>
+        </is>
+      </c>
       <c r="O151" t="n">
         <v>0</v>
       </c>
@@ -23346,7 +23358,11 @@
         <v>0</v>
       </c>
       <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/643958/6130b112-dc31-41a9-b171-8fd096b2248d.jpg</t>
+        </is>
+      </c>
       <c r="X151" t="n">
         <v>0</v>
       </c>
@@ -26510,7 +26526,11 @@
         <v>58558</v>
       </c>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>1781974092751</t>
+        </is>
+      </c>
       <c r="O172" t="n">
         <v>0</v>
       </c>
@@ -26531,7 +26551,11 @@
         <v>0</v>
       </c>
       <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58467/22cd83d3-7440-4eff-8f98-5199a445c291.jpg</t>
+        </is>
+      </c>
       <c r="X172" t="n">
         <v>0</v>
       </c>
@@ -27561,7 +27585,11 @@
         <v>148682</v>
       </c>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>1781974631552</t>
+        </is>
+      </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
@@ -27582,7 +27610,11 @@
         <v>0</v>
       </c>
       <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/643970/214f0553-0675-44f0-963d-055e7c52a63d.jpg</t>
+        </is>
+      </c>
       <c r="X179" t="n">
         <v>0</v>
       </c>
@@ -38944,7 +38976,11 @@
         <v>58607</v>
       </c>
       <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>1781974805143</t>
+        </is>
+      </c>
       <c r="O254" t="n">
         <v>0</v>
       </c>
@@ -38965,7 +39001,11 @@
         <v>0</v>
       </c>
       <c r="V254" t="inlineStr"/>
-      <c r="W254" t="inlineStr"/>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/58516/ba1c4c1b-329b-446b-9bba-396a3b8c3d4f.jpg</t>
+        </is>
+      </c>
       <c r="X254" t="n">
         <v>0</v>
       </c>
@@ -39093,7 +39133,11 @@
         <v>58608</v>
       </c>
       <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>1781974803716</t>
+        </is>
+      </c>
       <c r="O255" t="n">
         <v>0</v>
       </c>
@@ -39114,7 +39158,11 @@
         <v>0</v>
       </c>
       <c r="V255" t="inlineStr"/>
-      <c r="W255" t="inlineStr"/>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/58517/752e7012-8340-4c9c-b586-da3c73ab7726.jpg</t>
+        </is>
+      </c>
       <c r="X255" t="n">
         <v>0</v>
       </c>
@@ -49226,7 +49274,11 @@
         <v>64675</v>
       </c>
       <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>1781974088014</t>
+        </is>
+      </c>
       <c r="O322" t="n">
         <v>0</v>
       </c>
@@ -49247,7 +49299,11 @@
         <v>0</v>
       </c>
       <c r="V322" t="inlineStr"/>
-      <c r="W322" t="inlineStr"/>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4718/64585/a945ae17-2808-43c2-9cdf-a1c4b0a8d324.jpg</t>
+        </is>
+      </c>
       <c r="X322" t="n">
         <v>0</v>
       </c>
@@ -49532,7 +49588,11 @@
         <v>64677</v>
       </c>
       <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>1781974092259</t>
+        </is>
+      </c>
       <c r="O324" t="n">
         <v>0</v>
       </c>
@@ -49553,7 +49613,11 @@
         <v>0</v>
       </c>
       <c r="V324" t="inlineStr"/>
-      <c r="W324" t="inlineStr"/>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4718/64587/0f0d7aeb-6fa7-4ec3-b731-baa5a9d40487.jpg</t>
+        </is>
+      </c>
       <c r="X324" t="n">
         <v>0</v>
       </c>
@@ -49830,7 +49894,11 @@
         <v>64678</v>
       </c>
       <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>1781974089761</t>
+        </is>
+      </c>
       <c r="O326" t="n">
         <v>0</v>
       </c>
@@ -49851,7 +49919,11 @@
         <v>0</v>
       </c>
       <c r="V326" t="inlineStr"/>
-      <c r="W326" t="inlineStr"/>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64588/c2c618f2-0954-4fdd-8536-ac0a30f707bb.jpg</t>
+        </is>
+      </c>
       <c r="X326" t="n">
         <v>0</v>
       </c>
@@ -53220,7 +53292,11 @@
         <v>64711</v>
       </c>
       <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>1781974265481</t>
+        </is>
+      </c>
       <c r="O348" t="n">
         <v>0</v>
       </c>
@@ -53241,7 +53317,11 @@
         <v>0</v>
       </c>
       <c r="V348" t="inlineStr"/>
-      <c r="W348" t="inlineStr"/>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/64621/52b5bd03-f9e0-4a4b-9de9-0646ebcf0d33.jpg</t>
+        </is>
+      </c>
       <c r="X348" t="n">
         <v>0</v>
       </c>
@@ -53840,7 +53920,11 @@
         <v>151213</v>
       </c>
       <c r="M352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>1781974266632</t>
+        </is>
+      </c>
       <c r="O352" t="n">
         <v>0</v>
       </c>
@@ -53861,7 +53945,11 @@
         <v>0</v>
       </c>
       <c r="V352" t="inlineStr"/>
-      <c r="W352" t="inlineStr"/>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4723/646495/60f2105a-f6c5-424f-8e6e-a69b8585efe3.jpg</t>
+        </is>
+      </c>
       <c r="X352" t="n">
         <v>0</v>
       </c>
@@ -64594,7 +64682,11 @@
         <v>64754</v>
       </c>
       <c r="M422" t="inlineStr"/>
-      <c r="N422" t="inlineStr"/>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>1781974086141</t>
+        </is>
+      </c>
       <c r="O422" t="n">
         <v>0</v>
       </c>
@@ -64615,7 +64707,11 @@
         <v>0</v>
       </c>
       <c r="V422" t="inlineStr"/>
-      <c r="W422" t="inlineStr"/>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
+        </is>
+      </c>
       <c r="X422" t="n">
         <v>0</v>
       </c>
@@ -67181,7 +67277,11 @@
         <v>64765</v>
       </c>
       <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>1781974266039</t>
+        </is>
+      </c>
       <c r="O439" t="n">
         <v>0</v>
       </c>
@@ -67202,7 +67302,11 @@
         <v>0</v>
       </c>
       <c r="V439" t="inlineStr"/>
-      <c r="W439" t="inlineStr"/>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
+        </is>
+      </c>
       <c r="X439" t="n">
         <v>0</v>
       </c>
@@ -67636,7 +67740,11 @@
         <v>64768</v>
       </c>
       <c r="M442" t="inlineStr"/>
-      <c r="N442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>1781974266070</t>
+        </is>
+      </c>
       <c r="O442" t="n">
         <v>0</v>
       </c>
@@ -67657,7 +67765,11 @@
         <v>0</v>
       </c>
       <c r="V442" t="inlineStr"/>
-      <c r="W442" t="inlineStr"/>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
+        </is>
+      </c>
       <c r="X442" t="n">
         <v>0</v>
       </c>
@@ -67785,7 +67897,11 @@
         <v>64769</v>
       </c>
       <c r="M443" t="inlineStr"/>
-      <c r="N443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>1781974447124</t>
+        </is>
+      </c>
       <c r="O443" t="n">
         <v>0</v>
       </c>
@@ -67806,7 +67922,11 @@
         <v>0</v>
       </c>
       <c r="V443" t="inlineStr"/>
-      <c r="W443" t="inlineStr"/>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
+        </is>
+      </c>
       <c r="X443" t="n">
         <v>0</v>
       </c>
@@ -67934,7 +68054,11 @@
         <v>64770</v>
       </c>
       <c r="M444" t="inlineStr"/>
-      <c r="N444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>1781974628327</t>
+        </is>
+      </c>
       <c r="O444" t="n">
         <v>0</v>
       </c>
@@ -67955,7 +68079,11 @@
         <v>0</v>
       </c>
       <c r="V444" t="inlineStr"/>
-      <c r="W444" t="inlineStr"/>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
+        </is>
+      </c>
       <c r="X444" t="n">
         <v>0</v>
       </c>
@@ -68083,7 +68211,11 @@
         <v>64771</v>
       </c>
       <c r="M445" t="inlineStr"/>
-      <c r="N445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>1781974630372</t>
+        </is>
+      </c>
       <c r="O445" t="n">
         <v>0</v>
       </c>
@@ -68104,7 +68236,11 @@
         <v>0</v>
       </c>
       <c r="V445" t="inlineStr"/>
-      <c r="W445" t="inlineStr"/>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
+        </is>
+      </c>
       <c r="X445" t="n">
         <v>0</v>
       </c>
@@ -68389,7 +68525,11 @@
         <v>151229</v>
       </c>
       <c r="M447" t="inlineStr"/>
-      <c r="N447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>1781974627113</t>
+        </is>
+      </c>
       <c r="O447" t="n">
         <v>0</v>
       </c>
@@ -68410,7 +68550,11 @@
         <v>0</v>
       </c>
       <c r="V447" t="inlineStr"/>
-      <c r="W447" t="inlineStr"/>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
+        </is>
+      </c>
       <c r="X447" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -1628,7 +1628,11 @@
         <v>58442</v>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1781974805896</t>
+        </is>
+      </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
@@ -1649,7 +1653,11 @@
         <v>0</v>
       </c>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58351/c483a830-4a28-481d-8f58-8b2bac7ec44a.jpg</t>
+        </is>
+      </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
@@ -2224,7 +2232,11 @@
         <v>58446</v>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1781974804121</t>
+        </is>
+      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
@@ -2245,7 +2257,11 @@
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58355/dc5b9bbd-7012-43f1-8097-0c3026645583.jpg</t>
+        </is>
+      </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
@@ -39290,7 +39306,11 @@
         <v>58609</v>
       </c>
       <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>1781974985362</t>
+        </is>
+      </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
@@ -39311,7 +39331,11 @@
         <v>0</v>
       </c>
       <c r="V256" t="inlineStr"/>
-      <c r="W256" t="inlineStr"/>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/58518/fa3fc7e3-f637-4843-8df4-9737eb68bd4a.jpg</t>
+        </is>
+      </c>
       <c r="X256" t="n">
         <v>0</v>
       </c>
@@ -39753,7 +39777,11 @@
         <v>148714</v>
       </c>
       <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>1781975169722</t>
+        </is>
+      </c>
       <c r="O259" t="n">
         <v>0</v>
       </c>
@@ -39774,7 +39802,11 @@
         <v>0</v>
       </c>
       <c r="V259" t="inlineStr"/>
-      <c r="W259" t="inlineStr"/>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/644002/6c305558-b214-496d-9434-63855347395a.jpg</t>
+        </is>
+      </c>
       <c r="X259" t="n">
         <v>0</v>
       </c>
@@ -40051,7 +40083,11 @@
         <v>148716</v>
       </c>
       <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>1781974985915</t>
+        </is>
+      </c>
       <c r="O261" t="n">
         <v>0</v>
       </c>
@@ -40072,7 +40108,11 @@
         <v>0</v>
       </c>
       <c r="V261" t="inlineStr"/>
-      <c r="W261" t="inlineStr"/>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/644004/946de2b1-f305-449e-88ec-03ed0c983c52.jpg</t>
+        </is>
+      </c>
       <c r="X261" t="n">
         <v>0</v>
       </c>
@@ -61074,7 +61114,11 @@
         <v>64733</v>
       </c>
       <c r="M398" t="inlineStr"/>
-      <c r="N398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>1781975346942</t>
+        </is>
+      </c>
       <c r="O398" t="n">
         <v>0</v>
       </c>
@@ -61095,7 +61139,11 @@
         <v>0</v>
       </c>
       <c r="V398" t="inlineStr"/>
-      <c r="W398" t="inlineStr"/>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
+        </is>
+      </c>
       <c r="X398" t="n">
         <v>0</v>
       </c>
@@ -65904,7 +65952,11 @@
         <v>64759</v>
       </c>
       <c r="M430" t="inlineStr"/>
-      <c r="N430" t="inlineStr"/>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>1781975166154</t>
+        </is>
+      </c>
       <c r="O430" t="n">
         <v>0</v>
       </c>
@@ -65925,7 +65977,11 @@
         <v>0</v>
       </c>
       <c r="V430" t="inlineStr"/>
-      <c r="W430" t="inlineStr"/>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
+        </is>
+      </c>
       <c r="X430" t="n">
         <v>0</v>
       </c>
@@ -66053,7 +66109,11 @@
         <v>64760</v>
       </c>
       <c r="M431" t="inlineStr"/>
-      <c r="N431" t="inlineStr"/>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>1781974985005</t>
+        </is>
+      </c>
       <c r="O431" t="n">
         <v>0</v>
       </c>
@@ -66074,7 +66134,11 @@
         <v>0</v>
       </c>
       <c r="V431" t="inlineStr"/>
-      <c r="W431" t="inlineStr"/>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
+        </is>
+      </c>
       <c r="X431" t="n">
         <v>0</v>
       </c>
@@ -66202,7 +66266,11 @@
         <v>64761</v>
       </c>
       <c r="M432" t="inlineStr"/>
-      <c r="N432" t="inlineStr"/>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>1781975165502</t>
+        </is>
+      </c>
       <c r="O432" t="n">
         <v>0</v>
       </c>
@@ -66223,7 +66291,11 @@
         <v>0</v>
       </c>
       <c r="V432" t="inlineStr"/>
-      <c r="W432" t="inlineStr"/>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
+        </is>
+      </c>
       <c r="X432" t="n">
         <v>0</v>
       </c>
@@ -66351,7 +66423,11 @@
         <v>64762</v>
       </c>
       <c r="M433" t="inlineStr"/>
-      <c r="N433" t="inlineStr"/>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>1781975169663</t>
+        </is>
+      </c>
       <c r="O433" t="n">
         <v>0</v>
       </c>
@@ -66372,7 +66448,11 @@
         <v>0</v>
       </c>
       <c r="V433" t="inlineStr"/>
-      <c r="W433" t="inlineStr"/>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
+        </is>
+      </c>
       <c r="X433" t="n">
         <v>0</v>
       </c>
@@ -66814,7 +66894,11 @@
         <v>151227</v>
       </c>
       <c r="M436" t="inlineStr"/>
-      <c r="N436" t="inlineStr"/>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>1781974982952</t>
+        </is>
+      </c>
       <c r="O436" t="n">
         <v>0</v>
       </c>
@@ -66835,7 +66919,11 @@
         <v>0</v>
       </c>
       <c r="V436" t="inlineStr"/>
-      <c r="W436" t="inlineStr"/>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+        </is>
+      </c>
       <c r="X436" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -2083,7 +2083,11 @@
         <v>58445</v>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1781975706731</t>
+        </is>
+      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -2104,7 +2108,11 @@
         <v>0</v>
       </c>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58354/4a7bb637-bbed-47a8-90bb-25d5ff07d793.jpg</t>
+        </is>
+      </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
@@ -4068,7 +4076,11 @@
         <v>148636</v>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1781976065172</t>
+        </is>
+      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -4089,7 +4101,11 @@
         <v>0</v>
       </c>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/643924/9ec5a52c-b3e0-42c4-862b-6f73b1134c4a.jpg</t>
+        </is>
+      </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
@@ -4374,7 +4390,11 @@
         <v>58456</v>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1781976245361</t>
+        </is>
+      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
@@ -4395,7 +4415,11 @@
         <v>0</v>
       </c>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58365/91beeeae-b5ce-439c-95c0-61df79a6bd36.jpg</t>
+        </is>
+      </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
@@ -4821,7 +4845,11 @@
         <v>58459</v>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1781976425419</t>
+        </is>
+      </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
@@ -4842,7 +4870,11 @@
         <v>0</v>
       </c>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58368/a1f2d7cb-0741-4ae7-9889-7cbc138b33d9.jpg</t>
+        </is>
+      </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
@@ -23051,7 +23083,11 @@
         <v>58546</v>
       </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>1781975531047</t>
+        </is>
+      </c>
       <c r="O149" t="n">
         <v>0</v>
       </c>
@@ -23072,7 +23108,11 @@
         <v>0</v>
       </c>
       <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58455/7df59ea8-9fc0-416d-ad87-0b4b89b012c7.jpg</t>
+        </is>
+      </c>
       <c r="X149" t="n">
         <v>0</v>
       </c>
@@ -39934,7 +39974,11 @@
         <v>148715</v>
       </c>
       <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>1781975525039</t>
+        </is>
+      </c>
       <c r="O260" t="n">
         <v>0</v>
       </c>
@@ -39955,7 +39999,11 @@
         <v>0</v>
       </c>
       <c r="V260" t="inlineStr"/>
-      <c r="W260" t="inlineStr"/>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4354/644003/68ec328b-1bb0-459b-a4e4-0a3855641e30.jpg</t>
+        </is>
+      </c>
       <c r="X260" t="n">
         <v>0</v>
       </c>
@@ -61271,7 +61319,11 @@
         <v>64734</v>
       </c>
       <c r="M399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>1781975887400</t>
+        </is>
+      </c>
       <c r="O399" t="n">
         <v>0</v>
       </c>
@@ -61292,7 +61344,11 @@
         <v>0</v>
       </c>
       <c r="V399" t="inlineStr"/>
-      <c r="W399" t="inlineStr"/>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
+        </is>
+      </c>
       <c r="X399" t="n">
         <v>0</v>
       </c>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -1173,7 +1173,11 @@
         <v>58439</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1781977092341</t>
+        </is>
+      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1194,7 +1198,11 @@
         <v>0</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58348/47a03b71-0bd8-45d6-973f-09139f8bd4e9.jpg</t>
+        </is>
+      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -1322,7 +1330,11 @@
         <v>58440</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1781976991229</t>
+        </is>
+      </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -1343,7 +1355,11 @@
         <v>0</v>
       </c>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58349/64c964eb-4898-408b-a8bd-1593a5cad58f.jpg</t>
+        </is>
+      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
@@ -2397,7 +2413,11 @@
         <v>58447</v>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1781976801198</t>
+        </is>
+      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -2418,7 +2438,11 @@
         <v>0</v>
       </c>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58356/885141dd-fe4b-4dc6-8563-03ca4d106c50.jpg</t>
+        </is>
+      </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
@@ -2546,7 +2570,11 @@
         <v>58448</v>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1781976975863</t>
+        </is>
+      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -2567,7 +2595,11 @@
         <v>0</v>
       </c>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58357/44e62226-2686-4396-81cb-dba98de40d1e.jpg</t>
+        </is>
+      </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
@@ -3770,7 +3802,11 @@
         <v>148634</v>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1781976788997</t>
+        </is>
+      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3791,7 +3827,11 @@
         <v>0</v>
       </c>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/643922/d364d5fe-5e01-4e37-b8ee-722272220109.jpg</t>
+        </is>
+      </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
@@ -4547,7 +4587,11 @@
         <v>58457</v>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1781976905977</t>
+        </is>
+      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
@@ -4568,7 +4612,11 @@
         <v>0</v>
       </c>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58366/ab7d08c5-bb0b-4625-b393-1ca714cc6f04.jpg</t>
+        </is>
+      </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
@@ -4695,29 +4743,43 @@
       <c r="L28" t="n">
         <v>58458</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>1781976603280</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1781976602673</t>
+        </is>
+      </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>6a36ce1a370583337b6e6d07</t>
+        </is>
+      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58367/913b3a2d-bd41-4fda-9b86-e40660b325cd.jpg</t>
+        </is>
+      </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
@@ -4734,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -5002,7 +5064,11 @@
         <v>58460</v>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1781977142601</t>
+        </is>
+      </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
@@ -5023,7 +5089,11 @@
         <v>0</v>
       </c>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58369/56379528-e25e-47d6-9b3a-b4814eee8ac1.jpg</t>
+        </is>
+      </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
@@ -5308,7 +5378,11 @@
         <v>58462</v>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1781976899985</t>
+        </is>
+      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -5329,7 +5403,11 @@
         <v>0</v>
       </c>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58371/b3569fda-11d7-4446-bd36-76fafbcefd8c.jpg</t>
+        </is>
+      </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
@@ -5457,7 +5535,11 @@
         <v>58463</v>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1781977046257</t>
+        </is>
+      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -5478,7 +5560,11 @@
         <v>0</v>
       </c>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58372/025f1913-9f58-471c-882c-74c36c51dd89.jpg</t>
+        </is>
+      </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
@@ -5606,7 +5692,11 @@
         <v>58464</v>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1781976821662</t>
+        </is>
+      </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
@@ -5627,7 +5717,11 @@
         <v>0</v>
       </c>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58373/aad26a8b-6690-41d2-b6c0-ed5a5ff39943.jpg</t>
+        </is>
+      </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
@@ -5755,7 +5849,11 @@
         <v>58465</v>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1781977071050</t>
+        </is>
+      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -5776,7 +5874,11 @@
         <v>0</v>
       </c>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58374/5e755093-e1b1-494f-934a-3dbfa195e5d4.jpg</t>
+        </is>
+      </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
@@ -5904,7 +6006,11 @@
         <v>58466</v>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1781976771844</t>
+        </is>
+      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -5925,7 +6031,11 @@
         <v>0</v>
       </c>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58375/75732785-f146-44a4-9c68-1f523f82acee.jpg</t>
+        </is>
+      </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
@@ -6053,7 +6163,11 @@
         <v>58467</v>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1781976865911</t>
+        </is>
+      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -6074,7 +6188,11 @@
         <v>0</v>
       </c>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/58376/5ef329f5-dd03-429b-84bb-24021415751e.jpg</t>
+        </is>
+      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
@@ -6365,7 +6483,11 @@
         <v>148637</v>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1781976603602</t>
+        </is>
+      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -6386,7 +6508,11 @@
         <v>0</v>
       </c>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/643925/3ea974b6-f3f1-4bb2-82f8-7a1121e0e63f.jpg</t>
+        </is>
+      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
@@ -6514,7 +6640,11 @@
         <v>148638</v>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1781976900547</t>
+        </is>
+      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -6535,7 +6665,11 @@
         <v>0</v>
       </c>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/643926/87ddb5a5-bd45-411c-873e-7e10d8b810ee.jpg</t>
+        </is>
+      </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
@@ -6663,7 +6797,11 @@
         <v>148639</v>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1781976825916</t>
+        </is>
+      </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
@@ -6684,7 +6822,11 @@
         <v>0</v>
       </c>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4345/643927/5b4d87f0-eb0c-4a07-b8f3-c5a5d68f372e.jpg</t>
+        </is>
+      </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
@@ -7126,7 +7268,11 @@
         <v>58471</v>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1781976881350</t>
+        </is>
+      </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
@@ -7147,7 +7293,11 @@
         <v>0</v>
       </c>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58380/f2ef0d42-af7e-4ebf-a879-ce5f34a81efd.jpg</t>
+        </is>
+      </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
@@ -7275,7 +7425,11 @@
         <v>58472</v>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1781976900926</t>
+        </is>
+      </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -7296,7 +7450,11 @@
         <v>0</v>
       </c>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58381/ef7732d0-6967-4234-a3fc-54eea7d64935.jpg</t>
+        </is>
+      </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
@@ -7424,7 +7582,11 @@
         <v>58473</v>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1781976926644</t>
+        </is>
+      </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
@@ -7445,7 +7607,11 @@
         <v>0</v>
       </c>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58382/3c09ceca-f14d-4d2e-b4f8-b001aff42023.jpg</t>
+        </is>
+      </c>
       <c r="X46" t="n">
         <v>0</v>
       </c>
@@ -7573,7 +7739,11 @@
         <v>58474</v>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1781976877725</t>
+        </is>
+      </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
@@ -7594,7 +7764,11 @@
         <v>0</v>
       </c>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58383/ebac814e-1124-4c83-9d28-9b59950667f3.jpg</t>
+        </is>
+      </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
@@ -7722,7 +7896,11 @@
         <v>58475</v>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1781976874726</t>
+        </is>
+      </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
@@ -7743,7 +7921,11 @@
         <v>0</v>
       </c>
       <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58384/da134454-5537-4457-9b4d-7a393ea5bdd2.jpg</t>
+        </is>
+      </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
@@ -7871,7 +8053,11 @@
         <v>58476</v>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1781976902010</t>
+        </is>
+      </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
@@ -7892,7 +8078,11 @@
         <v>0</v>
       </c>
       <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58385/c0d1a4d2-5ac6-4ea1-bda4-71684e04b246.jpg</t>
+        </is>
+      </c>
       <c r="X49" t="n">
         <v>0</v>
       </c>
@@ -8648,7 +8838,11 @@
         <v>58481</v>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1781976922727</t>
+        </is>
+      </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
@@ -8669,7 +8863,11 @@
         <v>0</v>
       </c>
       <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58390/57c15141-9333-4aba-8450-3388fdbd3ede.jpg</t>
+        </is>
+      </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
@@ -8797,7 +8995,11 @@
         <v>58482</v>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1781976826642</t>
+        </is>
+      </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
@@ -8818,7 +9020,11 @@
         <v>0</v>
       </c>
       <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58391/a4380945-11ce-48d1-9ed1-06e3efbbf25c.jpg</t>
+        </is>
+      </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
@@ -9417,7 +9623,11 @@
         <v>58486</v>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1781976932484</t>
+        </is>
+      </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
@@ -9438,7 +9648,11 @@
         <v>0</v>
       </c>
       <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58395/c1be0b6b-d54b-4f03-b031-88324696e99a.jpg</t>
+        </is>
+      </c>
       <c r="X59" t="n">
         <v>0</v>
       </c>
@@ -9880,7 +10094,11 @@
         <v>58489</v>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1781976792583</t>
+        </is>
+      </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
@@ -9901,7 +10119,11 @@
         <v>0</v>
       </c>
       <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58398/5bf06af3-88a9-4842-af57-e203f2e5e1ec.jpg</t>
+        </is>
+      </c>
       <c r="X62" t="n">
         <v>0</v>
       </c>
@@ -10186,7 +10408,11 @@
         <v>58491</v>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1781976797199</t>
+        </is>
+      </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
@@ -10207,7 +10433,11 @@
         <v>0</v>
       </c>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58400/a1e68da9-4810-41b6-9e98-f107cc3afb1d.jpg</t>
+        </is>
+      </c>
       <c r="X64" t="n">
         <v>0</v>
       </c>
@@ -10963,7 +11193,11 @@
         <v>58496</v>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1781976875705</t>
+        </is>
+      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -10984,7 +11218,11 @@
         <v>0</v>
       </c>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58405/be7c4409-4217-4f14-8621-cac6bd144840.jpg</t>
+        </is>
+      </c>
       <c r="X69" t="n">
         <v>0</v>
       </c>
@@ -11269,7 +11507,11 @@
         <v>58498</v>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1781976868105</t>
+        </is>
+      </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
@@ -11290,7 +11532,11 @@
         <v>0</v>
       </c>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58407/74aa8f51-3157-4d37-8891-c91d6351ebf4.jpg</t>
+        </is>
+      </c>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -11418,7 +11664,11 @@
         <v>58499</v>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1781976795307</t>
+        </is>
+      </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
@@ -11439,7 +11689,11 @@
         <v>0</v>
       </c>
       <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/58408/59d907a2-5c94-4a2c-9f4d-da3972ac77f1.jpg</t>
+        </is>
+      </c>
       <c r="X72" t="n">
         <v>0</v>
       </c>
@@ -11567,7 +11821,11 @@
         <v>148640</v>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1781976931820</t>
+        </is>
+      </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
@@ -11588,7 +11846,11 @@
         <v>0</v>
       </c>
       <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643928/fe8032c7-fada-4bbe-9e4c-da1ccde2d3b7.jpg</t>
+        </is>
+      </c>
       <c r="X73" t="n">
         <v>0</v>
       </c>
@@ -11716,7 +11978,11 @@
         <v>148641</v>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1781976894540</t>
+        </is>
+      </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
@@ -11737,7 +12003,11 @@
         <v>0</v>
       </c>
       <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643929/e09216c2-7e01-4e73-ad1f-0d9098956ead.jpg</t>
+        </is>
+      </c>
       <c r="X74" t="n">
         <v>0</v>
       </c>
@@ -12022,7 +12292,11 @@
         <v>148643</v>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1781976764733</t>
+        </is>
+      </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
@@ -12043,7 +12317,11 @@
         <v>0</v>
       </c>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643931/0a908368-bed4-40be-9af4-880f109f9482.jpg</t>
+        </is>
+      </c>
       <c r="X76" t="n">
         <v>0</v>
       </c>
@@ -12171,7 +12449,11 @@
         <v>148644</v>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1781976874095</t>
+        </is>
+      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -12192,7 +12474,11 @@
         <v>0</v>
       </c>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643932/cbdcb851-4a66-4722-8ca2-2ef355c89012.jpg</t>
+        </is>
+      </c>
       <c r="X77" t="n">
         <v>0</v>
       </c>
@@ -12791,7 +13077,11 @@
         <v>148648</v>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1781977065462</t>
+        </is>
+      </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
@@ -12812,7 +13102,11 @@
         <v>0</v>
       </c>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643936/95cff88c-d4f7-45a2-a460-e8d5aaf3062d.jpg</t>
+        </is>
+      </c>
       <c r="X81" t="n">
         <v>0</v>
       </c>
@@ -12940,7 +13234,11 @@
         <v>148649</v>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1781976888242</t>
+        </is>
+      </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
@@ -12961,7 +13259,11 @@
         <v>0</v>
       </c>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643937/558948bf-e8ee-4d75-955e-6250c0f331f4.jpg</t>
+        </is>
+      </c>
       <c r="X82" t="n">
         <v>0</v>
       </c>
@@ -13246,7 +13548,11 @@
         <v>148651</v>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1781976857633</t>
+        </is>
+      </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
@@ -13267,7 +13573,11 @@
         <v>0</v>
       </c>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643939/35fbabf7-81b7-4822-abc6-778ad6f6782f.jpg</t>
+        </is>
+      </c>
       <c r="X84" t="n">
         <v>0</v>
       </c>
@@ -13395,7 +13705,11 @@
         <v>148652</v>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1781976805643</t>
+        </is>
+      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
@@ -13416,7 +13730,11 @@
         <v>0</v>
       </c>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4346/643940/2fdea8fb-c044-49d9-ba38-d6c37b5ab75d.jpg</t>
+        </is>
+      </c>
       <c r="X85" t="n">
         <v>0</v>
       </c>
@@ -13544,7 +13862,11 @@
         <v>58500</v>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1781976808897</t>
+        </is>
+      </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
@@ -13565,7 +13887,11 @@
         <v>0</v>
       </c>
       <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58409/6cd8b753-d271-46d9-8100-08aab8fc748b.jpg</t>
+        </is>
+      </c>
       <c r="X86" t="n">
         <v>0</v>
       </c>
@@ -13693,7 +14019,11 @@
         <v>58501</v>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>1781976904163</t>
+        </is>
+      </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
@@ -13714,7 +14044,11 @@
         <v>0</v>
       </c>
       <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58410/87695fa9-a2dc-42e8-bdc2-b4747c746c09.jpg</t>
+        </is>
+      </c>
       <c r="X87" t="n">
         <v>0</v>
       </c>
@@ -13999,7 +14333,11 @@
         <v>58503</v>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>1781976931923</t>
+        </is>
+      </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
@@ -14020,7 +14358,11 @@
         <v>0</v>
       </c>
       <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58412/b742b6b5-8da9-4262-9bac-90b02fae6bff.jpg</t>
+        </is>
+      </c>
       <c r="X89" t="n">
         <v>0</v>
       </c>
@@ -14148,7 +14490,11 @@
         <v>58504</v>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1781976787813</t>
+        </is>
+      </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
@@ -14169,7 +14515,11 @@
         <v>0</v>
       </c>
       <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58413/3b7b8b20-5137-4704-881e-c949f3276555.jpg</t>
+        </is>
+      </c>
       <c r="X90" t="n">
         <v>0</v>
       </c>
@@ -14454,7 +14804,11 @@
         <v>58506</v>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1781976771842</t>
+        </is>
+      </c>
       <c r="O92" t="n">
         <v>0</v>
       </c>
@@ -14475,7 +14829,11 @@
         <v>0</v>
       </c>
       <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58415/f6badbb1-a011-488a-8b51-bac5548440d7.jpg</t>
+        </is>
+      </c>
       <c r="X92" t="n">
         <v>0</v>
       </c>
@@ -14917,7 +15275,11 @@
         <v>58509</v>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>1781976783053</t>
+        </is>
+      </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
@@ -14938,7 +15300,11 @@
         <v>0</v>
       </c>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58418/7734da79-95cb-4469-ae6c-991216486da2.jpg</t>
+        </is>
+      </c>
       <c r="X95" t="n">
         <v>0</v>
       </c>
@@ -15066,7 +15432,11 @@
         <v>58510</v>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>1781976765413</t>
+        </is>
+      </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
@@ -15087,7 +15457,11 @@
         <v>0</v>
       </c>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58419/a3a070ab-7414-46ae-9ae5-68e06e4675ee.jpg</t>
+        </is>
+      </c>
       <c r="X96" t="n">
         <v>0</v>
       </c>
@@ -15215,7 +15589,11 @@
         <v>58511</v>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>1781976869823</t>
+        </is>
+      </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
@@ -15236,7 +15614,11 @@
         <v>0</v>
       </c>
       <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58420/538c92cf-ec4d-4919-8d3e-0ea282ebd653.jpg</t>
+        </is>
+      </c>
       <c r="X97" t="n">
         <v>0</v>
       </c>
@@ -15364,7 +15746,11 @@
         <v>58512</v>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>1781977082874</t>
+        </is>
+      </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
@@ -15385,7 +15771,11 @@
         <v>0</v>
       </c>
       <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/58421/2d7607c8-c5a6-490c-85ee-ab225bd78595.jpg</t>
+        </is>
+      </c>
       <c r="X98" t="n">
         <v>0</v>
       </c>
@@ -16455,7 +16845,11 @@
         <v>148657</v>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>1781976902604</t>
+        </is>
+      </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
@@ -16476,7 +16870,11 @@
         <v>0</v>
       </c>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643945/2b3c74b2-2faa-491b-950c-8a43bbd72a3a.jpg</t>
+        </is>
+      </c>
       <c r="X105" t="n">
         <v>0</v>
       </c>
@@ -16604,7 +17002,11 @@
         <v>148658</v>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>1781976758853</t>
+        </is>
+      </c>
       <c r="O106" t="n">
         <v>0</v>
       </c>
@@ -16625,7 +17027,11 @@
         <v>0</v>
       </c>
       <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643946/6b184262-e5f3-4907-9e30-d8c2dfb085d5.jpg</t>
+        </is>
+      </c>
       <c r="X106" t="n">
         <v>0</v>
       </c>
@@ -17224,7 +17630,11 @@
         <v>148662</v>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1781976912373</t>
+        </is>
+      </c>
       <c r="O110" t="n">
         <v>0</v>
       </c>
@@ -17245,7 +17655,11 @@
         <v>0</v>
       </c>
       <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643950/760d8099-d919-4135-a5ca-e57930d09105.jpg</t>
+        </is>
+      </c>
       <c r="X110" t="n">
         <v>0</v>
       </c>
@@ -17373,7 +17787,11 @@
         <v>148663</v>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>1781976942008</t>
+        </is>
+      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -17394,7 +17812,11 @@
         <v>0</v>
       </c>
       <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643951/8c46c30a-c1b3-4123-924d-5f6001073430.jpg</t>
+        </is>
+      </c>
       <c r="X111" t="n">
         <v>0</v>
       </c>
@@ -17522,7 +17944,11 @@
         <v>148664</v>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>1781976910696</t>
+        </is>
+      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -17543,7 +17969,11 @@
         <v>0</v>
       </c>
       <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4347/643952/fbb16a75-4be1-402c-8dc5-ec85cffeb329.jpg</t>
+        </is>
+      </c>
       <c r="X112" t="n">
         <v>0</v>
       </c>
@@ -17671,7 +18101,11 @@
         <v>58515</v>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>1781976899245</t>
+        </is>
+      </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
@@ -17692,7 +18126,11 @@
         <v>0</v>
       </c>
       <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58424/a9f68b10-e898-4f74-838a-0ca6adb6a89d.jpg</t>
+        </is>
+      </c>
       <c r="X113" t="n">
         <v>0</v>
       </c>
@@ -18267,7 +18705,11 @@
         <v>58519</v>
       </c>
       <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>1781977225119</t>
+        </is>
+      </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
@@ -18288,7 +18730,11 @@
         <v>0</v>
       </c>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58428/061ac5d8-2a81-49c2-bea4-832f841ee940.jpg</t>
+        </is>
+      </c>
       <c r="X117" t="n">
         <v>0</v>
       </c>
@@ -18416,7 +18862,11 @@
         <v>58520</v>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1781976862305</t>
+        </is>
+      </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
@@ -18437,7 +18887,11 @@
         <v>0</v>
       </c>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58429/8e91d3ca-cbd6-4f9e-a839-9bd223995a7d.jpg</t>
+        </is>
+      </c>
       <c r="X118" t="n">
         <v>0</v>
       </c>
@@ -18565,7 +19019,11 @@
         <v>58521</v>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>1781976925068</t>
+        </is>
+      </c>
       <c r="O119" t="n">
         <v>0</v>
       </c>
@@ -18586,7 +19044,11 @@
         <v>0</v>
       </c>
       <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58430/d0ed70a4-6127-46ed-a7d0-8faee90bf51c.jpg</t>
+        </is>
+      </c>
       <c r="X119" t="n">
         <v>0</v>
       </c>
@@ -18714,7 +19176,11 @@
         <v>58522</v>
       </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>1781976809802</t>
+        </is>
+      </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
@@ -18735,7 +19201,11 @@
         <v>0</v>
       </c>
       <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58431/0a0ee09c-d3b3-4890-8dd4-19f7c5d716ce.jpg</t>
+        </is>
+      </c>
       <c r="X120" t="n">
         <v>0</v>
       </c>
@@ -18863,7 +19333,11 @@
         <v>58523</v>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>1781977176197</t>
+        </is>
+      </c>
       <c r="O121" t="n">
         <v>0</v>
       </c>
@@ -18884,7 +19358,11 @@
         <v>0</v>
       </c>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58432/28da0f4a-5a4b-4321-aaea-1312e6a390c1.jpg</t>
+        </is>
+      </c>
       <c r="X121" t="n">
         <v>0</v>
       </c>
@@ -19012,7 +19490,11 @@
         <v>58524</v>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>1781976921601</t>
+        </is>
+      </c>
       <c r="O122" t="n">
         <v>0</v>
       </c>
@@ -19033,7 +19515,11 @@
         <v>0</v>
       </c>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58433/0bdf7139-9da1-4569-b5b9-ec88526bf36e.jpg</t>
+        </is>
+      </c>
       <c r="X122" t="n">
         <v>0</v>
       </c>
@@ -19467,7 +19953,11 @@
         <v>58527</v>
       </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>1781976849484</t>
+        </is>
+      </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
@@ -19488,7 +19978,11 @@
         <v>0</v>
       </c>
       <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58436/55dab491-6c64-4c45-8af1-6b7bc038d768.jpg</t>
+        </is>
+      </c>
       <c r="X125" t="n">
         <v>0</v>
       </c>
@@ -19616,7 +20110,11 @@
         <v>58528</v>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>1781976783811</t>
+        </is>
+      </c>
       <c r="O126" t="n">
         <v>0</v>
       </c>
@@ -19637,7 +20135,11 @@
         <v>0</v>
       </c>
       <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58437/90bead5a-bebf-44e4-80e9-c2e2ae8f9419.jpg</t>
+        </is>
+      </c>
       <c r="X126" t="n">
         <v>0</v>
       </c>
@@ -19765,7 +20267,11 @@
         <v>58529</v>
       </c>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>1781976940237</t>
+        </is>
+      </c>
       <c r="O127" t="n">
         <v>0</v>
       </c>
@@ -19786,7 +20292,11 @@
         <v>0</v>
       </c>
       <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58438/2f683123-d143-466f-a7b1-611aeb164d86.jpg</t>
+        </is>
+      </c>
       <c r="X127" t="n">
         <v>0</v>
       </c>
@@ -19914,7 +20424,11 @@
         <v>58530</v>
       </c>
       <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>1781976782085</t>
+        </is>
+      </c>
       <c r="O128" t="n">
         <v>0</v>
       </c>
@@ -19935,7 +20449,11 @@
         <v>0</v>
       </c>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58439/f952abd7-a432-44b6-9471-c1d4b7538a87.jpg</t>
+        </is>
+      </c>
       <c r="X128" t="n">
         <v>0</v>
       </c>
@@ -20212,7 +20730,11 @@
         <v>148666</v>
       </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>1781977151916</t>
+        </is>
+      </c>
       <c r="O130" t="n">
         <v>0</v>
       </c>
@@ -20233,7 +20755,11 @@
         <v>0</v>
       </c>
       <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/643954/ceb84911-e1b7-4a5b-a298-18a589e94b1a.jpg</t>
+        </is>
+      </c>
       <c r="X130" t="n">
         <v>0</v>
       </c>
@@ -20659,7 +21185,11 @@
         <v>148669</v>
       </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>1781976894067</t>
+        </is>
+      </c>
       <c r="O133" t="n">
         <v>0</v>
       </c>
@@ -20680,7 +21210,11 @@
         <v>0</v>
       </c>
       <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/643957/0527cd5e-f974-4bf7-ba33-6f6abac2945a.jpg</t>
+        </is>
+      </c>
       <c r="X133" t="n">
         <v>0</v>
       </c>
@@ -20808,7 +21342,11 @@
         <v>58531</v>
       </c>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>1781976803751</t>
+        </is>
+      </c>
       <c r="O134" t="n">
         <v>0</v>
       </c>
@@ -20829,7 +21367,11 @@
         <v>0</v>
       </c>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58440/41ba5024-e541-45fe-8d98-eb6214b49a48.jpg</t>
+        </is>
+      </c>
       <c r="X134" t="n">
         <v>0</v>
       </c>
@@ -21428,7 +21970,11 @@
         <v>58535</v>
       </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>1781976903401</t>
+        </is>
+      </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
@@ -21449,7 +21995,11 @@
         <v>0</v>
       </c>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58444/445f8fbb-6f8d-4aba-b1ba-83e01ff54463.jpg</t>
+        </is>
+      </c>
       <c r="X138" t="n">
         <v>0</v>
       </c>
@@ -21577,7 +22127,11 @@
         <v>58536</v>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>1781976809224</t>
+        </is>
+      </c>
       <c r="O139" t="n">
         <v>0</v>
       </c>
@@ -21598,7 +22152,11 @@
         <v>0</v>
       </c>
       <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58445/b6e8cc0e-830a-4c4c-8422-a2f2334309be.jpg</t>
+        </is>
+      </c>
       <c r="X139" t="n">
         <v>0</v>
       </c>
@@ -21726,7 +22284,11 @@
         <v>58537</v>
       </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>1781977037005</t>
+        </is>
+      </c>
       <c r="O140" t="n">
         <v>0</v>
       </c>
@@ -21747,7 +22309,11 @@
         <v>0</v>
       </c>
       <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58446/30496457-e7ef-4fbc-a509-d34714147d3e.jpg</t>
+        </is>
+      </c>
       <c r="X140" t="n">
         <v>0</v>
       </c>
@@ -21875,7 +22441,11 @@
         <v>58538</v>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>1781976939094</t>
+        </is>
+      </c>
       <c r="O141" t="n">
         <v>0</v>
       </c>
@@ -21896,7 +22466,11 @@
         <v>0</v>
       </c>
       <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58447/2b10db2f-c913-4cb8-8dac-4050f58b04e7.jpg</t>
+        </is>
+      </c>
       <c r="X141" t="n">
         <v>0</v>
       </c>
@@ -22024,7 +22598,11 @@
         <v>58539</v>
       </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>1781976931241</t>
+        </is>
+      </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
@@ -22045,7 +22623,11 @@
         <v>0</v>
       </c>
       <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58448/c3ec814c-ecd2-492a-b135-5bd92d99a246.jpg</t>
+        </is>
+      </c>
       <c r="X142" t="n">
         <v>0</v>
       </c>
@@ -22173,7 +22755,11 @@
         <v>58540</v>
       </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>1781976798497</t>
+        </is>
+      </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
@@ -22194,7 +22780,11 @@
         <v>0</v>
       </c>
       <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58449/ccec1fb5-b22c-45dc-856f-f8f8f93b697b.jpg</t>
+        </is>
+      </c>
       <c r="X143" t="n">
         <v>0</v>
       </c>
@@ -22479,7 +23069,11 @@
         <v>58542</v>
       </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>1781976790216</t>
+        </is>
+      </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
@@ -22500,7 +23094,11 @@
         <v>0</v>
       </c>
       <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58451/0a315c94-2c91-4003-aed2-2125d88d5c36.jpg</t>
+        </is>
+      </c>
       <c r="X145" t="n">
         <v>0</v>
       </c>
@@ -22628,7 +23226,11 @@
         <v>58543</v>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1781976935971</t>
+        </is>
+      </c>
       <c r="O146" t="n">
         <v>0</v>
       </c>
@@ -22649,7 +23251,11 @@
         <v>0</v>
       </c>
       <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58452/9502ca8d-2459-4213-8346-e3d46995ceba.jpg</t>
+        </is>
+      </c>
       <c r="X146" t="n">
         <v>0</v>
       </c>
@@ -23546,7 +24152,11 @@
         <v>148671</v>
       </c>
       <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>1781976815170</t>
+        </is>
+      </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
@@ -23567,7 +24177,11 @@
         <v>0</v>
       </c>
       <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/643959/9b6dd10a-3350-46b0-9857-95c5d21d846b.jpg</t>
+        </is>
+      </c>
       <c r="X152" t="n">
         <v>0</v>
       </c>
@@ -23695,7 +24309,11 @@
         <v>148672</v>
       </c>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>1781976934559</t>
+        </is>
+      </c>
       <c r="O153" t="n">
         <v>0</v>
       </c>
@@ -23716,7 +24334,11 @@
         <v>0</v>
       </c>
       <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/643960/0f17b108-19fe-47bc-8941-9c98a0b122f8.jpg</t>
+        </is>
+      </c>
       <c r="X153" t="n">
         <v>0</v>
       </c>
@@ -24307,7 +24929,11 @@
         <v>148676</v>
       </c>
       <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1781976939659</t>
+        </is>
+      </c>
       <c r="O157" t="n">
         <v>0</v>
       </c>
@@ -24328,7 +24954,11 @@
         <v>0</v>
       </c>
       <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/643964/774cdc7c-1638-4a98-95b7-ba4e87429da4.jpg</t>
+        </is>
+      </c>
       <c r="X157" t="n">
         <v>0</v>
       </c>
@@ -24770,7 +25400,11 @@
         <v>58550</v>
       </c>
       <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>1781976978100</t>
+        </is>
+      </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
@@ -24791,7 +25425,11 @@
         <v>0</v>
       </c>
       <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58459/c4c9a6f5-9497-4d25-ac2e-05ad419931d8.jpg</t>
+        </is>
+      </c>
       <c r="X160" t="n">
         <v>0</v>
       </c>
@@ -24919,7 +25557,11 @@
         <v>58551</v>
       </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>1781977111528</t>
+        </is>
+      </c>
       <c r="O161" t="n">
         <v>0</v>
       </c>
@@ -24940,7 +25582,11 @@
         <v>0</v>
       </c>
       <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58460/0bc5aeba-731e-434f-84c8-c86844a9ec44.jpg</t>
+        </is>
+      </c>
       <c r="X161" t="n">
         <v>0</v>
       </c>
@@ -25068,7 +25714,11 @@
         <v>58552</v>
       </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>1781976921559</t>
+        </is>
+      </c>
       <c r="O162" t="n">
         <v>0</v>
       </c>
@@ -25089,7 +25739,11 @@
         <v>0</v>
       </c>
       <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58461/320b7a64-0376-4b6b-a722-969ddfae2846.jpg</t>
+        </is>
+      </c>
       <c r="X162" t="n">
         <v>0</v>
       </c>
@@ -25374,7 +26028,11 @@
         <v>58554</v>
       </c>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>1781976957125</t>
+        </is>
+      </c>
       <c r="O164" t="n">
         <v>0</v>
       </c>
@@ -25395,7 +26053,11 @@
         <v>0</v>
       </c>
       <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58463/6fba6fb8-13d2-4e87-bb2a-6e515960e8f3.jpg</t>
+        </is>
+      </c>
       <c r="X164" t="n">
         <v>0</v>
       </c>
@@ -25523,7 +26185,11 @@
         <v>58555</v>
       </c>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>1781976805960</t>
+        </is>
+      </c>
       <c r="O165" t="n">
         <v>0</v>
       </c>
@@ -25544,7 +26210,11 @@
         <v>0</v>
       </c>
       <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58464/f1555ced-5325-443e-8f26-f2ac2dcce187.jpg</t>
+        </is>
+      </c>
       <c r="X165" t="n">
         <v>0</v>
       </c>
@@ -25671,29 +26341,43 @@
       <c r="L166" t="n">
         <v>58556</v>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>1781976896505</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>1781976895577</t>
+        </is>
+      </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
-      <c r="R166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>6a36cf3f370583337b6e7301</t>
+        </is>
+      </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="U166" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/58465/b5bf96a2-b443-47ef-a7a0-faf45525dd1d.jpg</t>
+        </is>
+      </c>
       <c r="X166" t="n">
         <v>0</v>
       </c>
@@ -25710,7 +26394,7 @@
         <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -25978,7 +26662,11 @@
         <v>148678</v>
       </c>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>1781976811492</t>
+        </is>
+      </c>
       <c r="O168" t="n">
         <v>0</v>
       </c>
@@ -25999,7 +26687,11 @@
         <v>0</v>
       </c>
       <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/643966/806641d9-0f7c-4fc4-9912-51157561216b.jpg</t>
+        </is>
+      </c>
       <c r="X168" t="n">
         <v>0</v>
       </c>
@@ -26284,7 +26976,11 @@
         <v>148680</v>
       </c>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>1781976832347</t>
+        </is>
+      </c>
       <c r="O170" t="n">
         <v>0</v>
       </c>
@@ -26305,7 +27001,11 @@
         <v>0</v>
       </c>
       <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4350/643968/ac2556fb-f4b8-41d0-b289-512d7dc65257.jpg</t>
+        </is>
+      </c>
       <c r="X170" t="n">
         <v>0</v>
       </c>
@@ -26432,29 +27132,43 @@
       <c r="L171" t="n">
         <v>58557</v>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>1781976751067</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>1781976750464</t>
+        </is>
+      </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
-      <c r="R171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>6a36ceae370583337b6e6d3d</t>
+        </is>
+      </c>
       <c r="S171" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58466/4231c6b7-e20d-4cc5-8a35-8808756d30f1.jpg</t>
+        </is>
+      </c>
       <c r="X171" t="n">
         <v>0</v>
       </c>
@@ -26471,13 +27185,13 @@
         <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AD171" t="n">
         <v>0</v>
       </c>
       <c r="AE171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF171" t="n">
         <v>0</v>
@@ -26489,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="AI171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ171" t="n">
         <v>0</v>
@@ -26888,7 +27602,11 @@
         <v>58560</v>
       </c>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>1781976838730</t>
+        </is>
+      </c>
       <c r="O174" t="n">
         <v>0</v>
       </c>
@@ -26909,7 +27627,11 @@
         <v>0</v>
       </c>
       <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58469/0d1cb3b9-6bfa-4ff1-8742-525f436915fc.jpg</t>
+        </is>
+      </c>
       <c r="X174" t="n">
         <v>0</v>
       </c>
@@ -27037,7 +27759,11 @@
         <v>58561</v>
       </c>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1781976881866</t>
+        </is>
+      </c>
       <c r="O175" t="n">
         <v>0</v>
       </c>
@@ -27058,7 +27784,11 @@
         <v>0</v>
       </c>
       <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58470/8ad3f178-9535-4e8b-b45f-f38b2934a9ea.jpg</t>
+        </is>
+      </c>
       <c r="X175" t="n">
         <v>0</v>
       </c>
@@ -27335,7 +28065,11 @@
         <v>58563</v>
       </c>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>1781976762003</t>
+        </is>
+      </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
@@ -27356,7 +28090,11 @@
         <v>0</v>
       </c>
       <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58472/a7ca2955-e128-44bc-b97d-67ece23edcda.jpg</t>
+        </is>
+      </c>
       <c r="X177" t="n">
         <v>0</v>
       </c>
@@ -27955,7 +28693,11 @@
         <v>148684</v>
       </c>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>1781976871283</t>
+        </is>
+      </c>
       <c r="O181" t="n">
         <v>0</v>
       </c>
@@ -27976,7 +28718,11 @@
         <v>0</v>
       </c>
       <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/643972/c49af578-bccf-42c1-b12d-327b10d6e6bc.jpg</t>
+        </is>
+      </c>
       <c r="X181" t="n">
         <v>0</v>
       </c>
@@ -28104,7 +28850,11 @@
         <v>148685</v>
       </c>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>1781976875449</t>
+        </is>
+      </c>
       <c r="O182" t="n">
         <v>0</v>
       </c>
@@ -28125,7 +28875,11 @@
         <v>0</v>
       </c>
       <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/643973/22c5f8d5-b0dc-4350-8b5b-2d239d7b060b.jpg</t>
+        </is>
+      </c>
       <c r="X182" t="n">
         <v>0</v>
       </c>
@@ -28410,7 +29164,11 @@
         <v>58565</v>
       </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>1781976891304</t>
+        </is>
+      </c>
       <c r="O184" t="n">
         <v>0</v>
       </c>
@@ -28431,7 +29189,11 @@
         <v>0</v>
       </c>
       <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr"/>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58474/bbd5ac62-ab9d-4dfe-95d7-be5a0d5f4a58.jpg</t>
+        </is>
+      </c>
       <c r="X184" t="n">
         <v>0</v>
       </c>
@@ -28716,7 +29478,11 @@
         <v>58567</v>
       </c>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>1781976943698</t>
+        </is>
+      </c>
       <c r="O186" t="n">
         <v>0</v>
       </c>
@@ -28737,7 +29503,11 @@
         <v>0</v>
       </c>
       <c r="V186" t="inlineStr"/>
-      <c r="W186" t="inlineStr"/>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58476/dfc45df6-13b5-4a6a-bff5-077b9588fc7c.jpg</t>
+        </is>
+      </c>
       <c r="X186" t="n">
         <v>0</v>
       </c>
@@ -29022,7 +29792,11 @@
         <v>58569</v>
       </c>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>1781976750913</t>
+        </is>
+      </c>
       <c r="O188" t="n">
         <v>0</v>
       </c>
@@ -29043,7 +29817,11 @@
         <v>0</v>
       </c>
       <c r="V188" t="inlineStr"/>
-      <c r="W188" t="inlineStr"/>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58478/a8cb3bed-a159-4031-a59d-b7b8405a56e9.jpg</t>
+        </is>
+      </c>
       <c r="X188" t="n">
         <v>0</v>
       </c>
@@ -29171,7 +29949,11 @@
         <v>58570</v>
       </c>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>1781976918037</t>
+        </is>
+      </c>
       <c r="O189" t="n">
         <v>0</v>
       </c>
@@ -29192,7 +29974,11 @@
         <v>0</v>
       </c>
       <c r="V189" t="inlineStr"/>
-      <c r="W189" t="inlineStr"/>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58479/54592d1f-3583-4c81-bf1c-6195408f3b19.jpg</t>
+        </is>
+      </c>
       <c r="X189" t="n">
         <v>0</v>
       </c>
@@ -29320,7 +30106,11 @@
         <v>58571</v>
       </c>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>1781976868077</t>
+        </is>
+      </c>
       <c r="O190" t="n">
         <v>0</v>
       </c>
@@ -29341,7 +30131,11 @@
         <v>0</v>
       </c>
       <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58480/5fdc3ecc-3f2d-4a82-ba83-6630baff4d86.jpg</t>
+        </is>
+      </c>
       <c r="X190" t="n">
         <v>0</v>
       </c>
@@ -29469,7 +30263,11 @@
         <v>58572</v>
       </c>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>1781976875999</t>
+        </is>
+      </c>
       <c r="O191" t="n">
         <v>0</v>
       </c>
@@ -29490,7 +30288,11 @@
         <v>0</v>
       </c>
       <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58481/1fbe3c11-7ce1-4875-8286-b18fb9a325cd.jpg</t>
+        </is>
+      </c>
       <c r="X191" t="n">
         <v>0</v>
       </c>
@@ -29618,7 +30420,11 @@
         <v>58573</v>
       </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>1781976888321</t>
+        </is>
+      </c>
       <c r="O192" t="n">
         <v>0</v>
       </c>
@@ -29639,7 +30445,11 @@
         <v>0</v>
       </c>
       <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58482/3cb34443-a33a-468e-a9d3-8a20c2b6a2b7.jpg</t>
+        </is>
+      </c>
       <c r="X192" t="n">
         <v>0</v>
       </c>
@@ -29923,29 +30733,43 @@
       <c r="L194" t="n">
         <v>58575</v>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>1781976883575</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>1781976882957</t>
+        </is>
+      </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>6a36cf33370583337b6e7295</t>
+        </is>
+      </c>
       <c r="S194" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="U194" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58484/749889d4-6c2f-49f5-a719-c408c30411da.jpg</t>
+        </is>
+      </c>
       <c r="X194" t="n">
         <v>0</v>
       </c>
@@ -29962,7 +30786,7 @@
         <v>0</v>
       </c>
       <c r="AC194" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -30073,7 +30897,11 @@
         <v>58576</v>
       </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>1781976919859</t>
+        </is>
+      </c>
       <c r="O195" t="n">
         <v>0</v>
       </c>
@@ -30094,7 +30922,11 @@
         <v>0</v>
       </c>
       <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58485/7b8b2a2a-a929-4508-b06a-60c2cd179eea.jpg</t>
+        </is>
+      </c>
       <c r="X195" t="n">
         <v>0</v>
       </c>
@@ -30222,7 +31054,11 @@
         <v>58577</v>
       </c>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>1781976908572</t>
+        </is>
+      </c>
       <c r="O196" t="n">
         <v>0</v>
       </c>
@@ -30243,7 +31079,11 @@
         <v>0</v>
       </c>
       <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58486/63564116-54ae-4d1a-b3e7-d8f376f21d76.jpg</t>
+        </is>
+      </c>
       <c r="X196" t="n">
         <v>0</v>
       </c>
@@ -30371,7 +31211,11 @@
         <v>58578</v>
       </c>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>1781976882483</t>
+        </is>
+      </c>
       <c r="O197" t="n">
         <v>0</v>
       </c>
@@ -30392,7 +31236,11 @@
         <v>0</v>
       </c>
       <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58487/4c7b931f-294a-4708-8960-9248831b7d4c.jpg</t>
+        </is>
+      </c>
       <c r="X197" t="n">
         <v>0</v>
       </c>
@@ -30520,7 +31368,11 @@
         <v>58579</v>
       </c>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>1781976872882</t>
+        </is>
+      </c>
       <c r="O198" t="n">
         <v>0</v>
       </c>
@@ -30541,7 +31393,11 @@
         <v>0</v>
       </c>
       <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58488/fd3410f6-fb26-4e57-8c2d-be5837eb5ebc.jpg</t>
+        </is>
+      </c>
       <c r="X198" t="n">
         <v>0</v>
       </c>
@@ -30669,7 +31525,11 @@
         <v>58580</v>
       </c>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>1781976832406</t>
+        </is>
+      </c>
       <c r="O199" t="n">
         <v>0</v>
       </c>
@@ -30690,7 +31550,11 @@
         <v>0</v>
       </c>
       <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr"/>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58489/be2dfc73-d3f5-4e51-86c4-c0f718cfa5db.jpg</t>
+        </is>
+      </c>
       <c r="X199" t="n">
         <v>0</v>
       </c>
@@ -30818,7 +31682,11 @@
         <v>58581</v>
       </c>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>1781976758846</t>
+        </is>
+      </c>
       <c r="O200" t="n">
         <v>0</v>
       </c>
@@ -30839,7 +31707,11 @@
         <v>0</v>
       </c>
       <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/58490/6bb72c86-e843-4a84-ab44-ad7d1ca92650.jpg</t>
+        </is>
+      </c>
       <c r="X200" t="n">
         <v>0</v>
       </c>
@@ -31281,7 +32153,11 @@
         <v>148688</v>
       </c>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>1781976887452</t>
+        </is>
+      </c>
       <c r="O203" t="n">
         <v>0</v>
       </c>
@@ -31302,7 +32178,11 @@
         <v>0</v>
       </c>
       <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr"/>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643976/2d388566-7653-4421-9fc5-55f0a348eb84.jpg</t>
+        </is>
+      </c>
       <c r="X203" t="n">
         <v>0</v>
       </c>
@@ -31430,7 +32310,11 @@
         <v>148689</v>
       </c>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>1781976930764</t>
+        </is>
+      </c>
       <c r="O204" t="n">
         <v>0</v>
       </c>
@@ -31451,7 +32335,11 @@
         <v>0</v>
       </c>
       <c r="V204" t="inlineStr"/>
-      <c r="W204" t="inlineStr"/>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643977/f5411dc6-177f-4a60-9072-046901d5a55a.jpg</t>
+        </is>
+      </c>
       <c r="X204" t="n">
         <v>0</v>
       </c>
@@ -31579,7 +32467,11 @@
         <v>148690</v>
       </c>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>1781976885107</t>
+        </is>
+      </c>
       <c r="O205" t="n">
         <v>0</v>
       </c>
@@ -31600,7 +32492,11 @@
         <v>0</v>
       </c>
       <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr"/>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643978/46a4cecf-378c-4e26-bbec-63242f3a2133.jpg</t>
+        </is>
+      </c>
       <c r="X205" t="n">
         <v>0</v>
       </c>
@@ -31728,7 +32624,11 @@
         <v>148691</v>
       </c>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>1781976943755</t>
+        </is>
+      </c>
       <c r="O206" t="n">
         <v>0</v>
       </c>
@@ -31749,7 +32649,11 @@
         <v>0</v>
       </c>
       <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr"/>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643979/0ba0f145-0a5a-453f-af11-b4a24476166d.jpg</t>
+        </is>
+      </c>
       <c r="X206" t="n">
         <v>0</v>
       </c>
@@ -32034,7 +32938,11 @@
         <v>148693</v>
       </c>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>1781976901716</t>
+        </is>
+      </c>
       <c r="O208" t="n">
         <v>0</v>
       </c>
@@ -32055,7 +32963,11 @@
         <v>0</v>
       </c>
       <c r="V208" t="inlineStr"/>
-      <c r="W208" t="inlineStr"/>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643981/959dd970-e2ce-45aa-9ec4-ee304b181e3b.jpg</t>
+        </is>
+      </c>
       <c r="X208" t="n">
         <v>0</v>
       </c>
@@ -32183,7 +33095,11 @@
         <v>148694</v>
       </c>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>1781976847018</t>
+        </is>
+      </c>
       <c r="O209" t="n">
         <v>0</v>
       </c>
@@ -32204,7 +33120,11 @@
         <v>0</v>
       </c>
       <c r="V209" t="inlineStr"/>
-      <c r="W209" t="inlineStr"/>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643982/4385a28b-1748-48d4-99dc-289e3bbe83dd.jpg</t>
+        </is>
+      </c>
       <c r="X209" t="n">
         <v>0</v>
       </c>
@@ -32489,7 +33409,11 @@
         <v>148696</v>
       </c>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>1781976923417</t>
+        </is>
+      </c>
       <c r="O211" t="n">
         <v>0</v>
       </c>
@@ -32510,7 +33434,11 @@
         <v>0</v>
       </c>
       <c r="V211" t="inlineStr"/>
-      <c r="W211" t="inlineStr"/>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643984/9607ae55-b4e0-4fe2-b6dd-d0cef64d79d6.jpg</t>
+        </is>
+      </c>
       <c r="X211" t="n">
         <v>0</v>
       </c>
@@ -32795,7 +33723,11 @@
         <v>148698</v>
       </c>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>1781976782211</t>
+        </is>
+      </c>
       <c r="O213" t="n">
         <v>0</v>
       </c>
@@ -32816,7 +33748,11 @@
         <v>0</v>
       </c>
       <c r="V213" t="inlineStr"/>
-      <c r="W213" t="inlineStr"/>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643986/646d8766-81f4-488e-9d21-887a1ca8d16f.jpg</t>
+        </is>
+      </c>
       <c r="X213" t="n">
         <v>0</v>
       </c>
@@ -33407,7 +34343,11 @@
         <v>148702</v>
       </c>
       <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>1781976831739</t>
+        </is>
+      </c>
       <c r="O217" t="n">
         <v>0</v>
       </c>
@@ -33428,7 +34368,11 @@
         <v>0</v>
       </c>
       <c r="V217" t="inlineStr"/>
-      <c r="W217" t="inlineStr"/>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643990/70a50220-dcc1-4e4d-b0d2-29b84d978435.jpg</t>
+        </is>
+      </c>
       <c r="X217" t="n">
         <v>0</v>
       </c>
@@ -33713,7 +34657,11 @@
         <v>58583</v>
       </c>
       <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>1781976922149</t>
+        </is>
+      </c>
       <c r="O219" t="n">
         <v>0</v>
       </c>
@@ -33734,7 +34682,11 @@
         <v>0</v>
       </c>
       <c r="V219" t="inlineStr"/>
-      <c r="W219" t="inlineStr"/>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58492/3ee76e5d-561f-495d-ab9d-322e0ff50c5c.jpg</t>
+        </is>
+      </c>
       <c r="X219" t="n">
         <v>0</v>
       </c>
@@ -34019,7 +34971,11 @@
         <v>58585</v>
       </c>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>1781976909530</t>
+        </is>
+      </c>
       <c r="O221" t="n">
         <v>0</v>
       </c>
@@ -34040,7 +34996,11 @@
         <v>0</v>
       </c>
       <c r="V221" t="inlineStr"/>
-      <c r="W221" t="inlineStr"/>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58494/7807236d-c597-42b3-8b6f-f07cb20b7142.jpg</t>
+        </is>
+      </c>
       <c r="X221" t="n">
         <v>0</v>
       </c>
@@ -34325,7 +35285,11 @@
         <v>58587</v>
       </c>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>1781977047592</t>
+        </is>
+      </c>
       <c r="O223" t="n">
         <v>0</v>
       </c>
@@ -34346,7 +35310,11 @@
         <v>0</v>
       </c>
       <c r="V223" t="inlineStr"/>
-      <c r="W223" t="inlineStr"/>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58496/d16a3642-4eef-4dcb-84dc-9a92ffbbf1f9.jpg</t>
+        </is>
+      </c>
       <c r="X223" t="n">
         <v>0</v>
       </c>
@@ -34623,7 +35591,11 @@
         <v>58589</v>
       </c>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>1781976930481</t>
+        </is>
+      </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
@@ -34644,7 +35616,11 @@
         <v>0</v>
       </c>
       <c r="V225" t="inlineStr"/>
-      <c r="W225" t="inlineStr"/>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58498/c51269bb-b3e4-409e-9735-7bef1bcf4cb5.jpg</t>
+        </is>
+      </c>
       <c r="X225" t="n">
         <v>0</v>
       </c>
@@ -34772,7 +35748,11 @@
         <v>58590</v>
       </c>
       <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>1781976948749</t>
+        </is>
+      </c>
       <c r="O226" t="n">
         <v>0</v>
       </c>
@@ -34793,7 +35773,11 @@
         <v>0</v>
       </c>
       <c r="V226" t="inlineStr"/>
-      <c r="W226" t="inlineStr"/>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58499/e7aa517c-185e-4b9a-970e-642feda12561.jpg</t>
+        </is>
+      </c>
       <c r="X226" t="n">
         <v>0</v>
       </c>
@@ -35235,7 +36219,11 @@
         <v>58593</v>
       </c>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>1781976875200</t>
+        </is>
+      </c>
       <c r="O229" t="n">
         <v>0</v>
       </c>
@@ -35256,7 +36244,11 @@
         <v>0</v>
       </c>
       <c r="V229" t="inlineStr"/>
-      <c r="W229" t="inlineStr"/>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58502/751db3b3-b8e1-4ee4-a33e-202a2270adb7.jpg</t>
+        </is>
+      </c>
       <c r="X229" t="n">
         <v>0</v>
       </c>
@@ -35384,7 +36376,11 @@
         <v>58594</v>
       </c>
       <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>1781976887101</t>
+        </is>
+      </c>
       <c r="O230" t="n">
         <v>0</v>
       </c>
@@ -35405,7 +36401,11 @@
         <v>0</v>
       </c>
       <c r="V230" t="inlineStr"/>
-      <c r="W230" t="inlineStr"/>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58503/3c637ea9-8b6f-4276-bad0-a50db318fe18.jpg</t>
+        </is>
+      </c>
       <c r="X230" t="n">
         <v>0</v>
       </c>
@@ -35533,7 +36533,11 @@
         <v>58595</v>
       </c>
       <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>1781976773579</t>
+        </is>
+      </c>
       <c r="O231" t="n">
         <v>0</v>
       </c>
@@ -35554,7 +36558,11 @@
         <v>0</v>
       </c>
       <c r="V231" t="inlineStr"/>
-      <c r="W231" t="inlineStr"/>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58504/dead076b-5dcc-4f97-957e-8ba74143a282.jpg</t>
+        </is>
+      </c>
       <c r="X231" t="n">
         <v>0</v>
       </c>
@@ -35682,7 +36690,11 @@
         <v>58596</v>
       </c>
       <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>1781976883100</t>
+        </is>
+      </c>
       <c r="O232" t="n">
         <v>0</v>
       </c>
@@ -35703,7 +36715,11 @@
         <v>0</v>
       </c>
       <c r="V232" t="inlineStr"/>
-      <c r="W232" t="inlineStr"/>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58505/eecd9bcb-fa4f-423e-a32f-ef7bea10fc78.jpg</t>
+        </is>
+      </c>
       <c r="X232" t="n">
         <v>0</v>
       </c>
@@ -35831,7 +36847,11 @@
         <v>58597</v>
       </c>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>1781976902313</t>
+        </is>
+      </c>
       <c r="O233" t="n">
         <v>0</v>
       </c>
@@ -35852,7 +36872,11 @@
         <v>0</v>
       </c>
       <c r="V233" t="inlineStr"/>
-      <c r="W233" t="inlineStr"/>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58506/894fb8b4-20f7-45f3-b97b-529ce670ce24.jpg</t>
+        </is>
+      </c>
       <c r="X233" t="n">
         <v>0</v>
       </c>
@@ -36137,7 +37161,11 @@
         <v>58599</v>
       </c>
       <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>1781976886103</t>
+        </is>
+      </c>
       <c r="O235" t="n">
         <v>0</v>
       </c>
@@ -36158,7 +37186,11 @@
         <v>0</v>
       </c>
       <c r="V235" t="inlineStr"/>
-      <c r="W235" t="inlineStr"/>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58508/4467e172-1cb0-4df7-afe0-c4ef1484c451.jpg</t>
+        </is>
+      </c>
       <c r="X235" t="n">
         <v>0</v>
       </c>
@@ -36443,7 +37475,11 @@
         <v>58601</v>
       </c>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>1781976935442</t>
+        </is>
+      </c>
       <c r="O237" t="n">
         <v>0</v>
       </c>
@@ -36464,7 +37500,11 @@
         <v>0</v>
       </c>
       <c r="V237" t="inlineStr"/>
-      <c r="W237" t="inlineStr"/>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58510/968a0d07-f259-41b8-99d2-7e643a821a23.jpg</t>
+        </is>
+      </c>
       <c r="X237" t="n">
         <v>0</v>
       </c>
@@ -36592,7 +37632,11 @@
         <v>58602</v>
       </c>
       <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>1781977124730</t>
+        </is>
+      </c>
       <c r="O238" t="n">
         <v>0</v>
       </c>
@@ -36613,7 +37657,11 @@
         <v>0</v>
       </c>
       <c r="V238" t="inlineStr"/>
-      <c r="W238" t="inlineStr"/>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58511/a5b1943d-67f6-4e08-8851-52d7cc4120ac.jpg</t>
+        </is>
+      </c>
       <c r="X238" t="n">
         <v>0</v>
       </c>
@@ -36741,7 +37789,11 @@
         <v>58603</v>
       </c>
       <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>1781976891956</t>
+        </is>
+      </c>
       <c r="O239" t="n">
         <v>0</v>
       </c>
@@ -36762,7 +37814,11 @@
         <v>0</v>
       </c>
       <c r="V239" t="inlineStr"/>
-      <c r="W239" t="inlineStr"/>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58512/de9c852f-0253-4872-bc52-e5984da1b6b7.jpg</t>
+        </is>
+      </c>
       <c r="X239" t="n">
         <v>0</v>
       </c>
@@ -36890,7 +37946,11 @@
         <v>58604</v>
       </c>
       <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>1781976802252</t>
+        </is>
+      </c>
       <c r="O240" t="n">
         <v>0</v>
       </c>
@@ -36911,7 +37971,11 @@
         <v>0</v>
       </c>
       <c r="V240" t="inlineStr"/>
-      <c r="W240" t="inlineStr"/>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58513/38a8de56-6706-43c2-879a-9821b2419e75.jpg</t>
+        </is>
+      </c>
       <c r="X240" t="n">
         <v>0</v>
       </c>
@@ -37039,7 +38103,11 @@
         <v>148703</v>
       </c>
       <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>1781976896956</t>
+        </is>
+      </c>
       <c r="O241" t="n">
         <v>0</v>
       </c>
@@ -37060,7 +38128,11 @@
         <v>0</v>
       </c>
       <c r="V241" t="inlineStr"/>
-      <c r="W241" t="inlineStr"/>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/643991/b4e8cdb2-4684-4a6a-adb3-7b062ca92411.jpg</t>
+        </is>
+      </c>
       <c r="X241" t="n">
         <v>0</v>
       </c>
@@ -37188,7 +38260,11 @@
         <v>148704</v>
       </c>
       <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>1781976934835</t>
+        </is>
+      </c>
       <c r="O242" t="n">
         <v>0</v>
       </c>
@@ -37209,7 +38285,11 @@
         <v>0</v>
       </c>
       <c r="V242" t="inlineStr"/>
-      <c r="W242" t="inlineStr"/>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/643992/269f8409-b297-4d98-831e-66d6393838d6.jpg</t>
+        </is>
+      </c>
       <c r="X242" t="n">
         <v>0</v>
       </c>
@@ -37337,7 +38417,11 @@
         <v>148705</v>
       </c>
       <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>1781976899827</t>
+        </is>
+      </c>
       <c r="O243" t="n">
         <v>0</v>
       </c>
@@ -37358,7 +38442,11 @@
         <v>0</v>
       </c>
       <c r="V243" t="inlineStr"/>
-      <c r="W243" t="inlineStr"/>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/643993/8c30a890-446a-41bf-8355-853f20014426.jpg</t>
+        </is>
+      </c>
       <c r="X243" t="n">
         <v>0</v>
       </c>
@@ -37800,7 +38888,11 @@
         <v>148708</v>
       </c>
       <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>1781976800850</t>
+        </is>
+      </c>
       <c r="O246" t="n">
         <v>0</v>
       </c>
@@ -37821,7 +38913,11 @@
         <v>0</v>
       </c>
       <c r="V246" t="inlineStr"/>
-      <c r="W246" t="inlineStr"/>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/643996/635311c2-47e0-4676-9ed2-b50cee58a074.jpg</t>
+        </is>
+      </c>
       <c r="X246" t="n">
         <v>0</v>
       </c>
@@ -38106,7 +39202,11 @@
         <v>148710</v>
       </c>
       <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>1781976798945</t>
+        </is>
+      </c>
       <c r="O248" t="n">
         <v>0</v>
       </c>
@@ -38127,7 +39227,11 @@
         <v>0</v>
       </c>
       <c r="V248" t="inlineStr"/>
-      <c r="W248" t="inlineStr"/>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/643998/c846cef8-1968-4fcb-bdcc-ca1e76632c4a.jpg</t>
+        </is>
+      </c>
       <c r="X248" t="n">
         <v>0</v>
       </c>
@@ -38412,7 +39516,11 @@
         <v>148712</v>
       </c>
       <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>1781976944449</t>
+        </is>
+      </c>
       <c r="O250" t="n">
         <v>0</v>
       </c>
@@ -38433,7 +39541,11 @@
         <v>0</v>
       </c>
       <c r="V250" t="inlineStr"/>
-      <c r="W250" t="inlineStr"/>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/644000/b9a2e8ce-2e6b-4086-b12f-d1d5a85fb600.jpg</t>
+        </is>
+      </c>
       <c r="X250" t="n">
         <v>0</v>
       </c>
@@ -40743,7 +41855,11 @@
         <v>58615</v>
       </c>
       <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>1781977090464</t>
+        </is>
+      </c>
       <c r="O265" t="n">
         <v>0</v>
       </c>
@@ -40764,7 +41880,11 @@
         <v>0</v>
       </c>
       <c r="V265" t="inlineStr"/>
-      <c r="W265" t="inlineStr"/>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58524/c28686cf-2803-46fb-affa-d681dea3fe4e.jpg</t>
+        </is>
+      </c>
       <c r="X265" t="n">
         <v>0</v>
       </c>
@@ -41206,7 +42326,11 @@
         <v>58618</v>
       </c>
       <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>1781976868093</t>
+        </is>
+      </c>
       <c r="O268" t="n">
         <v>0</v>
       </c>
@@ -41227,7 +42351,11 @@
         <v>0</v>
       </c>
       <c r="V268" t="inlineStr"/>
-      <c r="W268" t="inlineStr"/>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58527/6975f6a6-35a2-4166-9b8b-a56fb9160e61.jpg</t>
+        </is>
+      </c>
       <c r="X268" t="n">
         <v>0</v>
       </c>
@@ -41504,7 +42632,11 @@
         <v>58620</v>
       </c>
       <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>1781976771858</t>
+        </is>
+      </c>
       <c r="O270" t="n">
         <v>0</v>
       </c>
@@ -41525,7 +42657,11 @@
         <v>0</v>
       </c>
       <c r="V270" t="inlineStr"/>
-      <c r="W270" t="inlineStr"/>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58529/1b7552fe-ac52-490e-8ff9-6aedcaa006f6.jpg</t>
+        </is>
+      </c>
       <c r="X270" t="n">
         <v>0</v>
       </c>
@@ -41959,7 +43095,11 @@
         <v>58622</v>
       </c>
       <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>1781976819069</t>
+        </is>
+      </c>
       <c r="O273" t="n">
         <v>0</v>
       </c>
@@ -41980,7 +43120,11 @@
         <v>0</v>
       </c>
       <c r="V273" t="inlineStr"/>
-      <c r="W273" t="inlineStr"/>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58531/2b63489a-27ac-45b9-b887-05f18481fd20.jpg</t>
+        </is>
+      </c>
       <c r="X273" t="n">
         <v>0</v>
       </c>
@@ -42108,7 +43252,11 @@
         <v>58623</v>
       </c>
       <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>1781976912418</t>
+        </is>
+      </c>
       <c r="O274" t="n">
         <v>0</v>
       </c>
@@ -42129,7 +43277,11 @@
         <v>0</v>
       </c>
       <c r="V274" t="inlineStr"/>
-      <c r="W274" t="inlineStr"/>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58532/7d0e2cf1-ae1b-40cd-90fd-95253aeaadbc.jpg</t>
+        </is>
+      </c>
       <c r="X274" t="n">
         <v>0</v>
       </c>
@@ -42257,7 +43409,11 @@
         <v>58624</v>
       </c>
       <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>1781976828453</t>
+        </is>
+      </c>
       <c r="O275" t="n">
         <v>0</v>
       </c>
@@ -42278,7 +43434,11 @@
         <v>0</v>
       </c>
       <c r="V275" t="inlineStr"/>
-      <c r="W275" t="inlineStr"/>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58533/0ada95c3-ff79-418e-8d6e-ef5cde95b8b4.jpg</t>
+        </is>
+      </c>
       <c r="X275" t="n">
         <v>0</v>
       </c>
@@ -42406,7 +43566,11 @@
         <v>58625</v>
       </c>
       <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>1781976805084</t>
+        </is>
+      </c>
       <c r="O276" t="n">
         <v>0</v>
       </c>
@@ -42427,7 +43591,11 @@
         <v>0</v>
       </c>
       <c r="V276" t="inlineStr"/>
-      <c r="W276" t="inlineStr"/>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58534/f4311028-02dc-499e-98ba-4fdd3530f2d0.jpg</t>
+        </is>
+      </c>
       <c r="X276" t="n">
         <v>0</v>
       </c>
@@ -42555,7 +43723,11 @@
         <v>58626</v>
       </c>
       <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>1781976916131</t>
+        </is>
+      </c>
       <c r="O277" t="n">
         <v>0</v>
       </c>
@@ -42576,7 +43748,11 @@
         <v>0</v>
       </c>
       <c r="V277" t="inlineStr"/>
-      <c r="W277" t="inlineStr"/>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58535/7953d9d7-6fb0-4b55-bb47-5eb299d37960.jpg</t>
+        </is>
+      </c>
       <c r="X277" t="n">
         <v>0</v>
       </c>
@@ -42704,7 +43880,11 @@
         <v>58627</v>
       </c>
       <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>1781976862022</t>
+        </is>
+      </c>
       <c r="O278" t="n">
         <v>0</v>
       </c>
@@ -42725,7 +43905,11 @@
         <v>0</v>
       </c>
       <c r="V278" t="inlineStr"/>
-      <c r="W278" t="inlineStr"/>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58536/8cc1ddcd-244d-4fcb-be4e-d4ebe803635e.jpg</t>
+        </is>
+      </c>
       <c r="X278" t="n">
         <v>0</v>
       </c>
@@ -42853,7 +44037,11 @@
         <v>58628</v>
       </c>
       <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>1781976894924</t>
+        </is>
+      </c>
       <c r="O279" t="n">
         <v>0</v>
       </c>
@@ -42874,7 +44062,11 @@
         <v>0</v>
       </c>
       <c r="V279" t="inlineStr"/>
-      <c r="W279" t="inlineStr"/>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58537/3baf3b2d-b4ec-4af7-b855-45b0a969d02c.jpg</t>
+        </is>
+      </c>
       <c r="X279" t="n">
         <v>0</v>
       </c>
@@ -43002,7 +44194,11 @@
         <v>58629</v>
       </c>
       <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>1781976879565</t>
+        </is>
+      </c>
       <c r="O280" t="n">
         <v>0</v>
       </c>
@@ -43023,7 +44219,11 @@
         <v>0</v>
       </c>
       <c r="V280" t="inlineStr"/>
-      <c r="W280" t="inlineStr"/>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/58538/c333bf49-1e0e-4f3d-8e1e-5a562377809f.jpg</t>
+        </is>
+      </c>
       <c r="X280" t="n">
         <v>0</v>
       </c>
@@ -43308,7 +44508,11 @@
         <v>148719</v>
       </c>
       <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>1781976942614</t>
+        </is>
+      </c>
       <c r="O282" t="n">
         <v>0</v>
       </c>
@@ -43329,7 +44533,11 @@
         <v>0</v>
       </c>
       <c r="V282" t="inlineStr"/>
-      <c r="W282" t="inlineStr"/>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4356/644007/4894360a-98c0-437b-9734-9e504309ed63.jpg</t>
+        </is>
+      </c>
       <c r="X282" t="n">
         <v>0</v>
       </c>
@@ -43457,7 +44665,11 @@
         <v>58630</v>
       </c>
       <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>1781976903434</t>
+        </is>
+      </c>
       <c r="O283" t="n">
         <v>0</v>
       </c>
@@ -43478,7 +44690,11 @@
         <v>0</v>
       </c>
       <c r="V283" t="inlineStr"/>
-      <c r="W283" t="inlineStr"/>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58539/4692fc69-e8cf-44ac-8ac2-51a34a0f4bf1.jpg</t>
+        </is>
+      </c>
       <c r="X283" t="n">
         <v>0</v>
       </c>
@@ -43606,7 +44822,11 @@
         <v>58631</v>
       </c>
       <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>1781976911840</t>
+        </is>
+      </c>
       <c r="O284" t="n">
         <v>0</v>
       </c>
@@ -43627,7 +44847,11 @@
         <v>0</v>
       </c>
       <c r="V284" t="inlineStr"/>
-      <c r="W284" t="inlineStr"/>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58540/950eeb2f-a492-4bcb-8d72-b35a1b937d0f.jpg</t>
+        </is>
+      </c>
       <c r="X284" t="n">
         <v>0</v>
       </c>
@@ -43755,7 +44979,11 @@
         <v>58632</v>
       </c>
       <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>1781976890871</t>
+        </is>
+      </c>
       <c r="O285" t="n">
         <v>0</v>
       </c>
@@ -43776,7 +45004,11 @@
         <v>0</v>
       </c>
       <c r="V285" t="inlineStr"/>
-      <c r="W285" t="inlineStr"/>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58541/ee33f0f0-b64b-48af-b16e-2ecf6e1b6f57.jpg</t>
+        </is>
+      </c>
       <c r="X285" t="n">
         <v>0</v>
       </c>
@@ -43904,7 +45136,11 @@
         <v>58633</v>
       </c>
       <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>1781976882069</t>
+        </is>
+      </c>
       <c r="O286" t="n">
         <v>0</v>
       </c>
@@ -43925,7 +45161,11 @@
         <v>0</v>
       </c>
       <c r="V286" t="inlineStr"/>
-      <c r="W286" t="inlineStr"/>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58542/4fa23406-6191-4341-a43f-6e80ddd1dbbb.jpg</t>
+        </is>
+      </c>
       <c r="X286" t="n">
         <v>0</v>
       </c>
@@ -44210,7 +45450,11 @@
         <v>58635</v>
       </c>
       <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>1781976907815</t>
+        </is>
+      </c>
       <c r="O288" t="n">
         <v>0</v>
       </c>
@@ -44231,7 +45475,11 @@
         <v>0</v>
       </c>
       <c r="V288" t="inlineStr"/>
-      <c r="W288" t="inlineStr"/>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58544/a0738b3f-caf1-441d-895b-8e52d7a92d0b.jpg</t>
+        </is>
+      </c>
       <c r="X288" t="n">
         <v>0</v>
       </c>
@@ -44359,7 +45607,11 @@
         <v>58636</v>
       </c>
       <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>1781976883903</t>
+        </is>
+      </c>
       <c r="O289" t="n">
         <v>0</v>
       </c>
@@ -44380,7 +45632,11 @@
         <v>0</v>
       </c>
       <c r="V289" t="inlineStr"/>
-      <c r="W289" t="inlineStr"/>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58545/899082e2-42d6-4aea-8278-1f8d7d386afc.jpg</t>
+        </is>
+      </c>
       <c r="X289" t="n">
         <v>0</v>
       </c>
@@ -44508,7 +45764,11 @@
         <v>58637</v>
       </c>
       <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>1781976772983</t>
+        </is>
+      </c>
       <c r="O290" t="n">
         <v>0</v>
       </c>
@@ -44529,7 +45789,11 @@
         <v>0</v>
       </c>
       <c r="V290" t="inlineStr"/>
-      <c r="W290" t="inlineStr"/>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58546/ff9d06aa-70a0-41ad-9019-82b25563870b.jpg</t>
+        </is>
+      </c>
       <c r="X290" t="n">
         <v>0</v>
       </c>
@@ -44971,7 +46235,11 @@
         <v>58640</v>
       </c>
       <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>1781976807463</t>
+        </is>
+      </c>
       <c r="O293" t="n">
         <v>0</v>
       </c>
@@ -44992,7 +46260,11 @@
         <v>0</v>
       </c>
       <c r="V293" t="inlineStr"/>
-      <c r="W293" t="inlineStr"/>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58549/1e496419-be39-4688-9322-34b0ba8c84de.jpg</t>
+        </is>
+      </c>
       <c r="X293" t="n">
         <v>0</v>
       </c>
@@ -45120,7 +46392,11 @@
         <v>58641</v>
       </c>
       <c r="M294" t="inlineStr"/>
-      <c r="N294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>1781976896313</t>
+        </is>
+      </c>
       <c r="O294" t="n">
         <v>0</v>
       </c>
@@ -45141,7 +46417,11 @@
         <v>0</v>
       </c>
       <c r="V294" t="inlineStr"/>
-      <c r="W294" t="inlineStr"/>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58550/1bd4c4ba-81c7-4dd9-9522-7c752fa50e97.jpg</t>
+        </is>
+      </c>
       <c r="X294" t="n">
         <v>0</v>
       </c>
@@ -45269,7 +46549,11 @@
         <v>58642</v>
       </c>
       <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>1781976770072</t>
+        </is>
+      </c>
       <c r="O295" t="n">
         <v>0</v>
       </c>
@@ -45290,7 +46574,11 @@
         <v>0</v>
       </c>
       <c r="V295" t="inlineStr"/>
-      <c r="W295" t="inlineStr"/>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/58551/0d7a56c2-83c8-44b8-a4e2-506e8e7ba12b.jpg</t>
+        </is>
+      </c>
       <c r="X295" t="n">
         <v>0</v>
       </c>
@@ -45418,7 +46706,11 @@
         <v>148720</v>
       </c>
       <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>1781976822913</t>
+        </is>
+      </c>
       <c r="O296" t="n">
         <v>0</v>
       </c>
@@ -45439,7 +46731,11 @@
         <v>0</v>
       </c>
       <c r="V296" t="inlineStr"/>
-      <c r="W296" t="inlineStr"/>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4357/644008/6bd7103a-c088-4b5b-b16d-33a3bd2452fd.jpg</t>
+        </is>
+      </c>
       <c r="X296" t="n">
         <v>0</v>
       </c>
@@ -46014,7 +47310,11 @@
         <v>58646</v>
       </c>
       <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>1781977040596</t>
+        </is>
+      </c>
       <c r="O300" t="n">
         <v>0</v>
       </c>
@@ -46035,7 +47335,11 @@
         <v>0</v>
       </c>
       <c r="V300" t="inlineStr"/>
-      <c r="W300" t="inlineStr"/>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/58555/689448bb-41ad-4ab2-a4df-5f01291bace1.jpg</t>
+        </is>
+      </c>
       <c r="X300" t="n">
         <v>0</v>
       </c>
@@ -46163,7 +47467,11 @@
         <v>148721</v>
       </c>
       <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>1781976820241</t>
+        </is>
+      </c>
       <c r="O301" t="n">
         <v>0</v>
       </c>
@@ -46184,7 +47492,11 @@
         <v>0</v>
       </c>
       <c r="V301" t="inlineStr"/>
-      <c r="W301" t="inlineStr"/>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/644009/150b6baf-fad0-4bb6-bcee-4fda2cbc7e8b.jpg</t>
+        </is>
+      </c>
       <c r="X301" t="n">
         <v>0</v>
       </c>
@@ -46312,7 +47624,11 @@
         <v>148722</v>
       </c>
       <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>1781976798897</t>
+        </is>
+      </c>
       <c r="O302" t="n">
         <v>0</v>
       </c>
@@ -46333,7 +47649,11 @@
         <v>0</v>
       </c>
       <c r="V302" t="inlineStr"/>
-      <c r="W302" t="inlineStr"/>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/644010/dd5e3e89-c8a2-4df1-bf11-6c7f2e21a44a.jpg</t>
+        </is>
+      </c>
       <c r="X302" t="n">
         <v>0</v>
       </c>
@@ -46610,7 +47930,11 @@
         <v>148724</v>
       </c>
       <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>1781976756081</t>
+        </is>
+      </c>
       <c r="O304" t="n">
         <v>0</v>
       </c>
@@ -46631,7 +47955,11 @@
         <v>0</v>
       </c>
       <c r="V304" t="inlineStr"/>
-      <c r="W304" t="inlineStr"/>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/644012/4b724a69-11d1-410c-a623-00f4aaf77ffa.jpg</t>
+        </is>
+      </c>
       <c r="X304" t="n">
         <v>0</v>
       </c>
@@ -46759,7 +48087,11 @@
         <v>64662</v>
       </c>
       <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>1781976927868</t>
+        </is>
+      </c>
       <c r="O305" t="n">
         <v>0</v>
       </c>
@@ -46780,7 +48112,11 @@
         <v>0</v>
       </c>
       <c r="V305" t="inlineStr"/>
-      <c r="W305" t="inlineStr"/>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4716/64572/df982c0f-8d1f-44e0-90dc-0cde5c534a5a.jpg</t>
+        </is>
+      </c>
       <c r="X305" t="n">
         <v>0</v>
       </c>
@@ -47228,7 +48564,11 @@
         <v>151198</v>
       </c>
       <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>1781976752039</t>
+        </is>
+      </c>
       <c r="O308" t="n">
         <v>0</v>
       </c>
@@ -47249,7 +48589,11 @@
         <v>0</v>
       </c>
       <c r="V308" t="inlineStr"/>
-      <c r="W308" t="inlineStr"/>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4716/646485/188a0a4e-1713-4f14-93ed-86e97b736eb7.jpg</t>
+        </is>
+      </c>
       <c r="X308" t="n">
         <v>0</v>
       </c>
@@ -47533,29 +48877,43 @@
       <c r="L310" t="n">
         <v>64665</v>
       </c>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
+      <c r="M310" t="n">
+        <v>1781976873866</v>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>1781976873259</t>
+        </is>
+      </c>
       <c r="O310" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="P310" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="Q310" t="n">
         <v>0</v>
       </c>
-      <c r="R310" t="inlineStr"/>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>6a36cf29370583337b6e71f9</t>
+        </is>
+      </c>
       <c r="S310" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="T310" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="U310" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="V310" t="inlineStr"/>
-      <c r="W310" t="inlineStr"/>
+      <c r="W310" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/64575/ce78a52b-f8fe-4d96-b6cb-402b68357c14.jpg</t>
+        </is>
+      </c>
       <c r="X310" t="n">
         <v>0</v>
       </c>
@@ -47572,13 +48930,13 @@
         <v>0</v>
       </c>
       <c r="AC310" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="AD310" t="n">
         <v>0</v>
       </c>
       <c r="AE310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF310" t="n">
         <v>0</v>
@@ -47590,7 +48948,7 @@
         <v>0</v>
       </c>
       <c r="AI310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ310" t="n">
         <v>0</v>
@@ -47683,7 +49041,11 @@
         <v>64666</v>
       </c>
       <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>1781976904722</t>
+        </is>
+      </c>
       <c r="O311" t="n">
         <v>0</v>
       </c>
@@ -47704,7 +49066,11 @@
         <v>0</v>
       </c>
       <c r="V311" t="inlineStr"/>
-      <c r="W311" t="inlineStr"/>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/64576/9c2626e6-fb33-4296-be52-b26411203c7c.jpg</t>
+        </is>
+      </c>
       <c r="X311" t="n">
         <v>0</v>
       </c>
@@ -47981,7 +49347,11 @@
         <v>64668</v>
       </c>
       <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>1781976914707</t>
+        </is>
+      </c>
       <c r="O313" t="n">
         <v>0</v>
       </c>
@@ -48002,7 +49372,11 @@
         <v>0</v>
       </c>
       <c r="V313" t="inlineStr"/>
-      <c r="W313" t="inlineStr"/>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/64578/23379525-7919-4c2e-814c-66efc89f25b0.jpg</t>
+        </is>
+      </c>
       <c r="X313" t="n">
         <v>0</v>
       </c>
@@ -48130,7 +49504,11 @@
         <v>64669</v>
       </c>
       <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>1781976761856</t>
+        </is>
+      </c>
       <c r="O314" t="n">
         <v>0</v>
       </c>
@@ -48151,7 +49529,11 @@
         <v>0</v>
       </c>
       <c r="V314" t="inlineStr"/>
-      <c r="W314" t="inlineStr"/>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/64579/ff3e4fa4-0427-4f61-b376-09371d3ff9c0.jpg</t>
+        </is>
+      </c>
       <c r="X314" t="n">
         <v>0</v>
       </c>
@@ -48279,7 +49661,11 @@
         <v>151200</v>
       </c>
       <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>1781976944329</t>
+        </is>
+      </c>
       <c r="O315" t="n">
         <v>0</v>
       </c>
@@ -48300,7 +49686,11 @@
         <v>0</v>
       </c>
       <c r="V315" t="inlineStr"/>
-      <c r="W315" t="inlineStr"/>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/646487/f0e40b9b-d47a-4a44-a868-1d72f29643a7.jpg</t>
+        </is>
+      </c>
       <c r="X315" t="n">
         <v>0</v>
       </c>
@@ -48428,7 +49818,11 @@
         <v>151201</v>
       </c>
       <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>1781976791061</t>
+        </is>
+      </c>
       <c r="O316" t="n">
         <v>0</v>
       </c>
@@ -48449,7 +49843,11 @@
         <v>0</v>
       </c>
       <c r="V316" t="inlineStr"/>
-      <c r="W316" t="inlineStr"/>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/646488/1ebec707-761a-43fb-88eb-dce2b25338d6.jpg</t>
+        </is>
+      </c>
       <c r="X316" t="n">
         <v>0</v>
       </c>
@@ -49833,7 +51231,11 @@
         <v>151202</v>
       </c>
       <c r="M325" t="inlineStr"/>
-      <c r="N325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>1781976889275</t>
+        </is>
+      </c>
       <c r="O325" t="n">
         <v>0</v>
       </c>
@@ -49854,7 +51256,11 @@
         <v>0</v>
       </c>
       <c r="V325" t="inlineStr"/>
-      <c r="W325" t="inlineStr"/>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4718/646489/0d7d24fa-9f09-498f-8a13-40ecb611345e.jpg</t>
+        </is>
+      </c>
       <c r="X325" t="n">
         <v>0</v>
       </c>
@@ -50139,7 +51545,11 @@
         <v>64679</v>
       </c>
       <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>1781976810316</t>
+        </is>
+      </c>
       <c r="O327" t="n">
         <v>0</v>
       </c>
@@ -50160,7 +51570,11 @@
         <v>0</v>
       </c>
       <c r="V327" t="inlineStr"/>
-      <c r="W327" t="inlineStr"/>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64589/9e87ba08-2a50-4d07-8440-8639e9f4334a.jpg</t>
+        </is>
+      </c>
       <c r="X327" t="n">
         <v>0</v>
       </c>
@@ -50288,7 +51702,11 @@
         <v>64680</v>
       </c>
       <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>1781976780344</t>
+        </is>
+      </c>
       <c r="O328" t="n">
         <v>0</v>
       </c>
@@ -50309,7 +51727,11 @@
         <v>0</v>
       </c>
       <c r="V328" t="inlineStr"/>
-      <c r="W328" t="inlineStr"/>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64590/8585affc-cf2b-451c-a3f0-52bebfed0fd9.jpg</t>
+        </is>
+      </c>
       <c r="X328" t="n">
         <v>0</v>
       </c>
@@ -50751,7 +52173,11 @@
         <v>64683</v>
       </c>
       <c r="M331" t="inlineStr"/>
-      <c r="N331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>1781976944898</t>
+        </is>
+      </c>
       <c r="O331" t="n">
         <v>0</v>
       </c>
@@ -50772,7 +52198,11 @@
         <v>0</v>
       </c>
       <c r="V331" t="inlineStr"/>
-      <c r="W331" t="inlineStr"/>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4719/64593/59339de7-18ef-48ef-92c1-341cfdf0d693.jpg</t>
+        </is>
+      </c>
       <c r="X331" t="n">
         <v>0</v>
       </c>
@@ -51371,7 +52801,11 @@
         <v>64686</v>
       </c>
       <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>1781976786403</t>
+        </is>
+      </c>
       <c r="O335" t="n">
         <v>0</v>
       </c>
@@ -51392,7 +52826,11 @@
         <v>0</v>
       </c>
       <c r="V335" t="inlineStr"/>
-      <c r="W335" t="inlineStr"/>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64596/cb7221e8-031b-4719-bd30-9f74e4b81fef.jpg</t>
+        </is>
+      </c>
       <c r="X335" t="n">
         <v>0</v>
       </c>
@@ -51677,7 +53115,11 @@
         <v>64688</v>
       </c>
       <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>1781976915601</t>
+        </is>
+      </c>
       <c r="O337" t="n">
         <v>0</v>
       </c>
@@ -51698,7 +53140,11 @@
         <v>0</v>
       </c>
       <c r="V337" t="inlineStr"/>
-      <c r="W337" t="inlineStr"/>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64598/e1857c29-0c7e-4803-88fc-b4b6359e76b6.jpg</t>
+        </is>
+      </c>
       <c r="X337" t="n">
         <v>0</v>
       </c>
@@ -51826,7 +53272,11 @@
         <v>64689</v>
       </c>
       <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>1781976892870</t>
+        </is>
+      </c>
       <c r="O338" t="n">
         <v>0</v>
       </c>
@@ -51847,7 +53297,11 @@
         <v>0</v>
       </c>
       <c r="V338" t="inlineStr"/>
-      <c r="W338" t="inlineStr"/>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/64599/5ae964ff-7351-4c3f-bd76-7da892873bf5.jpg</t>
+        </is>
+      </c>
       <c r="X338" t="n">
         <v>0</v>
       </c>
@@ -52289,7 +53743,11 @@
         <v>151206</v>
       </c>
       <c r="M341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>1781976943782</t>
+        </is>
+      </c>
       <c r="O341" t="n">
         <v>0</v>
       </c>
@@ -52310,7 +53768,11 @@
         <v>0</v>
       </c>
       <c r="V341" t="inlineStr"/>
-      <c r="W341" t="inlineStr"/>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4720/646493/7c7ce129-a816-48fd-b64b-8c8670ce2fdb.jpg</t>
+        </is>
+      </c>
       <c r="X341" t="n">
         <v>0</v>
       </c>
@@ -56054,29 +57516,43 @@
       <c r="L365" t="n">
         <v>64698</v>
       </c>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
+      <c r="M365" t="n">
+        <v>1781976813192</v>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>1781976812454</t>
+        </is>
+      </c>
       <c r="O365" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="P365" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="Q365" t="n">
-        <v>0</v>
-      </c>
-      <c r="R365" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>6a36ceec370583337b6e6ff5</t>
+        </is>
+      </c>
       <c r="S365" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="T365" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="U365" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="V365" t="inlineStr"/>
-      <c r="W365" t="inlineStr"/>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64608/44430731-a4e5-42e1-8f84-2ced962019bd.jpg</t>
+        </is>
+      </c>
       <c r="X365" t="n">
         <v>0</v>
       </c>
@@ -56093,13 +57569,13 @@
         <v>0</v>
       </c>
       <c r="AC365" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AD365" t="n">
         <v>0</v>
       </c>
       <c r="AE365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF365" t="n">
         <v>0</v>
@@ -56518,7 +57994,11 @@
         <v>64701</v>
       </c>
       <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>1781976960124</t>
+        </is>
+      </c>
       <c r="O368" t="n">
         <v>0</v>
       </c>
@@ -56539,7 +58019,11 @@
         <v>0</v>
       </c>
       <c r="V368" t="inlineStr"/>
-      <c r="W368" t="inlineStr"/>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64611/9942f58a-bf41-4ed6-8c3a-bc940b3a00e3.jpg</t>
+        </is>
+      </c>
       <c r="X368" t="n">
         <v>0</v>
       </c>
@@ -57929,7 +59413,11 @@
         <v>64717</v>
       </c>
       <c r="M377" t="inlineStr"/>
-      <c r="N377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>1781976885564</t>
+        </is>
+      </c>
       <c r="O377" t="n">
         <v>0</v>
       </c>
@@ -57950,7 +59438,11 @@
         <v>0</v>
       </c>
       <c r="V377" t="inlineStr"/>
-      <c r="W377" t="inlineStr"/>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
+        </is>
+      </c>
       <c r="X377" t="n">
         <v>0</v>
       </c>
@@ -58078,7 +59570,11 @@
         <v>64718</v>
       </c>
       <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>1781976801113</t>
+        </is>
+      </c>
       <c r="O378" t="n">
         <v>0</v>
       </c>
@@ -58099,7 +59595,11 @@
         <v>0</v>
       </c>
       <c r="V378" t="inlineStr"/>
-      <c r="W378" t="inlineStr"/>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
+        </is>
+      </c>
       <c r="X378" t="n">
         <v>0</v>
       </c>
@@ -58227,7 +59727,11 @@
         <v>64719</v>
       </c>
       <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>1781976797855</t>
+        </is>
+      </c>
       <c r="O379" t="n">
         <v>0</v>
       </c>
@@ -58248,7 +59752,11 @@
         <v>0</v>
       </c>
       <c r="V379" t="inlineStr"/>
-      <c r="W379" t="inlineStr"/>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
+        </is>
+      </c>
       <c r="X379" t="n">
         <v>0</v>
       </c>
@@ -58690,7 +60198,11 @@
         <v>151215</v>
       </c>
       <c r="M382" t="inlineStr"/>
-      <c r="N382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>1781976919845</t>
+        </is>
+      </c>
       <c r="O382" t="n">
         <v>0</v>
       </c>
@@ -58711,7 +60223,11 @@
         <v>0</v>
       </c>
       <c r="V382" t="inlineStr"/>
-      <c r="W382" t="inlineStr"/>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
+        </is>
+      </c>
       <c r="X382" t="n">
         <v>0</v>
       </c>
@@ -58996,7 +60512,11 @@
         <v>151217</v>
       </c>
       <c r="M384" t="inlineStr"/>
-      <c r="N384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>1781977138945</t>
+        </is>
+      </c>
       <c r="O384" t="n">
         <v>0</v>
       </c>
@@ -59017,7 +60537,11 @@
         <v>0</v>
       </c>
       <c r="V384" t="inlineStr"/>
-      <c r="W384" t="inlineStr"/>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
+        </is>
+      </c>
       <c r="X384" t="n">
         <v>0</v>
       </c>
@@ -60715,7 +62239,11 @@
         <v>64730</v>
       </c>
       <c r="M395" t="inlineStr"/>
-      <c r="N395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>1781977074928</t>
+        </is>
+      </c>
       <c r="O395" t="n">
         <v>0</v>
       </c>
@@ -60736,7 +62264,11 @@
         <v>0</v>
       </c>
       <c r="V395" t="inlineStr"/>
-      <c r="W395" t="inlineStr"/>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
+        </is>
+      </c>
       <c r="X395" t="n">
         <v>0</v>
       </c>
@@ -60864,7 +62396,11 @@
         <v>64731</v>
       </c>
       <c r="M396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>1781977113305</t>
+        </is>
+      </c>
       <c r="O396" t="n">
         <v>0</v>
       </c>
@@ -60885,7 +62421,11 @@
         <v>0</v>
       </c>
       <c r="V396" t="inlineStr"/>
-      <c r="W396" t="inlineStr"/>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
+        </is>
+      </c>
       <c r="X396" t="n">
         <v>0</v>
       </c>
@@ -61013,7 +62553,11 @@
         <v>64732</v>
       </c>
       <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>1781977075062</t>
+        </is>
+      </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
@@ -61034,7 +62578,11 @@
         <v>0</v>
       </c>
       <c r="V397" t="inlineStr"/>
-      <c r="W397" t="inlineStr"/>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
+        </is>
+      </c>
       <c r="X397" t="n">
         <v>0</v>
       </c>
@@ -61774,7 +63322,11 @@
         <v>64737</v>
       </c>
       <c r="M402" t="inlineStr"/>
-      <c r="N402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>1781976878903</t>
+        </is>
+      </c>
       <c r="O402" t="n">
         <v>0</v>
       </c>
@@ -61795,7 +63347,11 @@
         <v>0</v>
       </c>
       <c r="V402" t="inlineStr"/>
-      <c r="W402" t="inlineStr"/>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
+        </is>
+      </c>
       <c r="X402" t="n">
         <v>0</v>
       </c>
@@ -61923,7 +63479,11 @@
         <v>64738</v>
       </c>
       <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>1781976780359</t>
+        </is>
+      </c>
       <c r="O403" t="n">
         <v>0</v>
       </c>
@@ -61944,7 +63504,11 @@
         <v>0</v>
       </c>
       <c r="V403" t="inlineStr"/>
-      <c r="W403" t="inlineStr"/>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
+        </is>
+      </c>
       <c r="X403" t="n">
         <v>0</v>
       </c>
@@ -62072,7 +63636,11 @@
         <v>151220</v>
       </c>
       <c r="M404" t="inlineStr"/>
-      <c r="N404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>1781977094685</t>
+        </is>
+      </c>
       <c r="O404" t="n">
         <v>0</v>
       </c>
@@ -62093,7 +63661,11 @@
         <v>0</v>
       </c>
       <c r="V404" t="inlineStr"/>
-      <c r="W404" t="inlineStr"/>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
+        </is>
+      </c>
       <c r="X404" t="n">
         <v>0</v>
       </c>
@@ -62221,7 +63793,11 @@
         <v>151221</v>
       </c>
       <c r="M405" t="inlineStr"/>
-      <c r="N405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>1781976782683</t>
+        </is>
+      </c>
       <c r="O405" t="n">
         <v>0</v>
       </c>
@@ -62242,7 +63818,11 @@
         <v>0</v>
       </c>
       <c r="V405" t="inlineStr"/>
-      <c r="W405" t="inlineStr"/>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
+        </is>
+      </c>
       <c r="X405" t="n">
         <v>0</v>
       </c>
@@ -62370,7 +63950,11 @@
         <v>64739</v>
       </c>
       <c r="M406" t="inlineStr"/>
-      <c r="N406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>1781976872268</t>
+        </is>
+      </c>
       <c r="O406" t="n">
         <v>0</v>
       </c>
@@ -62391,7 +63975,11 @@
         <v>0</v>
       </c>
       <c r="V406" t="inlineStr"/>
-      <c r="W406" t="inlineStr"/>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
+        </is>
+      </c>
       <c r="X406" t="n">
         <v>0</v>
       </c>
@@ -62519,7 +64107,11 @@
         <v>64740</v>
       </c>
       <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>1781976901500</t>
+        </is>
+      </c>
       <c r="O407" t="n">
         <v>0</v>
       </c>
@@ -62540,7 +64132,11 @@
         <v>0</v>
       </c>
       <c r="V407" t="inlineStr"/>
-      <c r="W407" t="inlineStr"/>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
+        </is>
+      </c>
       <c r="X407" t="n">
         <v>0</v>
       </c>
@@ -62982,7 +64578,11 @@
         <v>64743</v>
       </c>
       <c r="M410" t="inlineStr"/>
-      <c r="N410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>1781976861221</t>
+        </is>
+      </c>
       <c r="O410" t="n">
         <v>0</v>
       </c>
@@ -63003,7 +64603,11 @@
         <v>0</v>
       </c>
       <c r="V410" t="inlineStr"/>
-      <c r="W410" t="inlineStr"/>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
+        </is>
+      </c>
       <c r="X410" t="n">
         <v>0</v>
       </c>
@@ -63131,7 +64735,11 @@
         <v>64744</v>
       </c>
       <c r="M411" t="inlineStr"/>
-      <c r="N411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>1781976900341</t>
+        </is>
+      </c>
       <c r="O411" t="n">
         <v>0</v>
       </c>
@@ -63152,7 +64760,11 @@
         <v>0</v>
       </c>
       <c r="V411" t="inlineStr"/>
-      <c r="W411" t="inlineStr"/>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
+        </is>
+      </c>
       <c r="X411" t="n">
         <v>0</v>
       </c>
@@ -63437,7 +65049,11 @@
         <v>64746</v>
       </c>
       <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>1781976889527</t>
+        </is>
+      </c>
       <c r="O413" t="n">
         <v>0</v>
       </c>
@@ -63458,7 +65074,11 @@
         <v>0</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" t="inlineStr"/>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
+        </is>
+      </c>
       <c r="X413" t="n">
         <v>0</v>
       </c>
@@ -63586,7 +65206,11 @@
         <v>64747</v>
       </c>
       <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>1781976782857</t>
+        </is>
+      </c>
       <c r="O414" t="n">
         <v>0</v>
       </c>
@@ -63607,7 +65231,11 @@
         <v>0</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" t="inlineStr"/>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
+        </is>
+      </c>
       <c r="X414" t="n">
         <v>0</v>
       </c>
@@ -63892,7 +65520,11 @@
         <v>64749</v>
       </c>
       <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>1781976813571</t>
+        </is>
+      </c>
       <c r="O416" t="n">
         <v>0</v>
       </c>
@@ -63913,7 +65545,11 @@
         <v>0</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" t="inlineStr"/>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
+        </is>
+      </c>
       <c r="X416" t="n">
         <v>0</v>
       </c>
@@ -64041,7 +65677,11 @@
         <v>64750</v>
       </c>
       <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>1781976798491</t>
+        </is>
+      </c>
       <c r="O417" t="n">
         <v>0</v>
       </c>
@@ -64062,7 +65702,11 @@
         <v>0</v>
       </c>
       <c r="V417" t="inlineStr"/>
-      <c r="W417" t="inlineStr"/>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
+        </is>
+      </c>
       <c r="X417" t="n">
         <v>0</v>
       </c>
@@ -64339,7 +65983,11 @@
         <v>64752</v>
       </c>
       <c r="M419" t="inlineStr"/>
-      <c r="N419" t="inlineStr"/>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>1781976792595</t>
+        </is>
+      </c>
       <c r="O419" t="n">
         <v>0</v>
       </c>
@@ -64360,7 +66008,11 @@
         <v>0</v>
       </c>
       <c r="V419" t="inlineStr"/>
-      <c r="W419" t="inlineStr"/>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
+        </is>
+      </c>
       <c r="X419" t="n">
         <v>0</v>
       </c>
@@ -64488,7 +66140,11 @@
         <v>151222</v>
       </c>
       <c r="M420" t="inlineStr"/>
-      <c r="N420" t="inlineStr"/>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>1781976850366</t>
+        </is>
+      </c>
       <c r="O420" t="n">
         <v>0</v>
       </c>
@@ -64509,7 +66165,11 @@
         <v>0</v>
       </c>
       <c r="V420" t="inlineStr"/>
-      <c r="W420" t="inlineStr"/>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
+        </is>
+      </c>
       <c r="X420" t="n">
         <v>0</v>
       </c>
@@ -64637,7 +66297,11 @@
         <v>64753</v>
       </c>
       <c r="M421" t="inlineStr"/>
-      <c r="N421" t="inlineStr"/>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>1781976869394</t>
+        </is>
+      </c>
       <c r="O421" t="n">
         <v>0</v>
       </c>
@@ -64658,7 +66322,11 @@
         <v>0</v>
       </c>
       <c r="V421" t="inlineStr"/>
-      <c r="W421" t="inlineStr"/>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
+        </is>
+      </c>
       <c r="X421" t="n">
         <v>0</v>
       </c>
@@ -64943,7 +66611,11 @@
         <v>64755</v>
       </c>
       <c r="M423" t="inlineStr"/>
-      <c r="N423" t="inlineStr"/>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>1781976938520</t>
+        </is>
+      </c>
       <c r="O423" t="n">
         <v>0</v>
       </c>
@@ -64964,7 +66636,11 @@
         <v>0</v>
       </c>
       <c r="V423" t="inlineStr"/>
-      <c r="W423" t="inlineStr"/>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
+        </is>
+      </c>
       <c r="X423" t="n">
         <v>0</v>
       </c>
@@ -65092,7 +66768,11 @@
         <v>64756</v>
       </c>
       <c r="M424" t="inlineStr"/>
-      <c r="N424" t="inlineStr"/>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>1781977012376</t>
+        </is>
+      </c>
       <c r="O424" t="n">
         <v>0</v>
       </c>
@@ -65113,7 +66793,11 @@
         <v>0</v>
       </c>
       <c r="V424" t="inlineStr"/>
-      <c r="W424" t="inlineStr"/>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
+        </is>
+      </c>
       <c r="X424" t="n">
         <v>0</v>
       </c>
@@ -65241,7 +66925,11 @@
         <v>64757</v>
       </c>
       <c r="M425" t="inlineStr"/>
-      <c r="N425" t="inlineStr"/>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>1781977113973</t>
+        </is>
+      </c>
       <c r="O425" t="n">
         <v>0</v>
       </c>
@@ -65262,7 +66950,11 @@
         <v>0</v>
       </c>
       <c r="V425" t="inlineStr"/>
-      <c r="W425" t="inlineStr"/>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
+        </is>
+      </c>
       <c r="X425" t="n">
         <v>0</v>
       </c>
@@ -65390,7 +67082,11 @@
         <v>64758</v>
       </c>
       <c r="M426" t="inlineStr"/>
-      <c r="N426" t="inlineStr"/>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>1781976876830</t>
+        </is>
+      </c>
       <c r="O426" t="n">
         <v>0</v>
       </c>
@@ -65411,7 +67107,11 @@
         <v>0</v>
       </c>
       <c r="V426" t="inlineStr"/>
-      <c r="W426" t="inlineStr"/>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
+        </is>
+      </c>
       <c r="X426" t="n">
         <v>0</v>
       </c>
@@ -65539,7 +67239,11 @@
         <v>151223</v>
       </c>
       <c r="M427" t="inlineStr"/>
-      <c r="N427" t="inlineStr"/>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>1781976882480</t>
+        </is>
+      </c>
       <c r="O427" t="n">
         <v>0</v>
       </c>
@@ -65560,7 +67264,11 @@
         <v>0</v>
       </c>
       <c r="V427" t="inlineStr"/>
-      <c r="W427" t="inlineStr"/>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
+        </is>
+      </c>
       <c r="X427" t="n">
         <v>0</v>
       </c>
@@ -67578,7 +69286,11 @@
         <v>64766</v>
       </c>
       <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>1781976840577</t>
+        </is>
+      </c>
       <c r="O440" t="n">
         <v>0</v>
       </c>
@@ -67599,7 +69311,11 @@
         <v>0</v>
       </c>
       <c r="V440" t="inlineStr"/>
-      <c r="W440" t="inlineStr"/>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
+        </is>
+      </c>
       <c r="X440" t="n">
         <v>0</v>
       </c>
@@ -69063,22 +70779,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>477</v>
+        <v>1311</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>231</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>89</v>
+        <v>231</v>
       </c>
       <c r="H3" t="n">
-        <v>477</v>
+        <v>1311</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>230</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -69096,7 +70812,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -69583,22 +71299,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -69616,7 +71332,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -69687,22 +71403,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -69720,13 +71436,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -69738,7 +71454,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -69791,22 +71507,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -69824,7 +71540,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -70623,22 +72339,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -70656,13 +72372,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -70674,7 +72390,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -71247,22 +72963,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -71280,13 +72996,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -72245,22 +73961,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>477</v>
+        <v>3183</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>390</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>390</v>
       </c>
       <c r="G2" t="n">
-        <v>477</v>
+        <v>3183</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>388</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -72278,13 +73994,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>87</v>
+        <v>384</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -72296,7 +74012,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -72344,22 +74060,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1735</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>237</v>
+        <v>516</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>235</v>
+        <v>513</v>
       </c>
       <c r="G3" t="n">
-        <v>1693</v>
+        <v>3089</v>
       </c>
       <c r="H3" t="n">
-        <v>232</v>
+        <v>508</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -72377,13 +74093,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>230</v>
+        <v>503</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -72395,7 +74111,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -72604,22 +74320,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2212</v>
+        <v>6314</v>
       </c>
       <c r="C2" t="n">
-        <v>326</v>
+        <v>906</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>324</v>
+        <v>903</v>
       </c>
       <c r="F2" t="n">
-        <v>2170</v>
+        <v>6272</v>
       </c>
       <c r="G2" t="n">
-        <v>320</v>
+        <v>896</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -72637,13 +74353,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>317</v>
+        <v>887</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -72655,7 +74371,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -70497,162 +70485,162 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
@@ -73793,157 +73781,157 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
@@ -74162,152 +74150,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,227 +432,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -706,7 +718,11 @@
         <v>58436</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1781981829520</t>
+        </is>
+      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
@@ -727,7 +743,11 @@
         <v>0</v>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58345/ccae3538-0356-4def-bfac-3d8f4675f21a.jpg</t>
+        </is>
+      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -855,7 +875,11 @@
         <v>58437</v>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1781981644306</t>
+        </is>
+      </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
@@ -876,7 +900,11 @@
         <v>0</v>
       </c>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58346/11831b37-ab96-4043-87ba-176bc2b2c5b9.jpg</t>
+        </is>
+      </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
@@ -1789,7 +1817,11 @@
         <v>58443</v>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1781982363781</t>
+        </is>
+      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1810,7 +1842,11 @@
         <v>0</v>
       </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58352/36b573c9-a91b-4e8a-b92e-3cf1f8ab63fb.jpg</t>
+        </is>
+      </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
@@ -1938,7 +1974,11 @@
         <v>58444</v>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1781983756086</t>
+        </is>
+      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1959,7 +1999,11 @@
         <v>0</v>
       </c>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58353/454f77e5-8f35-4017-b9c0-9c3e4a43c7a0.jpg</t>
+        </is>
+      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -3335,7 +3379,11 @@
         <v>58453</v>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1781981828728</t>
+        </is>
+      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -3356,7 +3404,11 @@
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58362/4c9d3e63-95fe-4496-a881-82ca209ffba5.jpg</t>
+        </is>
+      </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -3484,7 +3536,11 @@
         <v>58454</v>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1781981469293</t>
+        </is>
+      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -3505,7 +3561,11 @@
         <v>0</v>
       </c>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58363/aaa83413-d111-4fa5-9620-e70bc4a72dc6.jpg</t>
+        </is>
+      </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
@@ -19792,7 +19852,11 @@
         <v>58526</v>
       </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>1781981105891</t>
+        </is>
+      </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
@@ -19813,7 +19877,11 @@
         <v>0</v>
       </c>
       <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58435/98b69f77-a004-43ca-9707-405d64d038ad.jpg</t>
+        </is>
+      </c>
       <c r="X124" t="n">
         <v>0</v>
       </c>
@@ -23370,29 +23438,43 @@
       <c r="L147" t="n">
         <v>58544</v>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>1781981468267</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>1781981467671</t>
+        </is>
+      </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
-      <c r="R147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>6a36e11bc89f29392f333c6e</t>
+        </is>
+      </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="U147" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58453/5f092f32-c2c4-4146-a609-a53268787a8e.jpg</t>
+        </is>
+      </c>
       <c r="X147" t="n">
         <v>0</v>
       </c>
@@ -23409,7 +23491,7 @@
         <v>0</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
@@ -23834,7 +23916,11 @@
         <v>58547</v>
       </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>1781981467380</t>
+        </is>
+      </c>
       <c r="O150" t="n">
         <v>0</v>
       </c>
@@ -23855,7 +23941,11 @@
         <v>0</v>
       </c>
       <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/58456/c835662b-bbe8-4286-9256-cbc3c23c9eab.jpg</t>
+        </is>
+      </c>
       <c r="X150" t="n">
         <v>0</v>
       </c>
@@ -70481,168 +70571,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF31"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -70749,6 +70849,12 @@
       <c r="AF2" t="n">
         <v>23</v>
       </c>
+      <c r="AG2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>95.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -70853,6 +70959,12 @@
       <c r="AF3" t="n">
         <v>17</v>
       </c>
+      <c r="AG3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -70957,6 +71069,12 @@
       <c r="AF4" t="n">
         <v>44</v>
       </c>
+      <c r="AG4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -71061,6 +71179,12 @@
       <c r="AF5" t="n">
         <v>27</v>
       </c>
+      <c r="AG5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -71165,6 +71289,12 @@
       <c r="AF6" t="n">
         <v>21</v>
       </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -71183,22 +71313,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>997</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -71216,7 +71346,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -71268,6 +71398,12 @@
       </c>
       <c r="AF7" t="n">
         <v>24</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>95.8</v>
       </c>
     </row>
     <row r="8">
@@ -71373,6 +71509,12 @@
       <c r="AF8" t="n">
         <v>13</v>
       </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -71477,6 +71619,12 @@
       <c r="AF9" t="n">
         <v>12</v>
       </c>
+      <c r="AG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>83.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -71581,6 +71729,12 @@
       <c r="AF10" t="n">
         <v>35</v>
       </c>
+      <c r="AG10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -71685,6 +71839,12 @@
       <c r="AF11" t="n">
         <v>34</v>
       </c>
+      <c r="AG11" t="n">
+        <v>33</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>97.09999999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -71789,6 +71949,12 @@
       <c r="AF12" t="n">
         <v>10</v>
       </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -71893,6 +72059,12 @@
       <c r="AF13" t="n">
         <v>11</v>
       </c>
+      <c r="AG13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>63.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -71997,6 +72169,12 @@
       <c r="AF14" t="n">
         <v>10</v>
       </c>
+      <c r="AG14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -72101,6 +72279,12 @@
       <c r="AF15" t="n">
         <v>14</v>
       </c>
+      <c r="AG15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -72205,6 +72389,12 @@
       <c r="AF16" t="n">
         <v>8</v>
       </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -72309,6 +72499,12 @@
       <c r="AF17" t="n">
         <v>5</v>
       </c>
+      <c r="AG17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -72413,6 +72609,12 @@
       <c r="AF18" t="n">
         <v>7</v>
       </c>
+      <c r="AG18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>85.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -72517,6 +72719,12 @@
       <c r="AF19" t="n">
         <v>9</v>
       </c>
+      <c r="AG19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -72621,6 +72829,12 @@
       <c r="AF20" t="n">
         <v>7</v>
       </c>
+      <c r="AG20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -72725,6 +72939,12 @@
       <c r="AF21" t="n">
         <v>9</v>
       </c>
+      <c r="AG21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -72829,6 +73049,12 @@
       <c r="AF22" t="n">
         <v>12</v>
       </c>
+      <c r="AG22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -72933,6 +73159,12 @@
       <c r="AF23" t="n">
         <v>11</v>
       </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -73037,6 +73269,12 @@
       <c r="AF24" t="n">
         <v>9</v>
       </c>
+      <c r="AG24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -73141,6 +73379,12 @@
       <c r="AF25" t="n">
         <v>11</v>
       </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -73245,6 +73489,12 @@
       <c r="AF26" t="n">
         <v>10</v>
       </c>
+      <c r="AG26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -73349,6 +73599,12 @@
       <c r="AF27" t="n">
         <v>11</v>
       </c>
+      <c r="AG27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>81.8</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -73453,6 +73709,12 @@
       <c r="AF28" t="n">
         <v>15</v>
       </c>
+      <c r="AG28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>93.3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -73557,6 +73819,12 @@
       <c r="AF29" t="n">
         <v>9</v>
       </c>
+      <c r="AG29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -73661,6 +73929,12 @@
       <c r="AF30" t="n">
         <v>8</v>
       </c>
+      <c r="AG30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -73764,6 +74038,12 @@
       </c>
       <c r="AF31" t="n">
         <v>10</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -73777,163 +74057,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -73949,22 +74239,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3183</v>
+        <v>4180</v>
       </c>
       <c r="D2" t="n">
-        <v>390</v>
+        <v>468</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>390</v>
+        <v>452</v>
       </c>
       <c r="G2" t="n">
-        <v>3183</v>
+        <v>4180</v>
       </c>
       <c r="H2" t="n">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -73982,7 +74272,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>384</v>
+        <v>446</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -74034,6 +74324,12 @@
       </c>
       <c r="AE2" t="n">
         <v>303</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>283</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -74133,6 +74429,12 @@
       </c>
       <c r="AE3" t="n">
         <v>143</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>139</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>97.2</v>
       </c>
     </row>
   </sheetData>
@@ -74146,158 +74448,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Uploaded Results</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Expected Results</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>INEC Upload Percent</t>
         </is>
       </c>
     </row>
@@ -74308,22 +74625,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6314</v>
+        <v>7311</v>
       </c>
       <c r="C2" t="n">
-        <v>906</v>
+        <v>984</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>903</v>
+        <v>965</v>
       </c>
       <c r="F2" t="n">
-        <v>6272</v>
+        <v>7269</v>
       </c>
       <c r="G2" t="n">
-        <v>896</v>
+        <v>958</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -74341,7 +74658,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>887</v>
+        <v>949</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -74393,6 +74710,15 @@
       </c>
       <c r="AD2" t="n">
         <v>446</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>422</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>446</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>94.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -3230,7 +3218,11 @@
         <v>58452</v>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1781989168496</t>
+        </is>
+      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -3251,7 +3243,11 @@
         <v>0</v>
       </c>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4344/58361/416b175b-d310-46b1-823f-903c003df1d9.jpg</t>
+        </is>
+      </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
@@ -18455,7 +18451,11 @@
         <v>58517</v>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>1781989185005</t>
+        </is>
+      </c>
       <c r="O115" t="n">
         <v>0</v>
       </c>
@@ -18476,7 +18476,11 @@
         <v>0</v>
       </c>
       <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58426/9d2567cd-f63d-44e8-ae16-e80c5e7f1d48.jpg</t>
+        </is>
+      </c>
       <c r="X115" t="n">
         <v>0</v>
       </c>
@@ -24858,7 +24862,11 @@
         <v>148675</v>
       </c>
       <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>1781989174145</t>
+        </is>
+      </c>
       <c r="O156" t="n">
         <v>0</v>
       </c>
@@ -24879,7 +24887,11 @@
         <v>0</v>
       </c>
       <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4349/643963/d40ad240-c6e9-405b-b507-2d798c03c033.jpg</t>
+        </is>
+      </c>
       <c r="X156" t="n">
         <v>0</v>
       </c>
@@ -27531,7 +27543,11 @@
         <v>58559</v>
       </c>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>1781989150355</t>
+        </is>
+      </c>
       <c r="O173" t="n">
         <v>0</v>
       </c>
@@ -27552,7 +27568,11 @@
         <v>0</v>
       </c>
       <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58468/f4c9af61-6597-4919-a174-8ef13dfe0174.jpg</t>
+        </is>
+      </c>
       <c r="X173" t="n">
         <v>0</v>
       </c>
@@ -41627,7 +41647,11 @@
         <v>58613</v>
       </c>
       <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>1781989186259</t>
+        </is>
+      </c>
       <c r="O263" t="n">
         <v>0</v>
       </c>
@@ -41648,7 +41672,11 @@
         <v>0</v>
       </c>
       <c r="V263" t="inlineStr"/>
-      <c r="W263" t="inlineStr"/>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58522/d2e6f629-d8c1-42b6-b812-878ac666ba37.jpg</t>
+        </is>
+      </c>
       <c r="X263" t="n">
         <v>0</v>
       </c>
@@ -47090,7 +47118,11 @@
         <v>58644</v>
       </c>
       <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>1781989197874</t>
+        </is>
+      </c>
       <c r="O298" t="n">
         <v>0</v>
       </c>
@@ -47111,7 +47143,11 @@
         <v>0</v>
       </c>
       <c r="V298" t="inlineStr"/>
-      <c r="W298" t="inlineStr"/>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/58553/4601650b-67ca-402c-9f59-276741939cef.jpg</t>
+        </is>
+      </c>
       <c r="X298" t="n">
         <v>0</v>
       </c>
@@ -49276,7 +49312,11 @@
         <v>64667</v>
       </c>
       <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>1781989138894</t>
+        </is>
+      </c>
       <c r="O312" t="n">
         <v>0</v>
       </c>
@@ -49297,7 +49337,11 @@
         <v>0</v>
       </c>
       <c r="V312" t="inlineStr"/>
-      <c r="W312" t="inlineStr"/>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4717/64577/18b8b138-b286-4064-94bc-7487241e1c0d.jpg</t>
+        </is>
+      </c>
       <c r="X312" t="n">
         <v>0</v>
       </c>
@@ -63251,7 +63295,11 @@
         <v>64736</v>
       </c>
       <c r="M401" t="inlineStr"/>
-      <c r="N401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>1781989191145</t>
+        </is>
+      </c>
       <c r="O401" t="n">
         <v>0</v>
       </c>
@@ -63272,7 +63320,11 @@
         <v>0</v>
       </c>
       <c r="V401" t="inlineStr"/>
-      <c r="W401" t="inlineStr"/>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
+        </is>
+      </c>
       <c r="X401" t="n">
         <v>0</v>
       </c>
@@ -70575,172 +70627,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -70850,10 +70902,10 @@
         <v>23</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -71290,10 +71342,10 @@
         <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>71.40000000000001</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="7">
@@ -71400,10 +71452,10 @@
         <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -71620,10 +71672,10 @@
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="10">
@@ -72060,10 +72112,10 @@
         <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>63.6</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="14">
@@ -72390,10 +72442,10 @@
         <v>8</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="17">
@@ -72610,10 +72662,10 @@
         <v>7</v>
       </c>
       <c r="AG18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH18" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -73600,10 +73652,10 @@
         <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH27" t="n">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -74061,167 +74113,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74326,10 +74378,10 @@
         <v>303</v>
       </c>
       <c r="AF2" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="AG2" t="n">
-        <v>93.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -74431,10 +74483,10 @@
         <v>143</v>
       </c>
       <c r="AF3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG3" t="n">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -74452,167 +74504,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74712,13 +74764,13 @@
         <v>446</v>
       </c>
       <c r="AE2" t="n">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AF2" t="n">
         <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>94.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,227 +432,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -70627,172 +70639,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74113,167 +74125,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74504,167 +74516,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,227 +420,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Election ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Election Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Election Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Ward Code</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Ward ID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Polling Unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PU Code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PU ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Polling Unit ID</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Result Updated Time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Result Info PU</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Image File</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
@@ -70639,172 +70627,172 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ward</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74125,167 +74113,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>
@@ -74516,167 +74504,167 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Ballots Issued</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ballots Used</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invalid Votes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total Accredited</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total Registered</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Valid Votes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>AAC</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ADC</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>APC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>APGA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>APM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>APP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>BP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>DLA</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LP</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>NDC</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NDP</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NNPP</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>NRM</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PDP</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>PRP</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>YP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>YPP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ZLP</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Polling Units</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>INEC Uploaded Results</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>INEC Expected Results</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>INEC Upload Percent</t>
         </is>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -18302,7 +18302,11 @@
         <v>58516</v>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>1782118739740</t>
+        </is>
+      </c>
       <c r="O114" t="n">
         <v>0</v>
       </c>
@@ -18323,7 +18327,11 @@
         <v>0</v>
       </c>
       <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58425/e90bfdc9-bc6d-48ee-ae47-85c5c6c385a1.jpg</t>
+        </is>
+      </c>
       <c r="X114" t="n">
         <v>0</v>
       </c>
@@ -18608,7 +18616,11 @@
         <v>58518</v>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>1782118740191</t>
+        </is>
+      </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
@@ -18629,7 +18641,11 @@
         <v>0</v>
       </c>
       <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/58427/73d7b088-5904-41cf-8b13-8041423e98c5.jpg</t>
+        </is>
+      </c>
       <c r="X116" t="n">
         <v>0</v>
       </c>
@@ -20641,7 +20657,11 @@
         <v>148665</v>
       </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>1782118765969</t>
+        </is>
+      </c>
       <c r="O129" t="n">
         <v>0</v>
       </c>
@@ -20662,7 +20682,11 @@
         <v>0</v>
       </c>
       <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/643953/bd0759ea-0a24-4d6b-855d-94a892fe1e8b.jpg</t>
+        </is>
+      </c>
       <c r="X129" t="n">
         <v>0</v>
       </c>
@@ -20947,7 +20971,11 @@
         <v>148667</v>
       </c>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>1782118777065</t>
+        </is>
+      </c>
       <c r="O131" t="n">
         <v>0</v>
       </c>
@@ -20968,7 +20996,11 @@
         <v>0</v>
       </c>
       <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/643955/e9089086-ec58-4563-bed3-256a049d4b9d.jpg</t>
+        </is>
+      </c>
       <c r="X131" t="n">
         <v>0</v>
       </c>
@@ -21096,7 +21128,11 @@
         <v>148668</v>
       </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>1782118873953</t>
+        </is>
+      </c>
       <c r="O132" t="n">
         <v>0</v>
       </c>
@@ -21117,7 +21153,11 @@
         <v>0</v>
       </c>
       <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4348/643956/27a97a26-7d97-48db-8e05-3ec51819e4b0.jpg</t>
+        </is>
+      </c>
       <c r="X132" t="n">
         <v>0</v>
       </c>
@@ -28014,7 +28054,11 @@
         <v>58562</v>
       </c>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>1782118768987</t>
+        </is>
+      </c>
       <c r="O176" t="n">
         <v>0</v>
       </c>
@@ -28035,7 +28079,11 @@
         <v>0</v>
       </c>
       <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4351/58471/91f949b6-a315-4bf3-86fc-5d7283c06600.jpg</t>
+        </is>
+      </c>
       <c r="X176" t="n">
         <v>0</v>
       </c>
@@ -33978,7 +34026,11 @@
         <v>148699</v>
       </c>
       <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>1782124556840</t>
+        </is>
+      </c>
       <c r="O214" t="n">
         <v>0</v>
       </c>
@@ -33999,7 +34051,11 @@
         <v>0</v>
       </c>
       <c r="V214" t="inlineStr"/>
-      <c r="W214" t="inlineStr"/>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4352/643987/5432ab19-e6f7-4045-9d03-1fab367a775b.jpg</t>
+        </is>
+      </c>
       <c r="X214" t="n">
         <v>0</v>
       </c>
@@ -35540,7 +35596,11 @@
         <v>58588</v>
       </c>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>1782124898997</t>
+        </is>
+      </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
@@ -35561,7 +35621,11 @@
         <v>0</v>
       </c>
       <c r="V224" t="inlineStr"/>
-      <c r="W224" t="inlineStr"/>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4353/58497/7a9cc8d9-94a7-430e-8bbb-a2a7419bebb9.jpg</t>
+        </is>
+      </c>
       <c r="X224" t="n">
         <v>0</v>
       </c>
@@ -41498,7 +41562,11 @@
         <v>58612</v>
       </c>
       <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>1782128022855</t>
+        </is>
+      </c>
       <c r="O262" t="n">
         <v>0</v>
       </c>
@@ -41519,7 +41587,11 @@
         <v>0</v>
       </c>
       <c r="V262" t="inlineStr"/>
-      <c r="W262" t="inlineStr"/>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58521/2a5d71f6-01e8-4df4-8274-0baff74b8732.jpg</t>
+        </is>
+      </c>
       <c r="X262" t="n">
         <v>0</v>
       </c>
@@ -42589,7 +42661,11 @@
         <v>58619</v>
       </c>
       <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>1782125796309</t>
+        </is>
+      </c>
       <c r="O269" t="n">
         <v>0</v>
       </c>
@@ -42610,7 +42686,11 @@
         <v>0</v>
       </c>
       <c r="V269" t="inlineStr"/>
-      <c r="W269" t="inlineStr"/>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58528/f7f05119-44f0-416b-9ee9-941bfae1ec26.jpg</t>
+        </is>
+      </c>
       <c r="X269" t="n">
         <v>0</v>
       </c>
@@ -42895,7 +42975,11 @@
         <v>58621</v>
       </c>
       <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>1782125899883</t>
+        </is>
+      </c>
       <c r="O271" t="n">
         <v>0</v>
       </c>
@@ -42916,7 +43000,11 @@
         <v>0</v>
       </c>
       <c r="V271" t="inlineStr"/>
-      <c r="W271" t="inlineStr"/>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4355/58530/188b7703-1f05-4ef9-974d-e60f47638107.jpg</t>
+        </is>
+      </c>
       <c r="X271" t="n">
         <v>0</v>
       </c>
@@ -46969,7 +47057,11 @@
         <v>58643</v>
       </c>
       <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>1782126996073</t>
+        </is>
+      </c>
       <c r="O297" t="n">
         <v>0</v>
       </c>
@@ -46990,7 +47082,11 @@
         <v>0</v>
       </c>
       <c r="V297" t="inlineStr"/>
-      <c r="W297" t="inlineStr"/>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/58552/4d4940e7-3257-4f56-a227-937ff54fdb00.jpg</t>
+        </is>
+      </c>
       <c r="X297" t="n">
         <v>0</v>
       </c>
@@ -47275,7 +47371,11 @@
         <v>58645</v>
       </c>
       <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>1782124927473</t>
+        </is>
+      </c>
       <c r="O299" t="n">
         <v>0</v>
       </c>
@@ -47296,7 +47396,11 @@
         <v>0</v>
       </c>
       <c r="V299" t="inlineStr"/>
-      <c r="W299" t="inlineStr"/>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/58554/9e63fd90-e236-45e6-9398-a41993c7a130.jpg</t>
+        </is>
+      </c>
       <c r="X299" t="n">
         <v>0</v>
       </c>
@@ -47895,7 +47999,11 @@
         <v>148723</v>
       </c>
       <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>1782126376544</t>
+        </is>
+      </c>
       <c r="O303" t="n">
         <v>0</v>
       </c>
@@ -47916,7 +48024,11 @@
         <v>0</v>
       </c>
       <c r="V303" t="inlineStr"/>
-      <c r="W303" t="inlineStr"/>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/378/4358/644011/313fb0c0-3ba6-49f0-8abd-9d9e5b7267b0.jpg</t>
+        </is>
+      </c>
       <c r="X303" t="n">
         <v>0</v>
       </c>
@@ -63146,7 +63258,11 @@
         <v>64735</v>
       </c>
       <c r="M400" t="inlineStr"/>
-      <c r="N400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>1782131641877</t>
+        </is>
+      </c>
       <c r="O400" t="n">
         <v>0</v>
       </c>
@@ -63167,7 +63283,11 @@
         <v>0</v>
       </c>
       <c r="V400" t="inlineStr"/>
-      <c r="W400" t="inlineStr"/>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
+        </is>
+      </c>
       <c r="X400" t="n">
         <v>0</v>
       </c>
@@ -71342,10 +71462,10 @@
         <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -71672,10 +71792,10 @@
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -71782,10 +71902,10 @@
         <v>35</v>
       </c>
       <c r="AG10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AH10" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -71892,10 +72012,10 @@
         <v>34</v>
       </c>
       <c r="AG11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AH11" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -72112,10 +72232,10 @@
         <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -72442,10 +72562,10 @@
         <v>8</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AH16" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -73652,10 +73772,10 @@
         <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -74378,10 +74498,10 @@
         <v>303</v>
       </c>
       <c r="AF2" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="AG2" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -74483,10 +74603,10 @@
         <v>143</v>
       </c>
       <c r="AF3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>98.59999999999999</v>
+        <v>99.3</v>
       </c>
     </row>
   </sheetData>
@@ -74764,13 +74884,13 @@
         <v>446</v>
       </c>
       <c r="AE2" t="n">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="AF2" t="n">
         <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>96.40000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -74498,10 +74498,10 @@
         <v>303</v>
       </c>
       <c r="AF2" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -74603,10 +74603,10 @@
         <v>143</v>
       </c>
       <c r="AF3" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>99.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -74884,13 +74884,13 @@
         <v>446</v>
       </c>
       <c r="AE2" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -74498,10 +74498,10 @@
         <v>303</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -74603,10 +74603,10 @@
         <v>143</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>99.3</v>
       </c>
     </row>
   </sheetData>
@@ -74884,13 +74884,13 @@
         <v>446</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="AF2" t="n">
         <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>99.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS447"/>
+  <dimension ref="A1:AS436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55986,66 +55986,72 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>GANITSURU I</t>
+          <t>GADDIMA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>19/43/06/001</t>
+          <t>19/43/07/001</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b167</t>
+          <t>6a35c3f587b1768452f7b15d</t>
         </is>
       </c>
       <c r="L354" t="n">
-        <v>64690</v>
-      </c>
-      <c r="M354" t="inlineStr"/>
+        <v>64698</v>
+      </c>
+      <c r="M354" t="n">
+        <v>1781976813192</v>
+      </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>1781968257299</t>
+          <t>1781976812454</t>
         </is>
       </c>
       <c r="O354" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="P354" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="Q354" t="n">
-        <v>0</v>
-      </c>
-      <c r="R354" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>6a36ceec370583337b6e6ff5</t>
+        </is>
+      </c>
       <c r="S354" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="T354" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="U354" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64600/3dd35025-7370-4a00-91d4-d6b4bba79957.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64608/44430731-a4e5-42e1-8f84-2ced962019bd.jpg</t>
         </is>
       </c>
       <c r="X354" t="n">
@@ -56064,13 +56070,13 @@
         <v>0</v>
       </c>
       <c r="AC354" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AD354" t="n">
         <v>0</v>
       </c>
       <c r="AE354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF354" t="n">
         <v>0</v>
@@ -56143,41 +56149,41 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>GANITSURU II</t>
+          <t>JIGAWA I</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>19/43/06/002</t>
+          <t>19/43/07/002</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b166</t>
+          <t>6a35c3f587b1768452f7b15c</t>
         </is>
       </c>
       <c r="L355" t="n">
-        <v>64691</v>
+        <v>64699</v>
       </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr">
         <is>
-          <t>1781968317384</t>
+          <t>1781968304168</t>
         </is>
       </c>
       <c r="O355" t="n">
@@ -56202,7 +56208,7 @@
       <c r="V355" t="inlineStr"/>
       <c r="W355" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64601/dba23b61-e372-4b61-be80-463edb25a272.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64609/d046c66d-ebc1-4a60-98e7-f9827cfc2ef2.jpg</t>
         </is>
       </c>
       <c r="X355" t="n">
@@ -56300,41 +56306,41 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>JEMAGU I</t>
+          <t>JIGAWA II</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>19/43/06/003</t>
+          <t>19/43/07/003</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b168</t>
+          <t>6a35c3f587b1768452f7b15a</t>
         </is>
       </c>
       <c r="L356" t="n">
-        <v>64692</v>
+        <v>64700</v>
       </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr">
         <is>
-          <t>1781968155932</t>
+          <t>1781968209595</t>
         </is>
       </c>
       <c r="O356" t="n">
@@ -56359,7 +56365,7 @@
       <c r="V356" t="inlineStr"/>
       <c r="W356" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64602/4ce5d013-2f71-43b8-bca9-cffb6003b606.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64610/50dc8996-3d84-4192-a526-ee3ff7ed2c73.jpg</t>
         </is>
       </c>
       <c r="X356" t="n">
@@ -56457,41 +56463,41 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>JEMAGU II</t>
+          <t>LITAU/GANJIKAR</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>19/43/06/004</t>
+          <t>19/43/07/004</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b163</t>
+          <t>6a35c3f587b1768452f7b15f</t>
         </is>
       </c>
       <c r="L357" t="n">
-        <v>64693</v>
+        <v>64701</v>
       </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="inlineStr">
         <is>
-          <t>1781968147780</t>
+          <t>1781976960124</t>
         </is>
       </c>
       <c r="O357" t="n">
@@ -56516,7 +56522,7 @@
       <c r="V357" t="inlineStr"/>
       <c r="W357" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64603/886832e3-7ccd-4f4c-9fc1-eb72bcc94b02.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64611/9942f58a-bf41-4ed6-8c3a-bc940b3a00e3.jpg</t>
         </is>
       </c>
       <c r="X357" t="n">
@@ -56614,72 +56620,66 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>MABOYI</t>
+          <t>MAJAWA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>19/43/06/005</t>
+          <t>19/43/07/005</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b169</t>
+          <t>6a35c3f587b1768452f7b159</t>
         </is>
       </c>
       <c r="L358" t="n">
-        <v>64694</v>
-      </c>
-      <c r="M358" t="n">
-        <v>1781969403093</v>
-      </c>
+        <v>64702</v>
+      </c>
+      <c r="M358" t="inlineStr"/>
       <c r="N358" t="inlineStr">
         <is>
-          <t>1781969402549</t>
+          <t>1781968167636</t>
         </is>
       </c>
       <c r="O358" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P358" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q358" t="n">
         <v>0</v>
       </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>6a36b1fa52b6362accb5cc1a</t>
-        </is>
-      </c>
+      <c r="R358" t="inlineStr"/>
       <c r="S358" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="T358" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="U358" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64604/ebef9e29-9513-4269-8a4d-0564c370edd3.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64612/e7a586fe-7050-4813-b4d2-f5eaecb5159e.jpg</t>
         </is>
       </c>
       <c r="X358" t="n">
@@ -56689,7 +56689,7 @@
         <v>0</v>
       </c>
       <c r="Z358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA358" t="n">
         <v>0</v>
@@ -56698,7 +56698,7 @@
         <v>0</v>
       </c>
       <c r="AC358" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="AD358" t="n">
         <v>0</v>
@@ -56777,41 +56777,41 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>MAKERA I</t>
+          <t>MARAYA NAIRA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>19/43/06/006</t>
+          <t>19/43/07/006</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b162</t>
+          <t>6a35c3f587b1768452f7b15b</t>
         </is>
       </c>
       <c r="L359" t="n">
-        <v>64695</v>
+        <v>64703</v>
       </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr">
         <is>
-          <t>1781968270426</t>
+          <t>1781972284783</t>
         </is>
       </c>
       <c r="O359" t="n">
@@ -56836,7 +56836,7 @@
       <c r="V359" t="inlineStr"/>
       <c r="W359" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64605/80844424-5323-4c0e-9062-adb699cb7808.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64613/bbf2dd97-9e62-4b41-a7bb-d2e629535220.jpg</t>
         </is>
       </c>
       <c r="X359" t="n">
@@ -56934,41 +56934,41 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>MAKERA II</t>
+          <t>TOKEN</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>19/43/06/007</t>
+          <t>19/43/07/007</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b165</t>
+          <t>6a35c3f587b1768452f7b15e</t>
         </is>
       </c>
       <c r="L360" t="n">
-        <v>64696</v>
+        <v>64704</v>
       </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr">
         <is>
-          <t>1781968273952</t>
+          <t>1781968288114</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -56993,7 +56993,7 @@
       <c r="V360" t="inlineStr"/>
       <c r="W360" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64606/b8d4919f-e5db-4ea0-ad8c-49f7aa931e7c.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64614/4af81029-93ec-4bfd-a4b7-a90eee1404cd.jpg</t>
         </is>
       </c>
       <c r="X360" t="n">
@@ -57091,41 +57091,41 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>YANLANYA</t>
+          <t>AMANA CITY ISLAMIYYA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>19/43/06/008</t>
+          <t>19/43/07/008</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b164</t>
+          <t>6a35c3f587b1768452f7b161</t>
         </is>
       </c>
       <c r="L361" t="n">
-        <v>64697</v>
+        <v>151210</v>
       </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="inlineStr">
         <is>
-          <t>1781968253472</t>
+          <t>1781968151237</t>
         </is>
       </c>
       <c r="O361" t="n">
@@ -57150,7 +57150,7 @@
       <c r="V361" t="inlineStr"/>
       <c r="W361" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64607/947286d9-4867-4d4c-a220-142dfa94017b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646500/bd4fbb32-460e-4132-89d2-d0a592e696f7.jpg</t>
         </is>
       </c>
       <c r="X361" t="n">
@@ -57248,41 +57248,41 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>JEMAGU PRIMARY SCHOOL III</t>
+          <t>LARABAR GADAR SARKI ISLAMIYYA</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>19/43/06/009</t>
+          <t>19/43/07/009</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16c</t>
+          <t>6a35c3f587b1768452f7b160</t>
         </is>
       </c>
       <c r="L362" t="n">
-        <v>151207</v>
+        <v>151211</v>
       </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr">
         <is>
-          <t>1781970842335</t>
+          <t>1781968248486</t>
         </is>
       </c>
       <c r="O362" t="n">
@@ -57307,7 +57307,7 @@
       <c r="V362" t="inlineStr"/>
       <c r="W362" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646497/6e783e9c-36aa-4f09-8d51-aeaaa1873f50.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646501/0328a449-5fac-4c4f-8ed4-04eb4435266b.jpg</t>
         </is>
       </c>
       <c r="X362" t="n">
@@ -57405,41 +57405,41 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>JEMAGU PRIMARY SCHOOL IV</t>
+          <t>DANHAWAGIWA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>19/43/06/010</t>
+          <t>19/43/09/001</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16a</t>
+          <t>6a35c3f587b1768452f7b213</t>
         </is>
       </c>
       <c r="L363" t="n">
-        <v>151208</v>
+        <v>64714</v>
       </c>
       <c r="M363" t="inlineStr"/>
       <c r="N363" t="inlineStr">
         <is>
-          <t>1781968176573</t>
+          <t>1781970484687</t>
         </is>
       </c>
       <c r="O363" t="n">
@@ -57464,7 +57464,7 @@
       <c r="V363" t="inlineStr"/>
       <c r="W363" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646498/2225d4e0-1127-41c6-be0e-0b9fa30dc617.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
         </is>
       </c>
       <c r="X363" t="n">
@@ -57562,41 +57562,41 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>5f0f3cf18f77bb3acad0a009</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>MAKERA PRIMARY SCHOOL III</t>
+          <t>GISHIRI WUYA I</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>19/43/06/011</t>
+          <t>19/43/09/002</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16b</t>
+          <t>6a35c3f587b1768452f7b215</t>
         </is>
       </c>
       <c r="L364" t="n">
-        <v>151209</v>
+        <v>64715</v>
       </c>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr">
         <is>
-          <t>1781968172505</t>
+          <t>1781970664668</t>
         </is>
       </c>
       <c r="O364" t="n">
@@ -57621,7 +57621,7 @@
       <c r="V364" t="inlineStr"/>
       <c r="W364" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646499/3213bc97-0f45-46d7-809a-47e8c6db7a24.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
         </is>
       </c>
       <c r="X364" t="n">
@@ -57719,72 +57719,72 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>GADDIMA</t>
+          <t>GISHIRI WUYA II</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>19/43/07/001</t>
+          <t>19/43/09/003</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15d</t>
+          <t>6a35c3f587b1768452f7b217</t>
         </is>
       </c>
       <c r="L365" t="n">
-        <v>64698</v>
+        <v>64716</v>
       </c>
       <c r="M365" t="n">
-        <v>1781976813192</v>
+        <v>1781969584429</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>1781976812454</t>
+          <t>1781969583795</t>
         </is>
       </c>
       <c r="O365" t="n">
-        <v>434</v>
+        <v>235</v>
       </c>
       <c r="P365" t="n">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="Q365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>6a36ceec370583337b6e6ff5</t>
+          <t>6a36b2af52b6362accb5cc50</t>
         </is>
       </c>
       <c r="S365" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="T365" t="n">
-        <v>434</v>
+        <v>235</v>
       </c>
       <c r="U365" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64608/44430731-a4e5-42e1-8f84-2ced962019bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
         </is>
       </c>
       <c r="X365" t="n">
@@ -57803,13 +57803,13 @@
         <v>0</v>
       </c>
       <c r="AC365" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="AD365" t="n">
         <v>0</v>
       </c>
       <c r="AE365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF365" t="n">
         <v>0</v>
@@ -57882,41 +57882,41 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>JIGAWA I</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>19/43/07/002</t>
+          <t>19/43/09/004</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15c</t>
+          <t>6a35c3f587b1768452f7b210</t>
         </is>
       </c>
       <c r="L366" t="n">
-        <v>64699</v>
+        <v>64717</v>
       </c>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="inlineStr">
         <is>
-          <t>1781968304168</t>
+          <t>1781976885564</t>
         </is>
       </c>
       <c r="O366" t="n">
@@ -57941,7 +57941,7 @@
       <c r="V366" t="inlineStr"/>
       <c r="W366" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64609/d046c66d-ebc1-4a60-98e7-f9827cfc2ef2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
         </is>
       </c>
       <c r="X366" t="n">
@@ -58039,41 +58039,41 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>JIGAWA II</t>
+          <t>KINCHAU</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>19/43/07/003</t>
+          <t>19/43/09/005</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15a</t>
+          <t>6a35c3f587b1768452f7b212</t>
         </is>
       </c>
       <c r="L367" t="n">
-        <v>64700</v>
+        <v>64718</v>
       </c>
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="inlineStr">
         <is>
-          <t>1781968209595</t>
+          <t>1781976801113</t>
         </is>
       </c>
       <c r="O367" t="n">
@@ -58098,7 +58098,7 @@
       <c r="V367" t="inlineStr"/>
       <c r="W367" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64610/50dc8996-3d84-4192-a526-ee3ff7ed2c73.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
         </is>
       </c>
       <c r="X367" t="n">
@@ -58196,41 +58196,41 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>LITAU/GANJIKAR</t>
+          <t>NAIRA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>19/43/07/004</t>
+          <t>19/43/09/006</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15f</t>
+          <t>6a35c3f587b1768452f7b214</t>
         </is>
       </c>
       <c r="L368" t="n">
-        <v>64701</v>
+        <v>64719</v>
       </c>
       <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr">
         <is>
-          <t>1781976960124</t>
+          <t>1781976797855</t>
         </is>
       </c>
       <c r="O368" t="n">
@@ -58255,7 +58255,7 @@
       <c r="V368" t="inlineStr"/>
       <c r="W368" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64611/9942f58a-bf41-4ed6-8c3a-bc940b3a00e3.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
         </is>
       </c>
       <c r="X368" t="n">
@@ -58353,41 +58353,41 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>MAJAWA</t>
+          <t>TURBA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>19/43/07/005</t>
+          <t>19/43/09/007</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b159</t>
+          <t>6a35c3f587b1768452f7b211</t>
         </is>
       </c>
       <c r="L369" t="n">
-        <v>64702</v>
+        <v>64720</v>
       </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr">
         <is>
-          <t>1781968167636</t>
+          <t>1781970126235</t>
         </is>
       </c>
       <c r="O369" t="n">
@@ -58412,7 +58412,7 @@
       <c r="V369" t="inlineStr"/>
       <c r="W369" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64612/e7a586fe-7050-4813-b4d2-f5eaecb5159e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
         </is>
       </c>
       <c r="X369" t="n">
@@ -58510,41 +58510,41 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>MARAYA NAIRA</t>
+          <t>WALAGIGI</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>19/43/07/006</t>
+          <t>19/43/09/008</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15b</t>
+          <t>6a35c3f587b1768452f7b216</t>
         </is>
       </c>
       <c r="L370" t="n">
-        <v>64703</v>
+        <v>64721</v>
       </c>
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr">
         <is>
-          <t>1781972284783</t>
+          <t>1781973924024</t>
         </is>
       </c>
       <c r="O370" t="n">
@@ -58569,7 +58569,7 @@
       <c r="V370" t="inlineStr"/>
       <c r="W370" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64613/bbf2dd97-9e62-4b41-a7bb-d2e629535220.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
         </is>
       </c>
       <c r="X370" t="n">
@@ -58667,41 +58667,41 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>TOKEN</t>
+          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>19/43/07/007</t>
+          <t>19/43/09/009</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15e</t>
+          <t>6a35c3f587b1768452f7b219</t>
         </is>
       </c>
       <c r="L371" t="n">
-        <v>64704</v>
+        <v>151215</v>
       </c>
       <c r="M371" t="inlineStr"/>
       <c r="N371" t="inlineStr">
         <is>
-          <t>1781968288114</t>
+          <t>1781976919845</t>
         </is>
       </c>
       <c r="O371" t="n">
@@ -58726,7 +58726,7 @@
       <c r="V371" t="inlineStr"/>
       <c r="W371" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64614/4af81029-93ec-4bfd-a4b7-a90eee1404cd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
         </is>
       </c>
       <c r="X371" t="n">
@@ -58824,41 +58824,41 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>AMANA CITY ISLAMIYYA</t>
+          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>19/43/07/008</t>
+          <t>19/43/09/010</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b161</t>
+          <t>6a35c3f587b1768452f7b218</t>
         </is>
       </c>
       <c r="L372" t="n">
-        <v>151210</v>
+        <v>151216</v>
       </c>
       <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr">
         <is>
-          <t>1781968151237</t>
+          <t>1781973731518</t>
         </is>
       </c>
       <c r="O372" t="n">
@@ -58883,7 +58883,7 @@
       <c r="V372" t="inlineStr"/>
       <c r="W372" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646500/bd4fbb32-460e-4132-89d2-d0a592e696f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
         </is>
       </c>
       <c r="X372" t="n">
@@ -58981,41 +58981,41 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>LARABAR GADAR SARKI ISLAMIYYA</t>
+          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>19/43/07/009</t>
+          <t>19/43/09/011</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b160</t>
+          <t>6a35c3f587b1768452f7b21a</t>
         </is>
       </c>
       <c r="L373" t="n">
-        <v>151211</v>
+        <v>151217</v>
       </c>
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr">
         <is>
-          <t>1781968248486</t>
+          <t>1781977138945</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -59040,7 +59040,7 @@
       <c r="V373" t="inlineStr"/>
       <c r="W373" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646501/0328a449-5fac-4c4f-8ed4-04eb4435266b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
         </is>
       </c>
       <c r="X373" t="n">
@@ -59138,41 +59138,41 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>DANHAWAGIWA</t>
+          <t>GANAKAKUN I</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>19/43/09/001</t>
+          <t>19/43/10/001</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b213</t>
+          <t>6a35c3f587b1768452f7b1cf</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>64714</v>
+        <v>64722</v>
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr">
         <is>
-          <t>1781970484687</t>
+          <t>1781968221436</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -59197,7 +59197,7 @@
       <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
         </is>
       </c>
       <c r="X374" t="n">
@@ -59295,41 +59295,41 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA I</t>
+          <t>GANAKAKUN II</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>19/43/09/002</t>
+          <t>19/43/10/002</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b215</t>
+          <t>6a35c3f587b1768452f7b1ce</t>
         </is>
       </c>
       <c r="L375" t="n">
-        <v>64715</v>
+        <v>64723</v>
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr">
         <is>
-          <t>1781970664668</t>
+          <t>1781968244797</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -59354,7 +59354,7 @@
       <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
         </is>
       </c>
       <c r="X375" t="n">
@@ -59452,72 +59452,66 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA II</t>
+          <t>MADARIN MABA I</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>19/43/09/003</t>
+          <t>19/43/10/003</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b217</t>
+          <t>6a35c3f587b1768452f7b1d3</t>
         </is>
       </c>
       <c r="L376" t="n">
-        <v>64716</v>
-      </c>
-      <c r="M376" t="n">
-        <v>1781969584429</v>
-      </c>
+        <v>64724</v>
+      </c>
+      <c r="M376" t="inlineStr"/>
       <c r="N376" t="inlineStr">
         <is>
-          <t>1781969583795</t>
+          <t>1781968265095</t>
         </is>
       </c>
       <c r="O376" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="P376" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q376" t="n">
         <v>0</v>
       </c>
-      <c r="R376" t="inlineStr">
-        <is>
-          <t>6a36b2af52b6362accb5cc50</t>
-        </is>
-      </c>
+      <c r="R376" t="inlineStr"/>
       <c r="S376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="T376" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="U376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
         </is>
       </c>
       <c r="X376" t="n">
@@ -59536,7 +59530,7 @@
         <v>0</v>
       </c>
       <c r="AC376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD376" t="n">
         <v>0</v>
@@ -59615,41 +59609,41 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARIN MABA II</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>19/43/09/004</t>
+          <t>19/43/10/004</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b210</t>
+          <t>6a35c3f587b1768452f7b1d0</t>
         </is>
       </c>
       <c r="L377" t="n">
-        <v>64717</v>
+        <v>64725</v>
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
-          <t>1781976885564</t>
+          <t>1781971564529</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -59674,7 +59668,7 @@
       <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
         </is>
       </c>
       <c r="X377" t="n">
@@ -59772,41 +59766,41 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>KINCHAU</t>
+          <t>MADARIN MABA III</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>19/43/09/005</t>
+          <t>19/43/10/005</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b212</t>
+          <t>6a35c3f587b1768452f7b1d2</t>
         </is>
       </c>
       <c r="L378" t="n">
-        <v>64718</v>
+        <v>64726</v>
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
-          <t>1781976801113</t>
+          <t>1781971929292</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -59831,7 +59825,7 @@
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
         </is>
       </c>
       <c r="X378" t="n">
@@ -59929,41 +59923,41 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>NAIRA</t>
+          <t>MARAYAR WUTA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>19/43/09/006</t>
+          <t>19/43/10/006</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b214</t>
+          <t>6a35c3f587b1768452f7b1cd</t>
         </is>
       </c>
       <c r="L379" t="n">
-        <v>64719</v>
+        <v>64727</v>
       </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
-          <t>1781976797855</t>
+          <t>1781971930377</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -59988,7 +59982,7 @@
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
         </is>
       </c>
       <c r="X379" t="n">
@@ -60086,41 +60080,41 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>TURBA</t>
+          <t>SABON GARIN NASARA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>19/43/09/007</t>
+          <t>19/43/10/007</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b211</t>
+          <t>6a35c3f587b1768452f7b1cc</t>
         </is>
       </c>
       <c r="L380" t="n">
-        <v>64720</v>
+        <v>64728</v>
       </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
-          <t>1781970126235</t>
+          <t>1781971922925</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -60145,7 +60139,7 @@
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
         </is>
       </c>
       <c r="X380" t="n">
@@ -60243,41 +60237,41 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>WALAGIGI</t>
+          <t>TALAWA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>19/43/09/008</t>
+          <t>19/43/10/008</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b216</t>
+          <t>6a35c3f587b1768452f7b1d1</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>64721</v>
+        <v>64729</v>
       </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
-          <t>1781973924024</t>
+          <t>1781968262106</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -60302,7 +60296,7 @@
       <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
         </is>
       </c>
       <c r="X381" t="n">
@@ -60400,41 +60394,41 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
+          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19/43/09/009</t>
+          <t>19/43/10/009</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b219</t>
+          <t>6a35c3f587b1768452f7b1d5</t>
         </is>
       </c>
       <c r="L382" t="n">
-        <v>151215</v>
+        <v>151218</v>
       </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
-          <t>1781976919845</t>
+          <t>1781972103434</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -60459,7 +60453,7 @@
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
         </is>
       </c>
       <c r="X382" t="n">
@@ -60557,41 +60551,41 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
+          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19/43/09/010</t>
+          <t>19/43/10/010</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b218</t>
+          <t>6a35c3f587b1768452f7b1d4</t>
         </is>
       </c>
       <c r="L383" t="n">
-        <v>151216</v>
+        <v>151219</v>
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr">
         <is>
-          <t>1781973731518</t>
+          <t>1781972285399</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -60616,7 +60610,7 @@
       <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
         </is>
       </c>
       <c r="X383" t="n">
@@ -60714,41 +60708,41 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
+          <t>FARTAWA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19/43/09/011</t>
+          <t>19/43/11/001</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21a</t>
+          <t>6a35c3f587b1768452f7b21c</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>151217</v>
+        <v>64730</v>
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr">
         <is>
-          <t>1781977138945</t>
+          <t>1781977074928</t>
         </is>
       </c>
       <c r="O384" t="n">
@@ -60773,7 +60767,7 @@
       <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
         </is>
       </c>
       <c r="X384" t="n">
@@ -60871,41 +60865,41 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>GANAKAKUN I</t>
+          <t>TAMBURAWAR GABAS I</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>19/43/10/001</t>
+          <t>19/43/11/002</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cf</t>
+          <t>6a35c3f587b1768452f7b223</t>
         </is>
       </c>
       <c r="L385" t="n">
-        <v>64722</v>
+        <v>64731</v>
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr">
         <is>
-          <t>1781968221436</t>
+          <t>1781977113305</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -60930,7 +60924,7 @@
       <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
         </is>
       </c>
       <c r="X385" t="n">
@@ -61028,41 +61022,41 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>GANAKAKUN II</t>
+          <t>TAMBURAWAR GABAS II</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19/43/10/002</t>
+          <t>19/43/11/003</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ce</t>
+          <t>6a35c3f587b1768452f7b21b</t>
         </is>
       </c>
       <c r="L386" t="n">
-        <v>64723</v>
+        <v>64732</v>
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr">
         <is>
-          <t>1781968244797</t>
+          <t>1781977075062</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -61087,7 +61081,7 @@
       <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
         </is>
       </c>
       <c r="X386" t="n">
@@ -61185,41 +61179,41 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>MADARIN MABA I</t>
+          <t>UNGUWAR ZURURU</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19/43/10/003</t>
+          <t>19/43/11/004</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d3</t>
+          <t>6a35c3f587b1768452f7b222</t>
         </is>
       </c>
       <c r="L387" t="n">
-        <v>64724</v>
+        <v>64733</v>
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr">
         <is>
-          <t>1781968265095</t>
+          <t>1781975346942</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -61244,7 +61238,7 @@
       <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
         </is>
       </c>
       <c r="X387" t="n">
@@ -61342,41 +61336,41 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>MADARIN MABA II</t>
+          <t>YANDADI I</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19/43/10/004</t>
+          <t>19/43/11/005</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d0</t>
+          <t>6a35c3f587b1768452f7b221</t>
         </is>
       </c>
       <c r="L388" t="n">
-        <v>64725</v>
+        <v>64734</v>
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr">
         <is>
-          <t>1781971564529</t>
+          <t>1781975887400</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -61401,7 +61395,7 @@
       <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
         </is>
       </c>
       <c r="X388" t="n">
@@ -61499,41 +61493,41 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>MADARIN MABA III</t>
+          <t>YANDADI II</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>19/43/10/005</t>
+          <t>19/43/11/006</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d2</t>
+          <t>6a35c3f587b1768452f7b21e</t>
         </is>
       </c>
       <c r="L389" t="n">
-        <v>64726</v>
+        <v>64735</v>
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr">
         <is>
-          <t>1781971929292</t>
+          <t>1782131641877</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -61558,7 +61552,7 @@
       <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
         </is>
       </c>
       <c r="X389" t="n">
@@ -61656,41 +61650,41 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>MARAYAR WUTA</t>
+          <t>YADAUDU I</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19/43/10/006</t>
+          <t>19/43/11/007</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cd</t>
+          <t>6a35c3f587b1768452f7b220</t>
         </is>
       </c>
       <c r="L390" t="n">
-        <v>64727</v>
+        <v>64736</v>
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr">
         <is>
-          <t>1781971930377</t>
+          <t>1781989191145</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -61715,7 +61709,7 @@
       <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
         </is>
       </c>
       <c r="X390" t="n">
@@ -61813,41 +61807,41 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>SABON GARIN NASARA</t>
+          <t>YADAUDU II</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19/43/10/007</t>
+          <t>19/43/11/008</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cc</t>
+          <t>6a35c3f587b1768452f7b21f</t>
         </is>
       </c>
       <c r="L391" t="n">
-        <v>64728</v>
+        <v>64737</v>
       </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr">
         <is>
-          <t>1781971922925</t>
+          <t>1781976878903</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -61872,7 +61866,7 @@
       <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
         </is>
       </c>
       <c r="X391" t="n">
@@ -61970,41 +61964,41 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>TALAWA</t>
+          <t>ZANGO DANMARKE</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19/43/10/008</t>
+          <t>19/43/11/009</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d1</t>
+          <t>6a35c3f587b1768452f7b21d</t>
         </is>
       </c>
       <c r="L392" t="n">
-        <v>64729</v>
+        <v>64738</v>
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
         <is>
-          <t>1781968262106</t>
+          <t>1781976780359</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -62029,7 +62023,7 @@
       <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
         </is>
       </c>
       <c r="X392" t="n">
@@ -62127,41 +62121,41 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>19/43/10/009</t>
+          <t>19/43/11/010</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d5</t>
+          <t>6a35c3f587b1768452f7b224</t>
         </is>
       </c>
       <c r="L393" t="n">
-        <v>151218</v>
+        <v>151220</v>
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr">
         <is>
-          <t>1781972103434</t>
+          <t>1781977094685</t>
         </is>
       </c>
       <c r="O393" t="n">
@@ -62186,7 +62180,7 @@
       <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
         </is>
       </c>
       <c r="X393" t="n">
@@ -62284,41 +62278,41 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>19/43/10/010</t>
+          <t>19/43/11/011</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d4</t>
+          <t>6a35c3f587b1768452f7b225</t>
         </is>
       </c>
       <c r="L394" t="n">
-        <v>151219</v>
+        <v>151221</v>
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
         <is>
-          <t>1781972285399</t>
+          <t>1781976782683</t>
         </is>
       </c>
       <c r="O394" t="n">
@@ -62343,7 +62337,7 @@
       <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
         </is>
       </c>
       <c r="X394" t="n">
@@ -62441,41 +62435,41 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>FARTAWA</t>
+          <t>CHARKA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19/43/11/001</t>
+          <t>19/43/12/001</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21c</t>
+          <t>6a35c3f587b1768452f7b171</t>
         </is>
       </c>
       <c r="L395" t="n">
-        <v>64730</v>
+        <v>64739</v>
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
         <is>
-          <t>1781977074928</t>
+          <t>1781976872268</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -62500,7 +62494,7 @@
       <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
         </is>
       </c>
       <c r="X395" t="n">
@@ -62598,41 +62592,41 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS I</t>
+          <t>DANFARI I</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19/43/11/002</t>
+          <t>19/43/12/002</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b223</t>
+          <t>6a35c3f587b1768452f7b16d</t>
         </is>
       </c>
       <c r="L396" t="n">
-        <v>64731</v>
+        <v>64740</v>
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr">
         <is>
-          <t>1781977113305</t>
+          <t>1781976901500</t>
         </is>
       </c>
       <c r="O396" t="n">
@@ -62657,7 +62651,7 @@
       <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
         </is>
       </c>
       <c r="X396" t="n">
@@ -62755,41 +62749,41 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS II</t>
+          <t>DANFARI II</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>19/43/11/003</t>
+          <t>19/43/12/003</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21b</t>
+          <t>6a35c3f587b1768452f7b175</t>
         </is>
       </c>
       <c r="L397" t="n">
-        <v>64732</v>
+        <v>64741</v>
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr">
         <is>
-          <t>1781977075062</t>
+          <t>1781968309565</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -62814,7 +62808,7 @@
       <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
         </is>
       </c>
       <c r="X397" t="n">
@@ -62912,41 +62906,41 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>UNGUWAR ZURURU</t>
+          <t>DANTSAWA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>19/43/11/004</t>
+          <t>19/43/12/004</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b222</t>
+          <t>6a35c3f587b1768452f7b170</t>
         </is>
       </c>
       <c r="L398" t="n">
-        <v>64733</v>
+        <v>64742</v>
       </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr">
         <is>
-          <t>1781975346942</t>
+          <t>1781968186810</t>
         </is>
       </c>
       <c r="O398" t="n">
@@ -62971,7 +62965,7 @@
       <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
         </is>
       </c>
       <c r="X398" t="n">
@@ -63069,41 +63063,41 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>YANDADI I</t>
+          <t>HALADAWA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19/43/11/005</t>
+          <t>19/43/12/005</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b221</t>
+          <t>6a35c3f587b1768452f7b179</t>
         </is>
       </c>
       <c r="L399" t="n">
-        <v>64734</v>
+        <v>64743</v>
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr">
         <is>
-          <t>1781975887400</t>
+          <t>1781976861221</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -63128,7 +63122,7 @@
       <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
         </is>
       </c>
       <c r="X399" t="n">
@@ -63226,41 +63220,41 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>YANDADI II</t>
+          <t>HAYIN WAZO</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>19/43/11/006</t>
+          <t>19/43/12/006</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21e</t>
+          <t>6a35c3f587b1768452f7b16f</t>
         </is>
       </c>
       <c r="L400" t="n">
-        <v>64735</v>
+        <v>64744</v>
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr">
         <is>
-          <t>1782131641877</t>
+          <t>1781976900341</t>
         </is>
       </c>
       <c r="O400" t="n">
@@ -63285,7 +63279,7 @@
       <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
         </is>
       </c>
       <c r="X400" t="n">
@@ -63383,41 +63377,41 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>YADAUDU I</t>
+          <t>JILAWA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19/43/11/007</t>
+          <t>19/43/12/007</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b220</t>
+          <t>6a35c3f587b1768452f7b174</t>
         </is>
       </c>
       <c r="L401" t="n">
-        <v>64736</v>
+        <v>64745</v>
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr">
         <is>
-          <t>1781989191145</t>
+          <t>1781968169241</t>
         </is>
       </c>
       <c r="O401" t="n">
@@ -63442,7 +63436,7 @@
       <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
         </is>
       </c>
       <c r="X401" t="n">
@@ -63540,41 +63534,41 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>YADAUDU II</t>
+          <t>KARGAWA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19/43/11/008</t>
+          <t>19/43/12/008</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21f</t>
+          <t>6a35c3f587b1768452f7b17a</t>
         </is>
       </c>
       <c r="L402" t="n">
-        <v>64737</v>
+        <v>64746</v>
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr">
         <is>
-          <t>1781976878903</t>
+          <t>1781976889527</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -63599,7 +63593,7 @@
       <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
         </is>
       </c>
       <c r="X402" t="n">
@@ -63697,41 +63691,41 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>ZANGO DANMARKE</t>
+          <t>MARAYAR ROGO</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19/43/11/009</t>
+          <t>19/43/12/009</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21d</t>
+          <t>6a35c3f587b1768452f7b178</t>
         </is>
       </c>
       <c r="L403" t="n">
-        <v>64738</v>
+        <v>64747</v>
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr">
         <is>
-          <t>1781976780359</t>
+          <t>1781976782857</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -63756,7 +63750,7 @@
       <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
         </is>
       </c>
       <c r="X403" t="n">
@@ -63854,41 +63848,41 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
+          <t>RIGAR GABAS</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19/43/11/010</t>
+          <t>19/43/12/010</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b224</t>
+          <t>6a35c3f587b1768452f7b177</t>
         </is>
       </c>
       <c r="L404" t="n">
-        <v>151220</v>
+        <v>64748</v>
       </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr">
         <is>
-          <t>1781977094685</t>
+          <t>1781968289759</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -63913,7 +63907,7 @@
       <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
         </is>
       </c>
       <c r="X404" t="n">
@@ -64011,41 +64005,41 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
+          <t>TANAGAR I</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19/43/11/011</t>
+          <t>19/43/12/011</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b225</t>
+          <t>6a35c3f587b1768452f7b173</t>
         </is>
       </c>
       <c r="L405" t="n">
-        <v>151221</v>
+        <v>64749</v>
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr">
         <is>
-          <t>1781976782683</t>
+          <t>1781976813571</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -64070,7 +64064,7 @@
       <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
         </is>
       </c>
       <c r="X405" t="n">
@@ -64183,26 +64177,26 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>CHARKA</t>
+          <t>TANAGAR II</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>19/43/12/001</t>
+          <t>19/43/12/012</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b171</t>
+          <t>6a35c3f587b1768452f7b172</t>
         </is>
       </c>
       <c r="L406" t="n">
-        <v>64739</v>
+        <v>64750</v>
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
-          <t>1781976872268</t>
+          <t>1781976798491</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -64227,7 +64221,7 @@
       <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
         </is>
       </c>
       <c r="X406" t="n">
@@ -64340,28 +64334,24 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>DANFARI I</t>
+          <t>WARKAI RUGAR YAMMA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>19/43/12/002</t>
+          <t>19/43/12/013</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16d</t>
+          <t>6a35c3f587b1768452f7b176</t>
         </is>
       </c>
       <c r="L407" t="n">
-        <v>64740</v>
+        <v>64751</v>
       </c>
       <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>1781976901500</t>
-        </is>
-      </c>
+      <c r="N407" t="inlineStr"/>
       <c r="O407" t="n">
         <v>0</v>
       </c>
@@ -64382,11 +64372,7 @@
         <v>0</v>
       </c>
       <c r="V407" t="inlineStr"/>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
-        </is>
-      </c>
+      <c r="W407" t="inlineStr"/>
       <c r="X407" t="n">
         <v>0</v>
       </c>
@@ -64497,26 +64483,26 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>DANFARI II</t>
+          <t>YALMA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>19/43/12/003</t>
+          <t>19/43/12/014</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b175</t>
+          <t>6a35c3f587b1768452f7b16e</t>
         </is>
       </c>
       <c r="L408" t="n">
-        <v>64741</v>
+        <v>64752</v>
       </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="inlineStr">
         <is>
-          <t>1781968309565</t>
+          <t>1781976792595</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -64541,7 +64527,7 @@
       <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
         </is>
       </c>
       <c r="X408" t="n">
@@ -64654,26 +64640,26 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DANTSAWA</t>
+          <t>TANAGAR III (TANAGAR VETERINARY)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19/43/12/004</t>
+          <t>19/43/12/015</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b170</t>
+          <t>6a35c3f587b1768452f7b17b</t>
         </is>
       </c>
       <c r="L409" t="n">
-        <v>64742</v>
+        <v>151222</v>
       </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr">
         <is>
-          <t>1781968186810</t>
+          <t>1781976850366</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -64698,7 +64684,7 @@
       <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
         </is>
       </c>
       <c r="X409" t="n">
@@ -64796,41 +64782,41 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>HALADAWA</t>
+          <t>DUSHE I</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19/43/12/005</t>
+          <t>19/43/13/001</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b179</t>
+          <t>6a35c3f487b1768452f7b098</t>
         </is>
       </c>
       <c r="L410" t="n">
-        <v>64743</v>
+        <v>64753</v>
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr">
         <is>
-          <t>1781976861221</t>
+          <t>1781976869394</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -64855,7 +64841,7 @@
       <c r="V410" t="inlineStr"/>
       <c r="W410" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
         </is>
       </c>
       <c r="X410" t="n">
@@ -64953,41 +64939,41 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>HAYIN WAZO</t>
+          <t>DUSHE II</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>19/43/12/006</t>
+          <t>19/43/13/002</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16f</t>
+          <t>6a35c3f487b1768452f7b09b</t>
         </is>
       </c>
       <c r="L411" t="n">
-        <v>64744</v>
+        <v>64754</v>
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr">
         <is>
-          <t>1781976900341</t>
+          <t>1781974086141</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -65012,7 +64998,7 @@
       <c r="V411" t="inlineStr"/>
       <c r="W411" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
         </is>
       </c>
       <c r="X411" t="n">
@@ -65110,41 +65096,41 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>JILAWA</t>
+          <t>JALAWA I</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19/43/12/007</t>
+          <t>19/43/13/003</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b174</t>
+          <t>6a35c3f487b1768452f7b09c</t>
         </is>
       </c>
       <c r="L412" t="n">
-        <v>64745</v>
+        <v>64755</v>
       </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr">
         <is>
-          <t>1781968169241</t>
+          <t>1781976938520</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -65169,7 +65155,7 @@
       <c r="V412" t="inlineStr"/>
       <c r="W412" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
         </is>
       </c>
       <c r="X412" t="n">
@@ -65267,41 +65253,41 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>KARGAWA</t>
+          <t>JALAWA II</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19/43/12/008</t>
+          <t>19/43/13/004</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17a</t>
+          <t>6a35c3f487b1768452f7b09a</t>
         </is>
       </c>
       <c r="L413" t="n">
-        <v>64746</v>
+        <v>64756</v>
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr">
         <is>
-          <t>1781976889527</t>
+          <t>1781977012376</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -65326,7 +65312,7 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
         </is>
       </c>
       <c r="X413" t="n">
@@ -65424,41 +65410,41 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>MARAYAR ROGO</t>
+          <t>WARAWA I</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19/43/12/009</t>
+          <t>19/43/13/005</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b178</t>
+          <t>6a35c3f487b1768452f7b099</t>
         </is>
       </c>
       <c r="L414" t="n">
-        <v>64747</v>
+        <v>64757</v>
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr">
         <is>
-          <t>1781976782857</t>
+          <t>1781977113973</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -65483,7 +65469,7 @@
       <c r="V414" t="inlineStr"/>
       <c r="W414" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
         </is>
       </c>
       <c r="X414" t="n">
@@ -65581,41 +65567,41 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>RIGAR GABAS</t>
+          <t>WARAWA II</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>19/43/12/010</t>
+          <t>19/43/13/006</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b177</t>
+          <t>6a35c3f487b1768452f7b09d</t>
         </is>
       </c>
       <c r="L415" t="n">
-        <v>64748</v>
+        <v>64758</v>
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr">
         <is>
-          <t>1781968289759</t>
+          <t>1781976876830</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -65640,7 +65626,7 @@
       <c r="V415" t="inlineStr"/>
       <c r="W415" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
         </is>
       </c>
       <c r="X415" t="n">
@@ -65738,41 +65724,41 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>TANAGAR I</t>
+          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19/43/12/011</t>
+          <t>19/43/13/007</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b173</t>
+          <t>6a35c3f487b1768452f7b09f</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>64749</v>
+        <v>151223</v>
       </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr">
         <is>
-          <t>1781976813571</t>
+          <t>1781976882480</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -65797,7 +65783,7 @@
       <c r="V416" t="inlineStr"/>
       <c r="W416" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
         </is>
       </c>
       <c r="X416" t="n">
@@ -65895,66 +65881,72 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>TANAGAR II</t>
+          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>19/43/12/012</t>
+          <t>19/43/13/008</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b172</t>
+          <t>6a35c3f487b1768452f7b0a0</t>
         </is>
       </c>
       <c r="L417" t="n">
-        <v>64750</v>
-      </c>
-      <c r="M417" t="inlineStr"/>
+        <v>151224</v>
+      </c>
+      <c r="M417" t="n">
+        <v>1781968214959</v>
+      </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>1781976798491</t>
+          <t>1781968212953</t>
         </is>
       </c>
       <c r="O417" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P417" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q417" t="n">
-        <v>0</v>
-      </c>
-      <c r="R417" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>6a36ad5552b6362accb5c7d0</t>
+        </is>
+      </c>
       <c r="S417" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T417" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="U417" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V417" t="inlineStr"/>
       <c r="W417" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
         </is>
       </c>
       <c r="X417" t="n">
@@ -65973,7 +65965,7 @@
         <v>0</v>
       </c>
       <c r="AC417" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD417" t="n">
         <v>0</v>
@@ -66052,39 +66044,43 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>WARKAI RUGAR YAMMA</t>
+          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19/43/12/013</t>
+          <t>19/43/13/009</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b176</t>
+          <t>6a35c3f487b1768452f7b09e</t>
         </is>
       </c>
       <c r="L418" t="n">
-        <v>64751</v>
+        <v>151225</v>
       </c>
       <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>1781968282375</t>
+        </is>
+      </c>
       <c r="O418" t="n">
         <v>0</v>
       </c>
@@ -66105,7 +66101,11 @@
         <v>0</v>
       </c>
       <c r="V418" t="inlineStr"/>
-      <c r="W418" t="inlineStr"/>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
+        </is>
+      </c>
       <c r="X418" t="n">
         <v>0</v>
       </c>
@@ -66201,41 +66201,41 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>YALMA</t>
+          <t>GUMAKA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19/43/12/014</t>
+          <t>19/43/14/001</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16e</t>
+          <t>6a35c3f587b1768452f7b17e</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>64752</v>
+        <v>64759</v>
       </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
         <is>
-          <t>1781976792595</t>
+          <t>1781975166154</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -66260,7 +66260,7 @@
       <c r="V419" t="inlineStr"/>
       <c r="W419" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
         </is>
       </c>
       <c r="X419" t="n">
@@ -66358,41 +66358,41 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>TANAGAR III (TANAGAR VETERINARY)</t>
+          <t>KANWA</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19/43/12/015</t>
+          <t>19/43/14/002</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17b</t>
+          <t>6a35c3f587b1768452f7b17c</t>
         </is>
       </c>
       <c r="L420" t="n">
-        <v>151222</v>
+        <v>64760</v>
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
         <is>
-          <t>1781976850366</t>
+          <t>1781974985005</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -66417,7 +66417,7 @@
       <c r="V420" t="inlineStr"/>
       <c r="W420" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
         </is>
       </c>
       <c r="X420" t="n">
@@ -66515,41 +66515,41 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>DUSHE I</t>
+          <t>POLICE ACADEMY</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19/43/13/001</t>
+          <t>19/43/14/003</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b098</t>
+          <t>6a35c3f587b1768452f7b17d</t>
         </is>
       </c>
       <c r="L421" t="n">
-        <v>64753</v>
+        <v>64761</v>
       </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
         <is>
-          <t>1781976869394</t>
+          <t>1781975165502</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -66574,7 +66574,7 @@
       <c r="V421" t="inlineStr"/>
       <c r="W421" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
         </is>
       </c>
       <c r="X421" t="n">
@@ -66672,41 +66672,41 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>DUSHE II</t>
+          <t>'YANDALLA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>19/43/13/002</t>
+          <t>19/43/14/004</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09b</t>
+          <t>6a35c3f587b1768452f7b17f</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>64754</v>
+        <v>64762</v>
       </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
         <is>
-          <t>1781974086141</t>
+          <t>1781975169663</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -66731,7 +66731,7 @@
       <c r="V422" t="inlineStr"/>
       <c r="W422" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
         </is>
       </c>
       <c r="X422" t="n">
@@ -66829,41 +66829,41 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>JALAWA I</t>
+          <t>'YANDALLA II</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>19/43/13/003</t>
+          <t>19/43/14/005</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09c</t>
+          <t>6a35c3f587b1768452f7b180</t>
         </is>
       </c>
       <c r="L423" t="n">
-        <v>64755</v>
+        <v>64763</v>
       </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr">
         <is>
-          <t>1781976938520</t>
+          <t>1781968201933</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -66888,7 +66888,7 @@
       <c r="V423" t="inlineStr"/>
       <c r="W423" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
         </is>
       </c>
       <c r="X423" t="n">
@@ -66986,41 +66986,41 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>JALAWA II</t>
+          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>19/43/13/004</t>
+          <t>19/43/14/006</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09a</t>
+          <t>6a35c3f587b1768452f7b183</t>
         </is>
       </c>
       <c r="L424" t="n">
-        <v>64756</v>
+        <v>151226</v>
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr">
         <is>
-          <t>1781977012376</t>
+          <t>1781968195719</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -67045,7 +67045,7 @@
       <c r="V424" t="inlineStr"/>
       <c r="W424" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
         </is>
       </c>
       <c r="X424" t="n">
@@ -67143,41 +67143,41 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>WARAWA I</t>
+          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>19/43/13/005</t>
+          <t>19/43/14/007</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b099</t>
+          <t>6a35c3f587b1768452f7b182</t>
         </is>
       </c>
       <c r="L425" t="n">
-        <v>64757</v>
+        <v>151227</v>
       </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr">
         <is>
-          <t>1781977113973</t>
+          <t>1781974982952</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -67202,7 +67202,7 @@
       <c r="V425" t="inlineStr"/>
       <c r="W425" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
         </is>
       </c>
       <c r="X425" t="n">
@@ -67300,41 +67300,41 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>WARAWA II</t>
+          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>19/43/13/006</t>
+          <t>19/43/14/008</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09d</t>
+          <t>6a35c3f587b1768452f7b181</t>
         </is>
       </c>
       <c r="L426" t="n">
-        <v>64758</v>
+        <v>151228</v>
       </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
-          <t>1781976876830</t>
+          <t>1781968682952</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -67359,7 +67359,7 @@
       <c r="V426" t="inlineStr"/>
       <c r="W426" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
         </is>
       </c>
       <c r="X426" t="n">
@@ -67457,41 +67457,41 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
+          <t>ALIMAWA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>19/43/13/007</t>
+          <t>19/43/15/001</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09f</t>
+          <t>6a35c3f587b1768452f7b1fd</t>
         </is>
       </c>
       <c r="L427" t="n">
-        <v>151223</v>
+        <v>64764</v>
       </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr">
         <is>
-          <t>1781976882480</t>
+          <t>1781968165832</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -67516,7 +67516,7 @@
       <c r="V427" t="inlineStr"/>
       <c r="W427" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
         </is>
       </c>
       <c r="X427" t="n">
@@ -67614,72 +67614,66 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
+          <t>BUROMAWA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>19/43/13/008</t>
+          <t>19/43/15/002</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b0a0</t>
+          <t>6a35c3f587b1768452f7b1fc</t>
         </is>
       </c>
       <c r="L428" t="n">
-        <v>151224</v>
-      </c>
-      <c r="M428" t="n">
-        <v>1781968214959</v>
-      </c>
+        <v>64765</v>
+      </c>
+      <c r="M428" t="inlineStr"/>
       <c r="N428" t="inlineStr">
         <is>
-          <t>1781968212953</t>
+          <t>1781974266039</t>
         </is>
       </c>
       <c r="O428" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P428" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q428" t="n">
-        <v>3</v>
-      </c>
-      <c r="R428" t="inlineStr">
-        <is>
-          <t>6a36ad5552b6362accb5c7d0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R428" t="inlineStr"/>
       <c r="S428" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T428" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="U428" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V428" t="inlineStr"/>
       <c r="W428" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
         </is>
       </c>
       <c r="X428" t="n">
@@ -67698,7 +67692,7 @@
         <v>0</v>
       </c>
       <c r="AC428" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD428" t="n">
         <v>0</v>
@@ -67777,41 +67771,41 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
+          <t>GIWARAN ALITINI I</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>19/43/13/009</t>
+          <t>19/43/15/003</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09e</t>
+          <t>6a35c3f587b1768452f7b1fe</t>
         </is>
       </c>
       <c r="L429" t="n">
-        <v>151225</v>
+        <v>64766</v>
       </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr">
         <is>
-          <t>1781968282375</t>
+          <t>1781976840577</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -67836,7 +67830,7 @@
       <c r="V429" t="inlineStr"/>
       <c r="W429" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
         </is>
       </c>
       <c r="X429" t="n">
@@ -67934,41 +67928,41 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>GUMAKA</t>
+          <t>GIWARAN ALITINI II</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>19/43/14/001</t>
+          <t>19/43/15/004</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17e</t>
+          <t>6a35c3f587b1768452f7b1fb</t>
         </is>
       </c>
       <c r="L430" t="n">
-        <v>64759</v>
+        <v>64767</v>
       </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr">
         <is>
-          <t>1781975166154</t>
+          <t>1781968281024</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -67993,7 +67987,7 @@
       <c r="V430" t="inlineStr"/>
       <c r="W430" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
         </is>
       </c>
       <c r="X430" t="n">
@@ -68091,41 +68085,41 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>KANWA</t>
+          <t>GIWARAN JIJIYAWA I</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>19/43/14/002</t>
+          <t>19/43/15/005</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17c</t>
+          <t>6a35c3f587b1768452f7b1ff</t>
         </is>
       </c>
       <c r="L431" t="n">
-        <v>64760</v>
+        <v>64768</v>
       </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr">
         <is>
-          <t>1781974985005</t>
+          <t>1781974266070</t>
         </is>
       </c>
       <c r="O431" t="n">
@@ -68150,7 +68144,7 @@
       <c r="V431" t="inlineStr"/>
       <c r="W431" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
         </is>
       </c>
       <c r="X431" t="n">
@@ -68248,41 +68242,41 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>POLICE ACADEMY</t>
+          <t>GIWARAN JIJIYAWA II</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>19/43/14/003</t>
+          <t>19/43/15/006</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17d</t>
+          <t>6a35c3f587b1768452f7b200</t>
         </is>
       </c>
       <c r="L432" t="n">
-        <v>64761</v>
+        <v>64769</v>
       </c>
       <c r="M432" t="inlineStr"/>
       <c r="N432" t="inlineStr">
         <is>
-          <t>1781975165502</t>
+          <t>1781974447124</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -68307,7 +68301,7 @@
       <c r="V432" t="inlineStr"/>
       <c r="W432" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
         </is>
       </c>
       <c r="X432" t="n">
@@ -68405,41 +68399,41 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>'YANDALLA</t>
+          <t>'YANGIZO I</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>19/43/14/004</t>
+          <t>19/43/15/007</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17f</t>
+          <t>6a35c3f587b1768452f7b1f8</t>
         </is>
       </c>
       <c r="L433" t="n">
-        <v>64762</v>
+        <v>64770</v>
       </c>
       <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr">
         <is>
-          <t>1781975169663</t>
+          <t>1781974628327</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -68464,7 +68458,7 @@
       <c r="V433" t="inlineStr"/>
       <c r="W433" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
         </is>
       </c>
       <c r="X433" t="n">
@@ -68562,41 +68556,41 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>'YANDALLA II</t>
+          <t>'YANGIZO II</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>19/43/14/005</t>
+          <t>19/43/15/008</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b180</t>
+          <t>6a35c3f587b1768452f7b1f9</t>
         </is>
       </c>
       <c r="L434" t="n">
-        <v>64763</v>
+        <v>64771</v>
       </c>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr">
         <is>
-          <t>1781968201933</t>
+          <t>1781974630372</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -68621,7 +68615,7 @@
       <c r="V434" t="inlineStr"/>
       <c r="W434" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
         </is>
       </c>
       <c r="X434" t="n">
@@ -68719,41 +68713,41 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
+          <t>'YANGIZO III</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>19/43/14/006</t>
+          <t>19/43/15/009</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b183</t>
+          <t>6a35c3f587b1768452f7b1fa</t>
         </is>
       </c>
       <c r="L435" t="n">
-        <v>151226</v>
+        <v>64772</v>
       </c>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr">
         <is>
-          <t>1781968195719</t>
+          <t>1781968246493</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -68778,7 +68772,7 @@
       <c r="V435" t="inlineStr"/>
       <c r="W435" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
         </is>
       </c>
       <c r="X435" t="n">
@@ -68876,41 +68870,41 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
+          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>19/43/14/007</t>
+          <t>19/43/15/010</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b182</t>
+          <t>6a35c3f587b1768452f7b201</t>
         </is>
       </c>
       <c r="L436" t="n">
-        <v>151227</v>
+        <v>151229</v>
       </c>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr">
         <is>
-          <t>1781974982952</t>
+          <t>1781974627113</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -68935,7 +68929,7 @@
       <c r="V436" t="inlineStr"/>
       <c r="W436" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
         </is>
       </c>
       <c r="X436" t="n">
@@ -69002,1733 +68996,6 @@
         <v>0</v>
       </c>
       <c r="AS436" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>YAN DALLA</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
-        </is>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
-        </is>
-      </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>19/43/14/008</t>
-        </is>
-      </c>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b181</t>
-        </is>
-      </c>
-      <c r="L437" t="n">
-        <v>151228</v>
-      </c>
-      <c r="M437" t="inlineStr"/>
-      <c r="N437" t="inlineStr">
-        <is>
-          <t>1781968682952</t>
-        </is>
-      </c>
-      <c r="O437" t="n">
-        <v>0</v>
-      </c>
-      <c r="P437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
-      <c r="R437" t="inlineStr"/>
-      <c r="S437" t="n">
-        <v>0</v>
-      </c>
-      <c r="T437" t="n">
-        <v>0</v>
-      </c>
-      <c r="U437" t="n">
-        <v>0</v>
-      </c>
-      <c r="V437" t="inlineStr"/>
-      <c r="W437" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
-        </is>
-      </c>
-      <c r="X437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS437" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>ALIMAWA</t>
-        </is>
-      </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>19/43/15/001</t>
-        </is>
-      </c>
-      <c r="K438" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fd</t>
-        </is>
-      </c>
-      <c r="L438" t="n">
-        <v>64764</v>
-      </c>
-      <c r="M438" t="inlineStr"/>
-      <c r="N438" t="inlineStr">
-        <is>
-          <t>1781968165832</t>
-        </is>
-      </c>
-      <c r="O438" t="n">
-        <v>0</v>
-      </c>
-      <c r="P438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
-      <c r="R438" t="inlineStr"/>
-      <c r="S438" t="n">
-        <v>0</v>
-      </c>
-      <c r="T438" t="n">
-        <v>0</v>
-      </c>
-      <c r="U438" t="n">
-        <v>0</v>
-      </c>
-      <c r="V438" t="inlineStr"/>
-      <c r="W438" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
-        </is>
-      </c>
-      <c r="X438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS438" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>BUROMAWA</t>
-        </is>
-      </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>19/43/15/002</t>
-        </is>
-      </c>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fc</t>
-        </is>
-      </c>
-      <c r="L439" t="n">
-        <v>64765</v>
-      </c>
-      <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>1781974266039</t>
-        </is>
-      </c>
-      <c r="O439" t="n">
-        <v>0</v>
-      </c>
-      <c r="P439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q439" t="n">
-        <v>0</v>
-      </c>
-      <c r="R439" t="inlineStr"/>
-      <c r="S439" t="n">
-        <v>0</v>
-      </c>
-      <c r="T439" t="n">
-        <v>0</v>
-      </c>
-      <c r="U439" t="n">
-        <v>0</v>
-      </c>
-      <c r="V439" t="inlineStr"/>
-      <c r="W439" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
-        </is>
-      </c>
-      <c r="X439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS439" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>GIWARAN ALITINI I</t>
-        </is>
-      </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>19/43/15/003</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fe</t>
-        </is>
-      </c>
-      <c r="L440" t="n">
-        <v>64766</v>
-      </c>
-      <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr">
-        <is>
-          <t>1781976840577</t>
-        </is>
-      </c>
-      <c r="O440" t="n">
-        <v>0</v>
-      </c>
-      <c r="P440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
-      <c r="R440" t="inlineStr"/>
-      <c r="S440" t="n">
-        <v>0</v>
-      </c>
-      <c r="T440" t="n">
-        <v>0</v>
-      </c>
-      <c r="U440" t="n">
-        <v>0</v>
-      </c>
-      <c r="V440" t="inlineStr"/>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
-        </is>
-      </c>
-      <c r="X440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS440" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>GIWARAN ALITINI II</t>
-        </is>
-      </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>19/43/15/004</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fb</t>
-        </is>
-      </c>
-      <c r="L441" t="n">
-        <v>64767</v>
-      </c>
-      <c r="M441" t="inlineStr"/>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>1781968281024</t>
-        </is>
-      </c>
-      <c r="O441" t="n">
-        <v>0</v>
-      </c>
-      <c r="P441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
-      <c r="R441" t="inlineStr"/>
-      <c r="S441" t="n">
-        <v>0</v>
-      </c>
-      <c r="T441" t="n">
-        <v>0</v>
-      </c>
-      <c r="U441" t="n">
-        <v>0</v>
-      </c>
-      <c r="V441" t="inlineStr"/>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
-        </is>
-      </c>
-      <c r="X441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS441" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>GIWARAN JIJIYAWA I</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>19/43/15/005</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1ff</t>
-        </is>
-      </c>
-      <c r="L442" t="n">
-        <v>64768</v>
-      </c>
-      <c r="M442" t="inlineStr"/>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>1781974266070</t>
-        </is>
-      </c>
-      <c r="O442" t="n">
-        <v>0</v>
-      </c>
-      <c r="P442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
-      <c r="R442" t="inlineStr"/>
-      <c r="S442" t="n">
-        <v>0</v>
-      </c>
-      <c r="T442" t="n">
-        <v>0</v>
-      </c>
-      <c r="U442" t="n">
-        <v>0</v>
-      </c>
-      <c r="V442" t="inlineStr"/>
-      <c r="W442" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
-        </is>
-      </c>
-      <c r="X442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS442" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>GIWARAN JIJIYAWA II</t>
-        </is>
-      </c>
-      <c r="J443" t="inlineStr">
-        <is>
-          <t>19/43/15/006</t>
-        </is>
-      </c>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b200</t>
-        </is>
-      </c>
-      <c r="L443" t="n">
-        <v>64769</v>
-      </c>
-      <c r="M443" t="inlineStr"/>
-      <c r="N443" t="inlineStr">
-        <is>
-          <t>1781974447124</t>
-        </is>
-      </c>
-      <c r="O443" t="n">
-        <v>0</v>
-      </c>
-      <c r="P443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q443" t="n">
-        <v>0</v>
-      </c>
-      <c r="R443" t="inlineStr"/>
-      <c r="S443" t="n">
-        <v>0</v>
-      </c>
-      <c r="T443" t="n">
-        <v>0</v>
-      </c>
-      <c r="U443" t="n">
-        <v>0</v>
-      </c>
-      <c r="V443" t="inlineStr"/>
-      <c r="W443" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
-        </is>
-      </c>
-      <c r="X443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS443" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>'YANGIZO I</t>
-        </is>
-      </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>19/43/15/007</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1f8</t>
-        </is>
-      </c>
-      <c r="L444" t="n">
-        <v>64770</v>
-      </c>
-      <c r="M444" t="inlineStr"/>
-      <c r="N444" t="inlineStr">
-        <is>
-          <t>1781974628327</t>
-        </is>
-      </c>
-      <c r="O444" t="n">
-        <v>0</v>
-      </c>
-      <c r="P444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q444" t="n">
-        <v>0</v>
-      </c>
-      <c r="R444" t="inlineStr"/>
-      <c r="S444" t="n">
-        <v>0</v>
-      </c>
-      <c r="T444" t="n">
-        <v>0</v>
-      </c>
-      <c r="U444" t="n">
-        <v>0</v>
-      </c>
-      <c r="V444" t="inlineStr"/>
-      <c r="W444" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
-        </is>
-      </c>
-      <c r="X444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS444" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>'YANGIZO II</t>
-        </is>
-      </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>19/43/15/008</t>
-        </is>
-      </c>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1f9</t>
-        </is>
-      </c>
-      <c r="L445" t="n">
-        <v>64771</v>
-      </c>
-      <c r="M445" t="inlineStr"/>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>1781974630372</t>
-        </is>
-      </c>
-      <c r="O445" t="n">
-        <v>0</v>
-      </c>
-      <c r="P445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
-      <c r="R445" t="inlineStr"/>
-      <c r="S445" t="n">
-        <v>0</v>
-      </c>
-      <c r="T445" t="n">
-        <v>0</v>
-      </c>
-      <c r="U445" t="n">
-        <v>0</v>
-      </c>
-      <c r="V445" t="inlineStr"/>
-      <c r="W445" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
-        </is>
-      </c>
-      <c r="X445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS445" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>'YANGIZO III</t>
-        </is>
-      </c>
-      <c r="J446" t="inlineStr">
-        <is>
-          <t>19/43/15/009</t>
-        </is>
-      </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fa</t>
-        </is>
-      </c>
-      <c r="L446" t="n">
-        <v>64772</v>
-      </c>
-      <c r="M446" t="inlineStr"/>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>1781968246493</t>
-        </is>
-      </c>
-      <c r="O446" t="n">
-        <v>0</v>
-      </c>
-      <c r="P446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
-      <c r="R446" t="inlineStr"/>
-      <c r="S446" t="n">
-        <v>0</v>
-      </c>
-      <c r="T446" t="n">
-        <v>0</v>
-      </c>
-      <c r="U446" t="n">
-        <v>0</v>
-      </c>
-      <c r="V446" t="inlineStr"/>
-      <c r="W446" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
-        </is>
-      </c>
-      <c r="X446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS446" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
-        </is>
-      </c>
-      <c r="J447" t="inlineStr">
-        <is>
-          <t>19/43/15/010</t>
-        </is>
-      </c>
-      <c r="K447" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b201</t>
-        </is>
-      </c>
-      <c r="L447" t="n">
-        <v>151229</v>
-      </c>
-      <c r="M447" t="inlineStr"/>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>1781974627113</t>
-        </is>
-      </c>
-      <c r="O447" t="n">
-        <v>0</v>
-      </c>
-      <c r="P447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
-      <c r="R447" t="inlineStr"/>
-      <c r="S447" t="n">
-        <v>0</v>
-      </c>
-      <c r="T447" t="n">
-        <v>0</v>
-      </c>
-      <c r="U447" t="n">
-        <v>0</v>
-      </c>
-      <c r="V447" t="inlineStr"/>
-      <c r="W447" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
-        </is>
-      </c>
-      <c r="X447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS447" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70743,7 +69010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73241,26 +71508,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JEMAGU</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>500</v>
+        <v>434</v>
       </c>
       <c r="E23" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="H23" t="n">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="I23" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -73269,7 +71536,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -73278,13 +71545,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -73329,10 +71596,10 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH23" t="n">
         <v>100</v>
@@ -73351,26 +71618,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>434</v>
+        <v>235</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="H24" t="n">
-        <v>434</v>
+        <v>235</v>
       </c>
       <c r="I24" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -73388,13 +71655,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -73439,10 +71706,10 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
         <v>100</v>
@@ -73461,26 +71728,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -73498,7 +71765,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -73549,10 +71816,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>100</v>
@@ -73571,7 +71838,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -73659,10 +71926,10 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
         <v>100</v>
@@ -73681,7 +71948,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -73769,13 +72036,13 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28">
@@ -73791,26 +72058,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -73828,7 +72095,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -73879,13 +72146,13 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -73901,26 +72168,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -73938,7 +72205,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -73989,10 +72256,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH29" t="n">
         <v>100</v>
@@ -74011,7 +72278,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -74099,122 +72366,12 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH31" t="n">
         <v>100</v>
       </c>
     </row>
@@ -74516,22 +72673,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3131</v>
+        <v>2631</v>
       </c>
       <c r="D3" t="n">
-        <v>516</v>
+        <v>436</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="G3" t="n">
-        <v>3089</v>
+        <v>2614</v>
       </c>
       <c r="H3" t="n">
-        <v>508</v>
+        <v>428</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -74540,7 +72697,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -74549,7 +72706,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>503</v>
+        <v>425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -74600,13 +72757,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="AF3" t="n">
         <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>99.3</v>
+        <v>107.6</v>
       </c>
     </row>
   </sheetData>
@@ -74797,22 +72954,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7311</v>
+        <v>6811</v>
       </c>
       <c r="C2" t="n">
-        <v>984</v>
+        <v>904</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>965</v>
+        <v>885</v>
       </c>
       <c r="F2" t="n">
-        <v>7269</v>
+        <v>6794</v>
       </c>
       <c r="G2" t="n">
-        <v>958</v>
+        <v>878</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -74821,7 +72978,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -74830,7 +72987,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>949</v>
+        <v>871</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -74881,16 +73038,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AE2" t="n">
         <v>445</v>
       </c>
       <c r="AF2" t="n">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AG2" t="n">
-        <v>99.8</v>
+        <v>102.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS436"/>
+  <dimension ref="A1:AS447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55986,72 +55986,66 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>GADDIMA</t>
+          <t>GANITSURU I</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>19/43/07/001</t>
+          <t>19/43/06/001</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15d</t>
+          <t>6a35c3f587b1768452f7b167</t>
         </is>
       </c>
       <c r="L354" t="n">
-        <v>64698</v>
-      </c>
-      <c r="M354" t="n">
-        <v>1781976813192</v>
-      </c>
+        <v>64690</v>
+      </c>
+      <c r="M354" t="inlineStr"/>
       <c r="N354" t="inlineStr">
         <is>
-          <t>1781976812454</t>
+          <t>1781968257299</t>
         </is>
       </c>
       <c r="O354" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="P354" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="Q354" t="n">
-        <v>2</v>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t>6a36ceec370583337b6e6ff5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R354" t="inlineStr"/>
       <c r="S354" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="T354" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="U354" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64608/44430731-a4e5-42e1-8f84-2ced962019bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64600/3dd35025-7370-4a00-91d4-d6b4bba79957.jpg</t>
         </is>
       </c>
       <c r="X354" t="n">
@@ -56070,13 +56064,13 @@
         <v>0</v>
       </c>
       <c r="AC354" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AD354" t="n">
         <v>0</v>
       </c>
       <c r="AE354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF354" t="n">
         <v>0</v>
@@ -56149,41 +56143,41 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>JIGAWA I</t>
+          <t>GANITSURU II</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>19/43/07/002</t>
+          <t>19/43/06/002</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15c</t>
+          <t>6a35c3f587b1768452f7b166</t>
         </is>
       </c>
       <c r="L355" t="n">
-        <v>64699</v>
+        <v>64691</v>
       </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr">
         <is>
-          <t>1781968304168</t>
+          <t>1781968317384</t>
         </is>
       </c>
       <c r="O355" t="n">
@@ -56208,7 +56202,7 @@
       <c r="V355" t="inlineStr"/>
       <c r="W355" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64609/d046c66d-ebc1-4a60-98e7-f9827cfc2ef2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64601/dba23b61-e372-4b61-be80-463edb25a272.jpg</t>
         </is>
       </c>
       <c r="X355" t="n">
@@ -56306,41 +56300,41 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>JIGAWA II</t>
+          <t>JEMAGU I</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>19/43/07/003</t>
+          <t>19/43/06/003</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15a</t>
+          <t>6a35c3f587b1768452f7b168</t>
         </is>
       </c>
       <c r="L356" t="n">
-        <v>64700</v>
+        <v>64692</v>
       </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr">
         <is>
-          <t>1781968209595</t>
+          <t>1781968155932</t>
         </is>
       </c>
       <c r="O356" t="n">
@@ -56365,7 +56359,7 @@
       <c r="V356" t="inlineStr"/>
       <c r="W356" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64610/50dc8996-3d84-4192-a526-ee3ff7ed2c73.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64602/4ce5d013-2f71-43b8-bca9-cffb6003b606.jpg</t>
         </is>
       </c>
       <c r="X356" t="n">
@@ -56463,41 +56457,41 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>LITAU/GANJIKAR</t>
+          <t>JEMAGU II</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>19/43/07/004</t>
+          <t>19/43/06/004</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15f</t>
+          <t>6a35c3f587b1768452f7b163</t>
         </is>
       </c>
       <c r="L357" t="n">
-        <v>64701</v>
+        <v>64693</v>
       </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="inlineStr">
         <is>
-          <t>1781976960124</t>
+          <t>1781968147780</t>
         </is>
       </c>
       <c r="O357" t="n">
@@ -56522,7 +56516,7 @@
       <c r="V357" t="inlineStr"/>
       <c r="W357" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64611/9942f58a-bf41-4ed6-8c3a-bc940b3a00e3.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64603/886832e3-7ccd-4f4c-9fc1-eb72bcc94b02.jpg</t>
         </is>
       </c>
       <c r="X357" t="n">
@@ -56620,66 +56614,72 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>MAJAWA</t>
+          <t>MABOYI</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>19/43/07/005</t>
+          <t>19/43/06/005</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b159</t>
+          <t>6a35c3f587b1768452f7b169</t>
         </is>
       </c>
       <c r="L358" t="n">
-        <v>64702</v>
-      </c>
-      <c r="M358" t="inlineStr"/>
+        <v>64694</v>
+      </c>
+      <c r="M358" t="n">
+        <v>1781969403093</v>
+      </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>1781968167636</t>
+          <t>1781969402549</t>
         </is>
       </c>
       <c r="O358" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P358" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q358" t="n">
         <v>0</v>
       </c>
-      <c r="R358" t="inlineStr"/>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>6a36b1fa52b6362accb5cc1a</t>
+        </is>
+      </c>
       <c r="S358" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T358" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="U358" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64612/e7a586fe-7050-4813-b4d2-f5eaecb5159e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64604/ebef9e29-9513-4269-8a4d-0564c370edd3.jpg</t>
         </is>
       </c>
       <c r="X358" t="n">
@@ -56689,7 +56689,7 @@
         <v>0</v>
       </c>
       <c r="Z358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA358" t="n">
         <v>0</v>
@@ -56698,7 +56698,7 @@
         <v>0</v>
       </c>
       <c r="AC358" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AD358" t="n">
         <v>0</v>
@@ -56777,41 +56777,41 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>MARAYA NAIRA</t>
+          <t>MAKERA I</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>19/43/07/006</t>
+          <t>19/43/06/006</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15b</t>
+          <t>6a35c3f587b1768452f7b162</t>
         </is>
       </c>
       <c r="L359" t="n">
-        <v>64703</v>
+        <v>64695</v>
       </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr">
         <is>
-          <t>1781972284783</t>
+          <t>1781968270426</t>
         </is>
       </c>
       <c r="O359" t="n">
@@ -56836,7 +56836,7 @@
       <c r="V359" t="inlineStr"/>
       <c r="W359" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64613/bbf2dd97-9e62-4b41-a7bb-d2e629535220.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64605/80844424-5323-4c0e-9062-adb699cb7808.jpg</t>
         </is>
       </c>
       <c r="X359" t="n">
@@ -56934,41 +56934,41 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>TOKEN</t>
+          <t>MAKERA II</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>19/43/07/007</t>
+          <t>19/43/06/007</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b15e</t>
+          <t>6a35c3f587b1768452f7b165</t>
         </is>
       </c>
       <c r="L360" t="n">
-        <v>64704</v>
+        <v>64696</v>
       </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr">
         <is>
-          <t>1781968288114</t>
+          <t>1781968273952</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -56993,7 +56993,7 @@
       <c r="V360" t="inlineStr"/>
       <c r="W360" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64614/4af81029-93ec-4bfd-a4b7-a90eee1404cd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64606/b8d4919f-e5db-4ea0-ad8c-49f7aa931e7c.jpg</t>
         </is>
       </c>
       <c r="X360" t="n">
@@ -57091,41 +57091,41 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>AMANA CITY ISLAMIYYA</t>
+          <t>YANLANYA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>19/43/07/008</t>
+          <t>19/43/06/008</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b161</t>
+          <t>6a35c3f587b1768452f7b164</t>
         </is>
       </c>
       <c r="L361" t="n">
-        <v>151210</v>
+        <v>64697</v>
       </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="inlineStr">
         <is>
-          <t>1781968151237</t>
+          <t>1781968253472</t>
         </is>
       </c>
       <c r="O361" t="n">
@@ -57150,7 +57150,7 @@
       <c r="V361" t="inlineStr"/>
       <c r="W361" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646500/bd4fbb32-460e-4132-89d2-d0a592e696f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/64607/947286d9-4867-4d4c-a220-142dfa94017b.jpg</t>
         </is>
       </c>
       <c r="X361" t="n">
@@ -57248,41 +57248,41 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00a</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>LARABAR GADAR SARKI ISLAMIYYA</t>
+          <t>JEMAGU PRIMARY SCHOOL III</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>19/43/07/009</t>
+          <t>19/43/06/009</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b160</t>
+          <t>6a35c3f587b1768452f7b16c</t>
         </is>
       </c>
       <c r="L362" t="n">
-        <v>151211</v>
+        <v>151207</v>
       </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr">
         <is>
-          <t>1781968248486</t>
+          <t>1781970842335</t>
         </is>
       </c>
       <c r="O362" t="n">
@@ -57307,7 +57307,7 @@
       <c r="V362" t="inlineStr"/>
       <c r="W362" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646501/0328a449-5fac-4c4f-8ed4-04eb4435266b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646497/6e783e9c-36aa-4f09-8d51-aeaaa1873f50.jpg</t>
         </is>
       </c>
       <c r="X362" t="n">
@@ -57405,41 +57405,41 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>DANHAWAGIWA</t>
+          <t>JEMAGU PRIMARY SCHOOL IV</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>19/43/09/001</t>
+          <t>19/43/06/010</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b213</t>
+          <t>6a35c3f587b1768452f7b16a</t>
         </is>
       </c>
       <c r="L363" t="n">
-        <v>64714</v>
+        <v>151208</v>
       </c>
       <c r="M363" t="inlineStr"/>
       <c r="N363" t="inlineStr">
         <is>
-          <t>1781970484687</t>
+          <t>1781968176573</t>
         </is>
       </c>
       <c r="O363" t="n">
@@ -57464,7 +57464,7 @@
       <c r="V363" t="inlineStr"/>
       <c r="W363" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646498/2225d4e0-1127-41c6-be0e-0b9fa30dc617.jpg</t>
         </is>
       </c>
       <c r="X363" t="n">
@@ -57562,41 +57562,41 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>06</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf18f77bb3acad0a009</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA I</t>
+          <t>MAKERA PRIMARY SCHOOL III</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>19/43/09/002</t>
+          <t>19/43/06/011</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b215</t>
+          <t>6a35c3f587b1768452f7b16b</t>
         </is>
       </c>
       <c r="L364" t="n">
-        <v>64715</v>
+        <v>151209</v>
       </c>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr">
         <is>
-          <t>1781970664668</t>
+          <t>1781968172505</t>
         </is>
       </c>
       <c r="O364" t="n">
@@ -57621,7 +57621,7 @@
       <c r="V364" t="inlineStr"/>
       <c r="W364" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4721/646499/3213bc97-0f45-46d7-809a-47e8c6db7a24.jpg</t>
         </is>
       </c>
       <c r="X364" t="n">
@@ -57719,72 +57719,72 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA II</t>
+          <t>GADDIMA</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>19/43/09/003</t>
+          <t>19/43/07/001</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b217</t>
+          <t>6a35c3f587b1768452f7b15d</t>
         </is>
       </c>
       <c r="L365" t="n">
-        <v>64716</v>
+        <v>64698</v>
       </c>
       <c r="M365" t="n">
-        <v>1781969584429</v>
+        <v>1781976813192</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>1781969583795</t>
+          <t>1781976812454</t>
         </is>
       </c>
       <c r="O365" t="n">
-        <v>235</v>
+        <v>434</v>
       </c>
       <c r="P365" t="n">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="Q365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>6a36b2af52b6362accb5cc50</t>
+          <t>6a36ceec370583337b6e6ff5</t>
         </is>
       </c>
       <c r="S365" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="T365" t="n">
-        <v>235</v>
+        <v>434</v>
       </c>
       <c r="U365" t="n">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64608/44430731-a4e5-42e1-8f84-2ced962019bd.jpg</t>
         </is>
       </c>
       <c r="X365" t="n">
@@ -57803,13 +57803,13 @@
         <v>0</v>
       </c>
       <c r="AC365" t="n">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="AD365" t="n">
         <v>0</v>
       </c>
       <c r="AE365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF365" t="n">
         <v>0</v>
@@ -57882,41 +57882,41 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA I</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>19/43/09/004</t>
+          <t>19/43/07/002</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b210</t>
+          <t>6a35c3f587b1768452f7b15c</t>
         </is>
       </c>
       <c r="L366" t="n">
-        <v>64717</v>
+        <v>64699</v>
       </c>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="inlineStr">
         <is>
-          <t>1781976885564</t>
+          <t>1781968304168</t>
         </is>
       </c>
       <c r="O366" t="n">
@@ -57941,7 +57941,7 @@
       <c r="V366" t="inlineStr"/>
       <c r="W366" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64609/d046c66d-ebc1-4a60-98e7-f9827cfc2ef2.jpg</t>
         </is>
       </c>
       <c r="X366" t="n">
@@ -58039,41 +58039,41 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>KINCHAU</t>
+          <t>JIGAWA II</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>19/43/09/005</t>
+          <t>19/43/07/003</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b212</t>
+          <t>6a35c3f587b1768452f7b15a</t>
         </is>
       </c>
       <c r="L367" t="n">
-        <v>64718</v>
+        <v>64700</v>
       </c>
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="inlineStr">
         <is>
-          <t>1781976801113</t>
+          <t>1781968209595</t>
         </is>
       </c>
       <c r="O367" t="n">
@@ -58098,7 +58098,7 @@
       <c r="V367" t="inlineStr"/>
       <c r="W367" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64610/50dc8996-3d84-4192-a526-ee3ff7ed2c73.jpg</t>
         </is>
       </c>
       <c r="X367" t="n">
@@ -58196,41 +58196,41 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>NAIRA</t>
+          <t>LITAU/GANJIKAR</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>19/43/09/006</t>
+          <t>19/43/07/004</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b214</t>
+          <t>6a35c3f587b1768452f7b15f</t>
         </is>
       </c>
       <c r="L368" t="n">
-        <v>64719</v>
+        <v>64701</v>
       </c>
       <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr">
         <is>
-          <t>1781976797855</t>
+          <t>1781976960124</t>
         </is>
       </c>
       <c r="O368" t="n">
@@ -58255,7 +58255,7 @@
       <c r="V368" t="inlineStr"/>
       <c r="W368" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64611/9942f58a-bf41-4ed6-8c3a-bc940b3a00e3.jpg</t>
         </is>
       </c>
       <c r="X368" t="n">
@@ -58353,41 +58353,41 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>TURBA</t>
+          <t>MAJAWA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>19/43/09/007</t>
+          <t>19/43/07/005</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b211</t>
+          <t>6a35c3f587b1768452f7b159</t>
         </is>
       </c>
       <c r="L369" t="n">
-        <v>64720</v>
+        <v>64702</v>
       </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr">
         <is>
-          <t>1781970126235</t>
+          <t>1781968167636</t>
         </is>
       </c>
       <c r="O369" t="n">
@@ -58412,7 +58412,7 @@
       <c r="V369" t="inlineStr"/>
       <c r="W369" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64612/e7a586fe-7050-4813-b4d2-f5eaecb5159e.jpg</t>
         </is>
       </c>
       <c r="X369" t="n">
@@ -58510,41 +58510,41 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>WALAGIGI</t>
+          <t>MARAYA NAIRA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>19/43/09/008</t>
+          <t>19/43/07/006</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b216</t>
+          <t>6a35c3f587b1768452f7b15b</t>
         </is>
       </c>
       <c r="L370" t="n">
-        <v>64721</v>
+        <v>64703</v>
       </c>
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr">
         <is>
-          <t>1781973924024</t>
+          <t>1781972284783</t>
         </is>
       </c>
       <c r="O370" t="n">
@@ -58569,7 +58569,7 @@
       <c r="V370" t="inlineStr"/>
       <c r="W370" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64613/bbf2dd97-9e62-4b41-a7bb-d2e629535220.jpg</t>
         </is>
       </c>
       <c r="X370" t="n">
@@ -58667,41 +58667,41 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
+          <t>TOKEN</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>19/43/09/009</t>
+          <t>19/43/07/007</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b219</t>
+          <t>6a35c3f587b1768452f7b15e</t>
         </is>
       </c>
       <c r="L371" t="n">
-        <v>151215</v>
+        <v>64704</v>
       </c>
       <c r="M371" t="inlineStr"/>
       <c r="N371" t="inlineStr">
         <is>
-          <t>1781976919845</t>
+          <t>1781968288114</t>
         </is>
       </c>
       <c r="O371" t="n">
@@ -58726,7 +58726,7 @@
       <c r="V371" t="inlineStr"/>
       <c r="W371" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/64614/4af81029-93ec-4bfd-a4b7-a90eee1404cd.jpg</t>
         </is>
       </c>
       <c r="X371" t="n">
@@ -58824,41 +58824,41 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
+          <t>AMANA CITY ISLAMIYYA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>19/43/09/010</t>
+          <t>19/43/07/008</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b218</t>
+          <t>6a35c3f587b1768452f7b161</t>
         </is>
       </c>
       <c r="L372" t="n">
-        <v>151216</v>
+        <v>151210</v>
       </c>
       <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr">
         <is>
-          <t>1781973731518</t>
+          <t>1781968151237</t>
         </is>
       </c>
       <c r="O372" t="n">
@@ -58883,7 +58883,7 @@
       <c r="V372" t="inlineStr"/>
       <c r="W372" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646500/bd4fbb32-460e-4132-89d2-d0a592e696f7.jpg</t>
         </is>
       </c>
       <c r="X372" t="n">
@@ -58981,41 +58981,41 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>07</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00a</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
+          <t>LARABAR GADAR SARKI ISLAMIYYA</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>19/43/09/011</t>
+          <t>19/43/07/009</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21a</t>
+          <t>6a35c3f587b1768452f7b160</t>
         </is>
       </c>
       <c r="L373" t="n">
-        <v>151217</v>
+        <v>151211</v>
       </c>
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr">
         <is>
-          <t>1781977138945</t>
+          <t>1781968248486</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -59040,7 +59040,7 @@
       <c r="V373" t="inlineStr"/>
       <c r="W373" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4722/646501/0328a449-5fac-4c4f-8ed4-04eb4435266b.jpg</t>
         </is>
       </c>
       <c r="X373" t="n">
@@ -59138,41 +59138,41 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>GANAKAKUN I</t>
+          <t>DANHAWAGIWA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>19/43/10/001</t>
+          <t>19/43/09/001</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cf</t>
+          <t>6a35c3f587b1768452f7b213</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>64722</v>
+        <v>64714</v>
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr">
         <is>
-          <t>1781968221436</t>
+          <t>1781970484687</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -59197,7 +59197,7 @@
       <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
         </is>
       </c>
       <c r="X374" t="n">
@@ -59295,41 +59295,41 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>GANAKAKUN II</t>
+          <t>GISHIRI WUYA I</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>19/43/10/002</t>
+          <t>19/43/09/002</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ce</t>
+          <t>6a35c3f587b1768452f7b215</t>
         </is>
       </c>
       <c r="L375" t="n">
-        <v>64723</v>
+        <v>64715</v>
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr">
         <is>
-          <t>1781968244797</t>
+          <t>1781970664668</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -59354,7 +59354,7 @@
       <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
         </is>
       </c>
       <c r="X375" t="n">
@@ -59452,66 +59452,72 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>MADARIN MABA I</t>
+          <t>GISHIRI WUYA II</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>19/43/10/003</t>
+          <t>19/43/09/003</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d3</t>
+          <t>6a35c3f587b1768452f7b217</t>
         </is>
       </c>
       <c r="L376" t="n">
-        <v>64724</v>
-      </c>
-      <c r="M376" t="inlineStr"/>
+        <v>64716</v>
+      </c>
+      <c r="M376" t="n">
+        <v>1781969584429</v>
+      </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>1781968265095</t>
+          <t>1781969583795</t>
         </is>
       </c>
       <c r="O376" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="P376" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q376" t="n">
         <v>0</v>
       </c>
-      <c r="R376" t="inlineStr"/>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>6a36b2af52b6362accb5cc50</t>
+        </is>
+      </c>
       <c r="S376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="T376" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="U376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
         </is>
       </c>
       <c r="X376" t="n">
@@ -59530,7 +59536,7 @@
         <v>0</v>
       </c>
       <c r="AC376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD376" t="n">
         <v>0</v>
@@ -59609,41 +59615,41 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>MADARIN MABA II</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>19/43/10/004</t>
+          <t>19/43/09/004</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d0</t>
+          <t>6a35c3f587b1768452f7b210</t>
         </is>
       </c>
       <c r="L377" t="n">
-        <v>64725</v>
+        <v>64717</v>
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
-          <t>1781971564529</t>
+          <t>1781976885564</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -59668,7 +59674,7 @@
       <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
         </is>
       </c>
       <c r="X377" t="n">
@@ -59766,41 +59772,41 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>MADARIN MABA III</t>
+          <t>KINCHAU</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>19/43/10/005</t>
+          <t>19/43/09/005</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d2</t>
+          <t>6a35c3f587b1768452f7b212</t>
         </is>
       </c>
       <c r="L378" t="n">
-        <v>64726</v>
+        <v>64718</v>
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
-          <t>1781971929292</t>
+          <t>1781976801113</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -59825,7 +59831,7 @@
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
         </is>
       </c>
       <c r="X378" t="n">
@@ -59923,41 +59929,41 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>MARAYAR WUTA</t>
+          <t>NAIRA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>19/43/10/006</t>
+          <t>19/43/09/006</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cd</t>
+          <t>6a35c3f587b1768452f7b214</t>
         </is>
       </c>
       <c r="L379" t="n">
-        <v>64727</v>
+        <v>64719</v>
       </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
-          <t>1781971930377</t>
+          <t>1781976797855</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -59982,7 +59988,7 @@
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
         </is>
       </c>
       <c r="X379" t="n">
@@ -60080,41 +60086,41 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>SABON GARIN NASARA</t>
+          <t>TURBA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>19/43/10/007</t>
+          <t>19/43/09/007</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cc</t>
+          <t>6a35c3f587b1768452f7b211</t>
         </is>
       </c>
       <c r="L380" t="n">
-        <v>64728</v>
+        <v>64720</v>
       </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
-          <t>1781971922925</t>
+          <t>1781970126235</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -60139,7 +60145,7 @@
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
         </is>
       </c>
       <c r="X380" t="n">
@@ -60237,41 +60243,41 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>TALAWA</t>
+          <t>WALAGIGI</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>19/43/10/008</t>
+          <t>19/43/09/008</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d1</t>
+          <t>6a35c3f587b1768452f7b216</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>64729</v>
+        <v>64721</v>
       </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
-          <t>1781968262106</t>
+          <t>1781973924024</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -60296,7 +60302,7 @@
       <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
         </is>
       </c>
       <c r="X381" t="n">
@@ -60394,41 +60400,41 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19/43/10/009</t>
+          <t>19/43/09/009</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d5</t>
+          <t>6a35c3f587b1768452f7b219</t>
         </is>
       </c>
       <c r="L382" t="n">
-        <v>151218</v>
+        <v>151215</v>
       </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
-          <t>1781972103434</t>
+          <t>1781976919845</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -60453,7 +60459,7 @@
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
         </is>
       </c>
       <c r="X382" t="n">
@@ -60551,41 +60557,41 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19/43/10/010</t>
+          <t>19/43/09/010</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d4</t>
+          <t>6a35c3f587b1768452f7b218</t>
         </is>
       </c>
       <c r="L383" t="n">
-        <v>151219</v>
+        <v>151216</v>
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr">
         <is>
-          <t>1781972285399</t>
+          <t>1781973731518</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -60610,7 +60616,7 @@
       <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
         </is>
       </c>
       <c r="X383" t="n">
@@ -60708,41 +60714,41 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>FARTAWA</t>
+          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19/43/11/001</t>
+          <t>19/43/09/011</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21c</t>
+          <t>6a35c3f587b1768452f7b21a</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>64730</v>
+        <v>151217</v>
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr">
         <is>
-          <t>1781977074928</t>
+          <t>1781977138945</t>
         </is>
       </c>
       <c r="O384" t="n">
@@ -60767,7 +60773,7 @@
       <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
         </is>
       </c>
       <c r="X384" t="n">
@@ -60865,41 +60871,41 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS I</t>
+          <t>GANAKAKUN I</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>19/43/11/002</t>
+          <t>19/43/10/001</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b223</t>
+          <t>6a35c3f587b1768452f7b1cf</t>
         </is>
       </c>
       <c r="L385" t="n">
-        <v>64731</v>
+        <v>64722</v>
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr">
         <is>
-          <t>1781977113305</t>
+          <t>1781968221436</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -60924,7 +60930,7 @@
       <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
         </is>
       </c>
       <c r="X385" t="n">
@@ -61022,41 +61028,41 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS II</t>
+          <t>GANAKAKUN II</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19/43/11/003</t>
+          <t>19/43/10/002</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21b</t>
+          <t>6a35c3f587b1768452f7b1ce</t>
         </is>
       </c>
       <c r="L386" t="n">
-        <v>64732</v>
+        <v>64723</v>
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr">
         <is>
-          <t>1781977075062</t>
+          <t>1781968244797</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -61081,7 +61087,7 @@
       <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
         </is>
       </c>
       <c r="X386" t="n">
@@ -61179,41 +61185,41 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>UNGUWAR ZURURU</t>
+          <t>MADARIN MABA I</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19/43/11/004</t>
+          <t>19/43/10/003</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b222</t>
+          <t>6a35c3f587b1768452f7b1d3</t>
         </is>
       </c>
       <c r="L387" t="n">
-        <v>64733</v>
+        <v>64724</v>
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr">
         <is>
-          <t>1781975346942</t>
+          <t>1781968265095</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -61238,7 +61244,7 @@
       <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
         </is>
       </c>
       <c r="X387" t="n">
@@ -61336,41 +61342,41 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>YANDADI I</t>
+          <t>MADARIN MABA II</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19/43/11/005</t>
+          <t>19/43/10/004</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b221</t>
+          <t>6a35c3f587b1768452f7b1d0</t>
         </is>
       </c>
       <c r="L388" t="n">
-        <v>64734</v>
+        <v>64725</v>
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr">
         <is>
-          <t>1781975887400</t>
+          <t>1781971564529</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -61395,7 +61401,7 @@
       <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
         </is>
       </c>
       <c r="X388" t="n">
@@ -61493,41 +61499,41 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>YANDADI II</t>
+          <t>MADARIN MABA III</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>19/43/11/006</t>
+          <t>19/43/10/005</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21e</t>
+          <t>6a35c3f587b1768452f7b1d2</t>
         </is>
       </c>
       <c r="L389" t="n">
-        <v>64735</v>
+        <v>64726</v>
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr">
         <is>
-          <t>1782131641877</t>
+          <t>1781971929292</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -61552,7 +61558,7 @@
       <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
         </is>
       </c>
       <c r="X389" t="n">
@@ -61650,41 +61656,41 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>YADAUDU I</t>
+          <t>MARAYAR WUTA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19/43/11/007</t>
+          <t>19/43/10/006</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b220</t>
+          <t>6a35c3f587b1768452f7b1cd</t>
         </is>
       </c>
       <c r="L390" t="n">
-        <v>64736</v>
+        <v>64727</v>
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr">
         <is>
-          <t>1781989191145</t>
+          <t>1781971930377</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -61709,7 +61715,7 @@
       <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
         </is>
       </c>
       <c r="X390" t="n">
@@ -61807,41 +61813,41 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>YADAUDU II</t>
+          <t>SABON GARIN NASARA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19/43/11/008</t>
+          <t>19/43/10/007</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21f</t>
+          <t>6a35c3f587b1768452f7b1cc</t>
         </is>
       </c>
       <c r="L391" t="n">
-        <v>64737</v>
+        <v>64728</v>
       </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr">
         <is>
-          <t>1781976878903</t>
+          <t>1781971922925</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -61866,7 +61872,7 @@
       <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
         </is>
       </c>
       <c r="X391" t="n">
@@ -61964,41 +61970,41 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>ZANGO DANMARKE</t>
+          <t>TALAWA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19/43/11/009</t>
+          <t>19/43/10/008</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21d</t>
+          <t>6a35c3f587b1768452f7b1d1</t>
         </is>
       </c>
       <c r="L392" t="n">
-        <v>64738</v>
+        <v>64729</v>
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
         <is>
-          <t>1781976780359</t>
+          <t>1781968262106</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -62023,7 +62029,7 @@
       <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
         </is>
       </c>
       <c r="X392" t="n">
@@ -62121,41 +62127,41 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
+          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>19/43/11/010</t>
+          <t>19/43/10/009</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b224</t>
+          <t>6a35c3f587b1768452f7b1d5</t>
         </is>
       </c>
       <c r="L393" t="n">
-        <v>151220</v>
+        <v>151218</v>
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr">
         <is>
-          <t>1781977094685</t>
+          <t>1781972103434</t>
         </is>
       </c>
       <c r="O393" t="n">
@@ -62180,7 +62186,7 @@
       <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
         </is>
       </c>
       <c r="X393" t="n">
@@ -62278,41 +62284,41 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
+          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>19/43/11/011</t>
+          <t>19/43/10/010</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b225</t>
+          <t>6a35c3f587b1768452f7b1d4</t>
         </is>
       </c>
       <c r="L394" t="n">
-        <v>151221</v>
+        <v>151219</v>
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
         <is>
-          <t>1781976782683</t>
+          <t>1781972285399</t>
         </is>
       </c>
       <c r="O394" t="n">
@@ -62337,7 +62343,7 @@
       <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
         </is>
       </c>
       <c r="X394" t="n">
@@ -62435,41 +62441,41 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>CHARKA</t>
+          <t>FARTAWA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19/43/12/001</t>
+          <t>19/43/11/001</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b171</t>
+          <t>6a35c3f587b1768452f7b21c</t>
         </is>
       </c>
       <c r="L395" t="n">
-        <v>64739</v>
+        <v>64730</v>
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
         <is>
-          <t>1781976872268</t>
+          <t>1781977074928</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -62494,7 +62500,7 @@
       <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
         </is>
       </c>
       <c r="X395" t="n">
@@ -62592,41 +62598,41 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>DANFARI I</t>
+          <t>TAMBURAWAR GABAS I</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19/43/12/002</t>
+          <t>19/43/11/002</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16d</t>
+          <t>6a35c3f587b1768452f7b223</t>
         </is>
       </c>
       <c r="L396" t="n">
-        <v>64740</v>
+        <v>64731</v>
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr">
         <is>
-          <t>1781976901500</t>
+          <t>1781977113305</t>
         </is>
       </c>
       <c r="O396" t="n">
@@ -62651,7 +62657,7 @@
       <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
         </is>
       </c>
       <c r="X396" t="n">
@@ -62749,41 +62755,41 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>DANFARI II</t>
+          <t>TAMBURAWAR GABAS II</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>19/43/12/003</t>
+          <t>19/43/11/003</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b175</t>
+          <t>6a35c3f587b1768452f7b21b</t>
         </is>
       </c>
       <c r="L397" t="n">
-        <v>64741</v>
+        <v>64732</v>
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr">
         <is>
-          <t>1781968309565</t>
+          <t>1781977075062</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -62808,7 +62814,7 @@
       <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
         </is>
       </c>
       <c r="X397" t="n">
@@ -62906,41 +62912,41 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>DANTSAWA</t>
+          <t>UNGUWAR ZURURU</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>19/43/12/004</t>
+          <t>19/43/11/004</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b170</t>
+          <t>6a35c3f587b1768452f7b222</t>
         </is>
       </c>
       <c r="L398" t="n">
-        <v>64742</v>
+        <v>64733</v>
       </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr">
         <is>
-          <t>1781968186810</t>
+          <t>1781975346942</t>
         </is>
       </c>
       <c r="O398" t="n">
@@ -62965,7 +62971,7 @@
       <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
         </is>
       </c>
       <c r="X398" t="n">
@@ -63063,41 +63069,41 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>HALADAWA</t>
+          <t>YANDADI I</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19/43/12/005</t>
+          <t>19/43/11/005</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b179</t>
+          <t>6a35c3f587b1768452f7b221</t>
         </is>
       </c>
       <c r="L399" t="n">
-        <v>64743</v>
+        <v>64734</v>
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr">
         <is>
-          <t>1781976861221</t>
+          <t>1781975887400</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -63122,7 +63128,7 @@
       <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
         </is>
       </c>
       <c r="X399" t="n">
@@ -63220,41 +63226,41 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>HAYIN WAZO</t>
+          <t>YANDADI II</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>19/43/12/006</t>
+          <t>19/43/11/006</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16f</t>
+          <t>6a35c3f587b1768452f7b21e</t>
         </is>
       </c>
       <c r="L400" t="n">
-        <v>64744</v>
+        <v>64735</v>
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr">
         <is>
-          <t>1781976900341</t>
+          <t>1782131641877</t>
         </is>
       </c>
       <c r="O400" t="n">
@@ -63279,7 +63285,7 @@
       <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
         </is>
       </c>
       <c r="X400" t="n">
@@ -63377,41 +63383,41 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>JILAWA</t>
+          <t>YADAUDU I</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19/43/12/007</t>
+          <t>19/43/11/007</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b174</t>
+          <t>6a35c3f587b1768452f7b220</t>
         </is>
       </c>
       <c r="L401" t="n">
-        <v>64745</v>
+        <v>64736</v>
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr">
         <is>
-          <t>1781968169241</t>
+          <t>1781989191145</t>
         </is>
       </c>
       <c r="O401" t="n">
@@ -63436,7 +63442,7 @@
       <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
         </is>
       </c>
       <c r="X401" t="n">
@@ -63534,41 +63540,41 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>KARGAWA</t>
+          <t>YADAUDU II</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19/43/12/008</t>
+          <t>19/43/11/008</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17a</t>
+          <t>6a35c3f587b1768452f7b21f</t>
         </is>
       </c>
       <c r="L402" t="n">
-        <v>64746</v>
+        <v>64737</v>
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr">
         <is>
-          <t>1781976889527</t>
+          <t>1781976878903</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -63593,7 +63599,7 @@
       <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
         </is>
       </c>
       <c r="X402" t="n">
@@ -63691,41 +63697,41 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>MARAYAR ROGO</t>
+          <t>ZANGO DANMARKE</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19/43/12/009</t>
+          <t>19/43/11/009</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b178</t>
+          <t>6a35c3f587b1768452f7b21d</t>
         </is>
       </c>
       <c r="L403" t="n">
-        <v>64747</v>
+        <v>64738</v>
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr">
         <is>
-          <t>1781976782857</t>
+          <t>1781976780359</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -63750,7 +63756,7 @@
       <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
         </is>
       </c>
       <c r="X403" t="n">
@@ -63848,41 +63854,41 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>RIGAR GABAS</t>
+          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19/43/12/010</t>
+          <t>19/43/11/010</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b177</t>
+          <t>6a35c3f587b1768452f7b224</t>
         </is>
       </c>
       <c r="L404" t="n">
-        <v>64748</v>
+        <v>151220</v>
       </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr">
         <is>
-          <t>1781968289759</t>
+          <t>1781977094685</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -63907,7 +63913,7 @@
       <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
         </is>
       </c>
       <c r="X404" t="n">
@@ -64005,41 +64011,41 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>TANAGAR I</t>
+          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19/43/12/011</t>
+          <t>19/43/11/011</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b173</t>
+          <t>6a35c3f587b1768452f7b225</t>
         </is>
       </c>
       <c r="L405" t="n">
-        <v>64749</v>
+        <v>151221</v>
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr">
         <is>
-          <t>1781976813571</t>
+          <t>1781976782683</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -64064,7 +64070,7 @@
       <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
         </is>
       </c>
       <c r="X405" t="n">
@@ -64177,26 +64183,26 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>TANAGAR II</t>
+          <t>CHARKA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>19/43/12/012</t>
+          <t>19/43/12/001</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b172</t>
+          <t>6a35c3f587b1768452f7b171</t>
         </is>
       </c>
       <c r="L406" t="n">
-        <v>64750</v>
+        <v>64739</v>
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
-          <t>1781976798491</t>
+          <t>1781976872268</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -64221,7 +64227,7 @@
       <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
         </is>
       </c>
       <c r="X406" t="n">
@@ -64334,24 +64340,28 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>WARKAI RUGAR YAMMA</t>
+          <t>DANFARI I</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>19/43/12/013</t>
+          <t>19/43/12/002</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b176</t>
+          <t>6a35c3f587b1768452f7b16d</t>
         </is>
       </c>
       <c r="L407" t="n">
-        <v>64751</v>
+        <v>64740</v>
       </c>
       <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>1781976901500</t>
+        </is>
+      </c>
       <c r="O407" t="n">
         <v>0</v>
       </c>
@@ -64372,7 +64382,11 @@
         <v>0</v>
       </c>
       <c r="V407" t="inlineStr"/>
-      <c r="W407" t="inlineStr"/>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
+        </is>
+      </c>
       <c r="X407" t="n">
         <v>0</v>
       </c>
@@ -64483,26 +64497,26 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>YALMA</t>
+          <t>DANFARI II</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>19/43/12/014</t>
+          <t>19/43/12/003</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16e</t>
+          <t>6a35c3f587b1768452f7b175</t>
         </is>
       </c>
       <c r="L408" t="n">
-        <v>64752</v>
+        <v>64741</v>
       </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="inlineStr">
         <is>
-          <t>1781976792595</t>
+          <t>1781968309565</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -64527,7 +64541,7 @@
       <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
         </is>
       </c>
       <c r="X408" t="n">
@@ -64640,26 +64654,26 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>TANAGAR III (TANAGAR VETERINARY)</t>
+          <t>DANTSAWA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19/43/12/015</t>
+          <t>19/43/12/004</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17b</t>
+          <t>6a35c3f587b1768452f7b170</t>
         </is>
       </c>
       <c r="L409" t="n">
-        <v>151222</v>
+        <v>64742</v>
       </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr">
         <is>
-          <t>1781976850366</t>
+          <t>1781968186810</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -64684,7 +64698,7 @@
       <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
         </is>
       </c>
       <c r="X409" t="n">
@@ -64782,41 +64796,41 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>DUSHE I</t>
+          <t>HALADAWA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19/43/13/001</t>
+          <t>19/43/12/005</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b098</t>
+          <t>6a35c3f587b1768452f7b179</t>
         </is>
       </c>
       <c r="L410" t="n">
-        <v>64753</v>
+        <v>64743</v>
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr">
         <is>
-          <t>1781976869394</t>
+          <t>1781976861221</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -64841,7 +64855,7 @@
       <c r="V410" t="inlineStr"/>
       <c r="W410" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
         </is>
       </c>
       <c r="X410" t="n">
@@ -64939,41 +64953,41 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>DUSHE II</t>
+          <t>HAYIN WAZO</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>19/43/13/002</t>
+          <t>19/43/12/006</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09b</t>
+          <t>6a35c3f587b1768452f7b16f</t>
         </is>
       </c>
       <c r="L411" t="n">
-        <v>64754</v>
+        <v>64744</v>
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr">
         <is>
-          <t>1781974086141</t>
+          <t>1781976900341</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -64998,7 +65012,7 @@
       <c r="V411" t="inlineStr"/>
       <c r="W411" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
         </is>
       </c>
       <c r="X411" t="n">
@@ -65096,41 +65110,41 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>JALAWA I</t>
+          <t>JILAWA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19/43/13/003</t>
+          <t>19/43/12/007</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09c</t>
+          <t>6a35c3f587b1768452f7b174</t>
         </is>
       </c>
       <c r="L412" t="n">
-        <v>64755</v>
+        <v>64745</v>
       </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr">
         <is>
-          <t>1781976938520</t>
+          <t>1781968169241</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -65155,7 +65169,7 @@
       <c r="V412" t="inlineStr"/>
       <c r="W412" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
         </is>
       </c>
       <c r="X412" t="n">
@@ -65253,41 +65267,41 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>JALAWA II</t>
+          <t>KARGAWA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19/43/13/004</t>
+          <t>19/43/12/008</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09a</t>
+          <t>6a35c3f587b1768452f7b17a</t>
         </is>
       </c>
       <c r="L413" t="n">
-        <v>64756</v>
+        <v>64746</v>
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr">
         <is>
-          <t>1781977012376</t>
+          <t>1781976889527</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -65312,7 +65326,7 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
         </is>
       </c>
       <c r="X413" t="n">
@@ -65410,41 +65424,41 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>WARAWA I</t>
+          <t>MARAYAR ROGO</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19/43/13/005</t>
+          <t>19/43/12/009</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b099</t>
+          <t>6a35c3f587b1768452f7b178</t>
         </is>
       </c>
       <c r="L414" t="n">
-        <v>64757</v>
+        <v>64747</v>
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr">
         <is>
-          <t>1781977113973</t>
+          <t>1781976782857</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -65469,7 +65483,7 @@
       <c r="V414" t="inlineStr"/>
       <c r="W414" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
         </is>
       </c>
       <c r="X414" t="n">
@@ -65567,41 +65581,41 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>WARAWA II</t>
+          <t>RIGAR GABAS</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>19/43/13/006</t>
+          <t>19/43/12/010</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09d</t>
+          <t>6a35c3f587b1768452f7b177</t>
         </is>
       </c>
       <c r="L415" t="n">
-        <v>64758</v>
+        <v>64748</v>
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr">
         <is>
-          <t>1781976876830</t>
+          <t>1781968289759</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -65626,7 +65640,7 @@
       <c r="V415" t="inlineStr"/>
       <c r="W415" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
         </is>
       </c>
       <c r="X415" t="n">
@@ -65724,41 +65738,41 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
+          <t>TANAGAR I</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19/43/13/007</t>
+          <t>19/43/12/011</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09f</t>
+          <t>6a35c3f587b1768452f7b173</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>151223</v>
+        <v>64749</v>
       </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr">
         <is>
-          <t>1781976882480</t>
+          <t>1781976813571</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -65783,7 +65797,7 @@
       <c r="V416" t="inlineStr"/>
       <c r="W416" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
         </is>
       </c>
       <c r="X416" t="n">
@@ -65881,72 +65895,66 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
+          <t>TANAGAR II</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>19/43/13/008</t>
+          <t>19/43/12/012</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b0a0</t>
+          <t>6a35c3f587b1768452f7b172</t>
         </is>
       </c>
       <c r="L417" t="n">
-        <v>151224</v>
-      </c>
-      <c r="M417" t="n">
-        <v>1781968214959</v>
-      </c>
+        <v>64750</v>
+      </c>
+      <c r="M417" t="inlineStr"/>
       <c r="N417" t="inlineStr">
         <is>
-          <t>1781968212953</t>
+          <t>1781976798491</t>
         </is>
       </c>
       <c r="O417" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P417" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q417" t="n">
-        <v>3</v>
-      </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>6a36ad5552b6362accb5c7d0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R417" t="inlineStr"/>
       <c r="S417" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T417" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="U417" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V417" t="inlineStr"/>
       <c r="W417" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
         </is>
       </c>
       <c r="X417" t="n">
@@ -65965,7 +65973,7 @@
         <v>0</v>
       </c>
       <c r="AC417" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD417" t="n">
         <v>0</v>
@@ -66044,43 +66052,39 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
+          <t>WARKAI RUGAR YAMMA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19/43/13/009</t>
+          <t>19/43/12/013</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09e</t>
+          <t>6a35c3f587b1768452f7b176</t>
         </is>
       </c>
       <c r="L418" t="n">
-        <v>151225</v>
+        <v>64751</v>
       </c>
       <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr">
-        <is>
-          <t>1781968282375</t>
-        </is>
-      </c>
+      <c r="N418" t="inlineStr"/>
       <c r="O418" t="n">
         <v>0</v>
       </c>
@@ -66101,11 +66105,7 @@
         <v>0</v>
       </c>
       <c r="V418" t="inlineStr"/>
-      <c r="W418" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
-        </is>
-      </c>
+      <c r="W418" t="inlineStr"/>
       <c r="X418" t="n">
         <v>0</v>
       </c>
@@ -66201,41 +66201,41 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>GUMAKA</t>
+          <t>YALMA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19/43/14/001</t>
+          <t>19/43/12/014</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17e</t>
+          <t>6a35c3f587b1768452f7b16e</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>64759</v>
+        <v>64752</v>
       </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
         <is>
-          <t>1781975166154</t>
+          <t>1781976792595</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -66260,7 +66260,7 @@
       <c r="V419" t="inlineStr"/>
       <c r="W419" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
         </is>
       </c>
       <c r="X419" t="n">
@@ -66358,41 +66358,41 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>KANWA</t>
+          <t>TANAGAR III (TANAGAR VETERINARY)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19/43/14/002</t>
+          <t>19/43/12/015</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17c</t>
+          <t>6a35c3f587b1768452f7b17b</t>
         </is>
       </c>
       <c r="L420" t="n">
-        <v>64760</v>
+        <v>151222</v>
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
         <is>
-          <t>1781974985005</t>
+          <t>1781976850366</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -66417,7 +66417,7 @@
       <c r="V420" t="inlineStr"/>
       <c r="W420" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
         </is>
       </c>
       <c r="X420" t="n">
@@ -66515,41 +66515,41 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>POLICE ACADEMY</t>
+          <t>DUSHE I</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19/43/14/003</t>
+          <t>19/43/13/001</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17d</t>
+          <t>6a35c3f487b1768452f7b098</t>
         </is>
       </c>
       <c r="L421" t="n">
-        <v>64761</v>
+        <v>64753</v>
       </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
         <is>
-          <t>1781975165502</t>
+          <t>1781976869394</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -66574,7 +66574,7 @@
       <c r="V421" t="inlineStr"/>
       <c r="W421" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
         </is>
       </c>
       <c r="X421" t="n">
@@ -66672,41 +66672,41 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>'YANDALLA</t>
+          <t>DUSHE II</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>19/43/14/004</t>
+          <t>19/43/13/002</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17f</t>
+          <t>6a35c3f487b1768452f7b09b</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>64762</v>
+        <v>64754</v>
       </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
         <is>
-          <t>1781975169663</t>
+          <t>1781974086141</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -66731,7 +66731,7 @@
       <c r="V422" t="inlineStr"/>
       <c r="W422" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
         </is>
       </c>
       <c r="X422" t="n">
@@ -66829,41 +66829,41 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>'YANDALLA II</t>
+          <t>JALAWA I</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>19/43/14/005</t>
+          <t>19/43/13/003</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b180</t>
+          <t>6a35c3f487b1768452f7b09c</t>
         </is>
       </c>
       <c r="L423" t="n">
-        <v>64763</v>
+        <v>64755</v>
       </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr">
         <is>
-          <t>1781968201933</t>
+          <t>1781976938520</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -66888,7 +66888,7 @@
       <c r="V423" t="inlineStr"/>
       <c r="W423" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
         </is>
       </c>
       <c r="X423" t="n">
@@ -66986,41 +66986,41 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
+          <t>JALAWA II</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>19/43/14/006</t>
+          <t>19/43/13/004</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b183</t>
+          <t>6a35c3f487b1768452f7b09a</t>
         </is>
       </c>
       <c r="L424" t="n">
-        <v>151226</v>
+        <v>64756</v>
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr">
         <is>
-          <t>1781968195719</t>
+          <t>1781977012376</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -67045,7 +67045,7 @@
       <c r="V424" t="inlineStr"/>
       <c r="W424" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
         </is>
       </c>
       <c r="X424" t="n">
@@ -67143,41 +67143,41 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
+          <t>WARAWA I</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>19/43/14/007</t>
+          <t>19/43/13/005</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b182</t>
+          <t>6a35c3f487b1768452f7b099</t>
         </is>
       </c>
       <c r="L425" t="n">
-        <v>151227</v>
+        <v>64757</v>
       </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr">
         <is>
-          <t>1781974982952</t>
+          <t>1781977113973</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -67202,7 +67202,7 @@
       <c r="V425" t="inlineStr"/>
       <c r="W425" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
         </is>
       </c>
       <c r="X425" t="n">
@@ -67300,41 +67300,41 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
+          <t>WARAWA II</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>19/43/14/008</t>
+          <t>19/43/13/006</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b181</t>
+          <t>6a35c3f487b1768452f7b09d</t>
         </is>
       </c>
       <c r="L426" t="n">
-        <v>151228</v>
+        <v>64758</v>
       </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
-          <t>1781968682952</t>
+          <t>1781976876830</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -67359,7 +67359,7 @@
       <c r="V426" t="inlineStr"/>
       <c r="W426" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
         </is>
       </c>
       <c r="X426" t="n">
@@ -67457,41 +67457,41 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>ALIMAWA</t>
+          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>19/43/15/001</t>
+          <t>19/43/13/007</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fd</t>
+          <t>6a35c3f487b1768452f7b09f</t>
         </is>
       </c>
       <c r="L427" t="n">
-        <v>64764</v>
+        <v>151223</v>
       </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr">
         <is>
-          <t>1781968165832</t>
+          <t>1781976882480</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -67516,7 +67516,7 @@
       <c r="V427" t="inlineStr"/>
       <c r="W427" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
         </is>
       </c>
       <c r="X427" t="n">
@@ -67614,66 +67614,72 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>BUROMAWA</t>
+          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>19/43/15/002</t>
+          <t>19/43/13/008</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fc</t>
+          <t>6a35c3f487b1768452f7b0a0</t>
         </is>
       </c>
       <c r="L428" t="n">
-        <v>64765</v>
-      </c>
-      <c r="M428" t="inlineStr"/>
+        <v>151224</v>
+      </c>
+      <c r="M428" t="n">
+        <v>1781968214959</v>
+      </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>1781974266039</t>
+          <t>1781968212953</t>
         </is>
       </c>
       <c r="O428" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P428" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q428" t="n">
-        <v>0</v>
-      </c>
-      <c r="R428" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>6a36ad5552b6362accb5c7d0</t>
+        </is>
+      </c>
       <c r="S428" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T428" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="U428" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V428" t="inlineStr"/>
       <c r="W428" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
         </is>
       </c>
       <c r="X428" t="n">
@@ -67692,7 +67698,7 @@
         <v>0</v>
       </c>
       <c r="AC428" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD428" t="n">
         <v>0</v>
@@ -67771,41 +67777,41 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>GIWARAN ALITINI I</t>
+          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>19/43/15/003</t>
+          <t>19/43/13/009</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fe</t>
+          <t>6a35c3f487b1768452f7b09e</t>
         </is>
       </c>
       <c r="L429" t="n">
-        <v>64766</v>
+        <v>151225</v>
       </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr">
         <is>
-          <t>1781976840577</t>
+          <t>1781968282375</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -67830,7 +67836,7 @@
       <c r="V429" t="inlineStr"/>
       <c r="W429" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
         </is>
       </c>
       <c r="X429" t="n">
@@ -67928,41 +67934,41 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>GIWARAN ALITINI II</t>
+          <t>GUMAKA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>19/43/15/004</t>
+          <t>19/43/14/001</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fb</t>
+          <t>6a35c3f587b1768452f7b17e</t>
         </is>
       </c>
       <c r="L430" t="n">
-        <v>64767</v>
+        <v>64759</v>
       </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr">
         <is>
-          <t>1781968281024</t>
+          <t>1781975166154</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -67987,7 +67993,7 @@
       <c r="V430" t="inlineStr"/>
       <c r="W430" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
         </is>
       </c>
       <c r="X430" t="n">
@@ -68085,41 +68091,41 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>GIWARAN JIJIYAWA I</t>
+          <t>KANWA</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>19/43/15/005</t>
+          <t>19/43/14/002</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ff</t>
+          <t>6a35c3f587b1768452f7b17c</t>
         </is>
       </c>
       <c r="L431" t="n">
-        <v>64768</v>
+        <v>64760</v>
       </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr">
         <is>
-          <t>1781974266070</t>
+          <t>1781974985005</t>
         </is>
       </c>
       <c r="O431" t="n">
@@ -68144,7 +68150,7 @@
       <c r="V431" t="inlineStr"/>
       <c r="W431" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
         </is>
       </c>
       <c r="X431" t="n">
@@ -68242,41 +68248,41 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>GIWARAN JIJIYAWA II</t>
+          <t>POLICE ACADEMY</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>19/43/15/006</t>
+          <t>19/43/14/003</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b200</t>
+          <t>6a35c3f587b1768452f7b17d</t>
         </is>
       </c>
       <c r="L432" t="n">
-        <v>64769</v>
+        <v>64761</v>
       </c>
       <c r="M432" t="inlineStr"/>
       <c r="N432" t="inlineStr">
         <is>
-          <t>1781974447124</t>
+          <t>1781975165502</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -68301,7 +68307,7 @@
       <c r="V432" t="inlineStr"/>
       <c r="W432" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
         </is>
       </c>
       <c r="X432" t="n">
@@ -68399,41 +68405,41 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>'YANGIZO I</t>
+          <t>'YANDALLA</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>19/43/15/007</t>
+          <t>19/43/14/004</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1f8</t>
+          <t>6a35c3f587b1768452f7b17f</t>
         </is>
       </c>
       <c r="L433" t="n">
-        <v>64770</v>
+        <v>64762</v>
       </c>
       <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr">
         <is>
-          <t>1781974628327</t>
+          <t>1781975169663</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -68458,7 +68464,7 @@
       <c r="V433" t="inlineStr"/>
       <c r="W433" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
         </is>
       </c>
       <c r="X433" t="n">
@@ -68556,41 +68562,41 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>'YANGIZO II</t>
+          <t>'YANDALLA II</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>19/43/15/008</t>
+          <t>19/43/14/005</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1f9</t>
+          <t>6a35c3f587b1768452f7b180</t>
         </is>
       </c>
       <c r="L434" t="n">
-        <v>64771</v>
+        <v>64763</v>
       </c>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr">
         <is>
-          <t>1781974630372</t>
+          <t>1781968201933</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -68615,7 +68621,7 @@
       <c r="V434" t="inlineStr"/>
       <c r="W434" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
         </is>
       </c>
       <c r="X434" t="n">
@@ -68713,41 +68719,41 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>'YANGIZO III</t>
+          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>19/43/15/009</t>
+          <t>19/43/14/006</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fa</t>
+          <t>6a35c3f587b1768452f7b183</t>
         </is>
       </c>
       <c r="L435" t="n">
-        <v>64772</v>
+        <v>151226</v>
       </c>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr">
         <is>
-          <t>1781968246493</t>
+          <t>1781968195719</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -68772,7 +68778,7 @@
       <c r="V435" t="inlineStr"/>
       <c r="W435" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
         </is>
       </c>
       <c r="X435" t="n">
@@ -68870,41 +68876,41 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
+          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>19/43/15/010</t>
+          <t>19/43/14/007</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b201</t>
+          <t>6a35c3f587b1768452f7b182</t>
         </is>
       </c>
       <c r="L436" t="n">
-        <v>151229</v>
+        <v>151227</v>
       </c>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr">
         <is>
-          <t>1781974627113</t>
+          <t>1781974982952</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -68929,73 +68935,1800 @@
       <c r="V436" t="inlineStr"/>
       <c r="W436" t="inlineStr">
         <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+        </is>
+      </c>
+      <c r="X436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>YAN DALLA</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a011</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>19/43/14/008</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b181</t>
+        </is>
+      </c>
+      <c r="L437" t="n">
+        <v>151228</v>
+      </c>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>1781968682952</t>
+        </is>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="inlineStr"/>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="inlineStr"/>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
+        </is>
+      </c>
+      <c r="X437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>ALIMAWA</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>19/43/15/001</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fd</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>64764</v>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>1781968165832</t>
+        </is>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="inlineStr"/>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>0</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="inlineStr"/>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
+        </is>
+      </c>
+      <c r="X438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>BUROMAWA</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>19/43/15/002</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fc</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>64765</v>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>1781974266039</t>
+        </is>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="inlineStr"/>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="inlineStr"/>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
+        </is>
+      </c>
+      <c r="X439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>GIWARAN ALITINI I</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>19/43/15/003</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fe</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>64766</v>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>1781976840577</t>
+        </is>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" t="inlineStr"/>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="inlineStr"/>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
+        </is>
+      </c>
+      <c r="X440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>GIWARAN ALITINI II</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>19/43/15/004</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fb</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>64767</v>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>1781968281024</t>
+        </is>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" t="inlineStr"/>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>0</v>
+      </c>
+      <c r="V441" t="inlineStr"/>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
+        </is>
+      </c>
+      <c r="X441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>GIWARAN JIJIYAWA I</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>19/43/15/005</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1ff</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>64768</v>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>1781974266070</t>
+        </is>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="inlineStr"/>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="inlineStr"/>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
+        </is>
+      </c>
+      <c r="X442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>GIWARAN JIJIYAWA II</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>19/43/15/006</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b200</t>
+        </is>
+      </c>
+      <c r="L443" t="n">
+        <v>64769</v>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>1781974447124</t>
+        </is>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>0</v>
+      </c>
+      <c r="R443" t="inlineStr"/>
+      <c r="S443" t="n">
+        <v>0</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V443" t="inlineStr"/>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
+        </is>
+      </c>
+      <c r="X443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>'YANGIZO I</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>19/43/15/007</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1f8</t>
+        </is>
+      </c>
+      <c r="L444" t="n">
+        <v>64770</v>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>1781974628327</t>
+        </is>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>0</v>
+      </c>
+      <c r="R444" t="inlineStr"/>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
+      <c r="V444" t="inlineStr"/>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
+        </is>
+      </c>
+      <c r="X444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>'YANGIZO II</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>19/43/15/008</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1f9</t>
+        </is>
+      </c>
+      <c r="L445" t="n">
+        <v>64771</v>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>1781974630372</t>
+        </is>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>0</v>
+      </c>
+      <c r="R445" t="inlineStr"/>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0</v>
+      </c>
+      <c r="V445" t="inlineStr"/>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
+        </is>
+      </c>
+      <c r="X445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>'YANGIZO III</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>19/43/15/009</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fa</t>
+        </is>
+      </c>
+      <c r="L446" t="n">
+        <v>64772</v>
+      </c>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>1781968246493</t>
+        </is>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="inlineStr"/>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
+      <c r="V446" t="inlineStr"/>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
+        </is>
+      </c>
+      <c r="X446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>19/43/15/010</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b201</t>
+        </is>
+      </c>
+      <c r="L447" t="n">
+        <v>151229</v>
+      </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>1781974627113</t>
+        </is>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="inlineStr"/>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0</v>
+      </c>
+      <c r="V447" t="inlineStr"/>
+      <c r="W447" t="inlineStr">
+        <is>
           <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
         </is>
       </c>
-      <c r="X436" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y436" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS436" t="n">
+      <c r="X447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS447" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69010,7 +70743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH30"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71508,36 +73241,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JIGAWA</t>
+          <t>JEMAGU</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>434</v>
+        <v>500</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" t="n">
+        <v>475</v>
+      </c>
+      <c r="I23" t="n">
+        <v>80</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>123</v>
-      </c>
-      <c r="H23" t="n">
-        <v>434</v>
-      </c>
-      <c r="I23" t="n">
-        <v>121</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -71545,13 +73278,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -71596,10 +73329,10 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>100</v>
@@ -71618,26 +73351,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>JIGAWA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>235</v>
+        <v>434</v>
       </c>
       <c r="E24" t="n">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="H24" t="n">
-        <v>235</v>
+        <v>434</v>
       </c>
       <c r="I24" t="n">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -71655,13 +73388,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -71706,10 +73439,10 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH24" t="n">
         <v>100</v>
@@ -71728,26 +73461,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -71765,7 +73498,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -71816,10 +73549,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>100</v>
@@ -71838,7 +73571,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -71926,10 +73659,10 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
         <v>100</v>
@@ -71948,7 +73681,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -72036,13 +73769,13 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -72058,26 +73791,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -72095,7 +73828,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -72146,13 +73879,13 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="29">
@@ -72168,26 +73901,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -72205,7 +73938,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -72256,10 +73989,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH29" t="n">
         <v>100</v>
@@ -72278,100 +74011,210 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>YAN DALLA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>YANGIZO</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
         <v>10</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG31" t="n">
         <v>10</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH31" t="n">
         <v>100</v>
       </c>
     </row>
@@ -72673,22 +74516,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2631</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>436</v>
+        <v>516</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>433</v>
+        <v>513</v>
       </c>
       <c r="G3" t="n">
-        <v>2614</v>
+        <v>3089</v>
       </c>
       <c r="H3" t="n">
-        <v>428</v>
+        <v>508</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -72697,7 +74540,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -72706,7 +74549,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>425</v>
+        <v>503</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -72757,13 +74600,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AF3" t="n">
         <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>107.6</v>
+        <v>99.3</v>
       </c>
     </row>
   </sheetData>
@@ -72954,22 +74797,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6811</v>
+        <v>7311</v>
       </c>
       <c r="C2" t="n">
-        <v>904</v>
+        <v>984</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>885</v>
+        <v>965</v>
       </c>
       <c r="F2" t="n">
-        <v>6794</v>
+        <v>7269</v>
       </c>
       <c r="G2" t="n">
-        <v>878</v>
+        <v>958</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -72978,7 +74821,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -72987,7 +74830,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>871</v>
+        <v>949</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -73038,16 +74881,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AE2" t="n">
         <v>445</v>
       </c>
       <c r="AF2" t="n">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>102.3</v>
+        <v>99.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS447"/>
+  <dimension ref="A1:AS436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59138,41 +59138,41 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>DANHAWAGIWA</t>
+          <t>GANAKAKUN I</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>19/43/09/001</t>
+          <t>19/43/10/001</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b213</t>
+          <t>6a35c3f587b1768452f7b1cf</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>64714</v>
+        <v>64722</v>
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr">
         <is>
-          <t>1781970484687</t>
+          <t>1781968221436</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -59197,7 +59197,7 @@
       <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
         </is>
       </c>
       <c r="X374" t="n">
@@ -59295,41 +59295,41 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA I</t>
+          <t>GANAKAKUN II</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>19/43/09/002</t>
+          <t>19/43/10/002</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b215</t>
+          <t>6a35c3f587b1768452f7b1ce</t>
         </is>
       </c>
       <c r="L375" t="n">
-        <v>64715</v>
+        <v>64723</v>
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr">
         <is>
-          <t>1781970664668</t>
+          <t>1781968244797</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -59354,7 +59354,7 @@
       <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
         </is>
       </c>
       <c r="X375" t="n">
@@ -59452,72 +59452,66 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>GISHIRI WUYA II</t>
+          <t>MADARIN MABA I</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>19/43/09/003</t>
+          <t>19/43/10/003</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b217</t>
+          <t>6a35c3f587b1768452f7b1d3</t>
         </is>
       </c>
       <c r="L376" t="n">
-        <v>64716</v>
-      </c>
-      <c r="M376" t="n">
-        <v>1781969584429</v>
-      </c>
+        <v>64724</v>
+      </c>
+      <c r="M376" t="inlineStr"/>
       <c r="N376" t="inlineStr">
         <is>
-          <t>1781969583795</t>
+          <t>1781968265095</t>
         </is>
       </c>
       <c r="O376" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="P376" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q376" t="n">
         <v>0</v>
       </c>
-      <c r="R376" t="inlineStr">
-        <is>
-          <t>6a36b2af52b6362accb5cc50</t>
-        </is>
-      </c>
+      <c r="R376" t="inlineStr"/>
       <c r="S376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="T376" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="U376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
         </is>
       </c>
       <c r="X376" t="n">
@@ -59536,7 +59530,7 @@
         <v>0</v>
       </c>
       <c r="AC376" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD376" t="n">
         <v>0</v>
@@ -59615,41 +59609,41 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARIN MABA II</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>19/43/09/004</t>
+          <t>19/43/10/004</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b210</t>
+          <t>6a35c3f587b1768452f7b1d0</t>
         </is>
       </c>
       <c r="L377" t="n">
-        <v>64717</v>
+        <v>64725</v>
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
-          <t>1781976885564</t>
+          <t>1781971564529</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -59674,7 +59668,7 @@
       <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
         </is>
       </c>
       <c r="X377" t="n">
@@ -59772,41 +59766,41 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>KINCHAU</t>
+          <t>MADARIN MABA III</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>19/43/09/005</t>
+          <t>19/43/10/005</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b212</t>
+          <t>6a35c3f587b1768452f7b1d2</t>
         </is>
       </c>
       <c r="L378" t="n">
-        <v>64718</v>
+        <v>64726</v>
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
-          <t>1781976801113</t>
+          <t>1781971929292</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -59831,7 +59825,7 @@
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
         </is>
       </c>
       <c r="X378" t="n">
@@ -59929,41 +59923,41 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>NAIRA</t>
+          <t>MARAYAR WUTA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>19/43/09/006</t>
+          <t>19/43/10/006</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b214</t>
+          <t>6a35c3f587b1768452f7b1cd</t>
         </is>
       </c>
       <c r="L379" t="n">
-        <v>64719</v>
+        <v>64727</v>
       </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
-          <t>1781976797855</t>
+          <t>1781971930377</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -59988,7 +59982,7 @@
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
         </is>
       </c>
       <c r="X379" t="n">
@@ -60086,41 +60080,41 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>TURBA</t>
+          <t>SABON GARIN NASARA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>19/43/09/007</t>
+          <t>19/43/10/007</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b211</t>
+          <t>6a35c3f587b1768452f7b1cc</t>
         </is>
       </c>
       <c r="L380" t="n">
-        <v>64720</v>
+        <v>64728</v>
       </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
-          <t>1781970126235</t>
+          <t>1781971922925</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -60145,7 +60139,7 @@
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
         </is>
       </c>
       <c r="X380" t="n">
@@ -60243,41 +60237,41 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>WALAGIGI</t>
+          <t>TALAWA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>19/43/09/008</t>
+          <t>19/43/10/008</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b216</t>
+          <t>6a35c3f587b1768452f7b1d1</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>64721</v>
+        <v>64729</v>
       </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
-          <t>1781973924024</t>
+          <t>1781968262106</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -60302,7 +60296,7 @@
       <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
         </is>
       </c>
       <c r="X381" t="n">
@@ -60400,41 +60394,41 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
+          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19/43/09/009</t>
+          <t>19/43/10/009</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b219</t>
+          <t>6a35c3f587b1768452f7b1d5</t>
         </is>
       </c>
       <c r="L382" t="n">
-        <v>151215</v>
+        <v>151218</v>
       </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
-          <t>1781976919845</t>
+          <t>1781972103434</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -60459,7 +60453,7 @@
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
         </is>
       </c>
       <c r="X382" t="n">
@@ -60557,41 +60551,41 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
+          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19/43/09/010</t>
+          <t>19/43/10/010</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b218</t>
+          <t>6a35c3f587b1768452f7b1d4</t>
         </is>
       </c>
       <c r="L383" t="n">
-        <v>151216</v>
+        <v>151219</v>
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr">
         <is>
-          <t>1781973731518</t>
+          <t>1781972285399</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -60616,7 +60610,7 @@
       <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
         </is>
       </c>
       <c r="X383" t="n">
@@ -60714,41 +60708,41 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00c</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
+          <t>FARTAWA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19/43/09/011</t>
+          <t>19/43/11/001</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21a</t>
+          <t>6a35c3f587b1768452f7b21c</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>151217</v>
+        <v>64730</v>
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr">
         <is>
-          <t>1781977138945</t>
+          <t>1781977074928</t>
         </is>
       </c>
       <c r="O384" t="n">
@@ -60773,7 +60767,7 @@
       <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
         </is>
       </c>
       <c r="X384" t="n">
@@ -60871,41 +60865,41 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>GANAKAKUN I</t>
+          <t>TAMBURAWAR GABAS I</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>19/43/10/001</t>
+          <t>19/43/11/002</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cf</t>
+          <t>6a35c3f587b1768452f7b223</t>
         </is>
       </c>
       <c r="L385" t="n">
-        <v>64722</v>
+        <v>64731</v>
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr">
         <is>
-          <t>1781968221436</t>
+          <t>1781977113305</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -60930,7 +60924,7 @@
       <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
         </is>
       </c>
       <c r="X385" t="n">
@@ -61028,41 +61022,41 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>GANAKAKUN II</t>
+          <t>TAMBURAWAR GABAS II</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19/43/10/002</t>
+          <t>19/43/11/003</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ce</t>
+          <t>6a35c3f587b1768452f7b21b</t>
         </is>
       </c>
       <c r="L386" t="n">
-        <v>64723</v>
+        <v>64732</v>
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr">
         <is>
-          <t>1781968244797</t>
+          <t>1781977075062</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -61087,7 +61081,7 @@
       <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
         </is>
       </c>
       <c r="X386" t="n">
@@ -61185,41 +61179,41 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>MADARIN MABA I</t>
+          <t>UNGUWAR ZURURU</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19/43/10/003</t>
+          <t>19/43/11/004</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d3</t>
+          <t>6a35c3f587b1768452f7b222</t>
         </is>
       </c>
       <c r="L387" t="n">
-        <v>64724</v>
+        <v>64733</v>
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr">
         <is>
-          <t>1781968265095</t>
+          <t>1781975346942</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -61244,7 +61238,7 @@
       <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
         </is>
       </c>
       <c r="X387" t="n">
@@ -61342,41 +61336,41 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>MADARIN MABA II</t>
+          <t>YANDADI I</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19/43/10/004</t>
+          <t>19/43/11/005</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d0</t>
+          <t>6a35c3f587b1768452f7b221</t>
         </is>
       </c>
       <c r="L388" t="n">
-        <v>64725</v>
+        <v>64734</v>
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr">
         <is>
-          <t>1781971564529</t>
+          <t>1781975887400</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -61401,7 +61395,7 @@
       <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
         </is>
       </c>
       <c r="X388" t="n">
@@ -61499,41 +61493,41 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>MADARIN MABA III</t>
+          <t>YANDADI II</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>19/43/10/005</t>
+          <t>19/43/11/006</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d2</t>
+          <t>6a35c3f587b1768452f7b21e</t>
         </is>
       </c>
       <c r="L389" t="n">
-        <v>64726</v>
+        <v>64735</v>
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr">
         <is>
-          <t>1781971929292</t>
+          <t>1782131641877</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -61558,7 +61552,7 @@
       <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
         </is>
       </c>
       <c r="X389" t="n">
@@ -61656,41 +61650,41 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>MARAYAR WUTA</t>
+          <t>YADAUDU I</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19/43/10/006</t>
+          <t>19/43/11/007</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cd</t>
+          <t>6a35c3f587b1768452f7b220</t>
         </is>
       </c>
       <c r="L390" t="n">
-        <v>64727</v>
+        <v>64736</v>
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr">
         <is>
-          <t>1781971930377</t>
+          <t>1781989191145</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -61715,7 +61709,7 @@
       <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
         </is>
       </c>
       <c r="X390" t="n">
@@ -61813,41 +61807,41 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>SABON GARIN NASARA</t>
+          <t>YADAUDU II</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19/43/10/007</t>
+          <t>19/43/11/008</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cc</t>
+          <t>6a35c3f587b1768452f7b21f</t>
         </is>
       </c>
       <c r="L391" t="n">
-        <v>64728</v>
+        <v>64737</v>
       </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr">
         <is>
-          <t>1781971922925</t>
+          <t>1781976878903</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -61872,7 +61866,7 @@
       <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
         </is>
       </c>
       <c r="X391" t="n">
@@ -61970,41 +61964,41 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>TALAWA</t>
+          <t>ZANGO DANMARKE</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19/43/10/008</t>
+          <t>19/43/11/009</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d1</t>
+          <t>6a35c3f587b1768452f7b21d</t>
         </is>
       </c>
       <c r="L392" t="n">
-        <v>64729</v>
+        <v>64738</v>
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
         <is>
-          <t>1781968262106</t>
+          <t>1781976780359</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -62029,7 +62023,7 @@
       <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
         </is>
       </c>
       <c r="X392" t="n">
@@ -62127,41 +62121,41 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>19/43/10/009</t>
+          <t>19/43/11/010</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d5</t>
+          <t>6a35c3f587b1768452f7b224</t>
         </is>
       </c>
       <c r="L393" t="n">
-        <v>151218</v>
+        <v>151220</v>
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr">
         <is>
-          <t>1781972103434</t>
+          <t>1781977094685</t>
         </is>
       </c>
       <c r="O393" t="n">
@@ -62186,7 +62180,7 @@
       <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
         </is>
       </c>
       <c r="X393" t="n">
@@ -62284,41 +62278,41 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>19/43/10/010</t>
+          <t>19/43/11/011</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d4</t>
+          <t>6a35c3f587b1768452f7b225</t>
         </is>
       </c>
       <c r="L394" t="n">
-        <v>151219</v>
+        <v>151221</v>
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
         <is>
-          <t>1781972285399</t>
+          <t>1781976782683</t>
         </is>
       </c>
       <c r="O394" t="n">
@@ -62343,7 +62337,7 @@
       <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
         </is>
       </c>
       <c r="X394" t="n">
@@ -62441,41 +62435,41 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>FARTAWA</t>
+          <t>CHARKA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19/43/11/001</t>
+          <t>19/43/12/001</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21c</t>
+          <t>6a35c3f587b1768452f7b171</t>
         </is>
       </c>
       <c r="L395" t="n">
-        <v>64730</v>
+        <v>64739</v>
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
         <is>
-          <t>1781977074928</t>
+          <t>1781976872268</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -62500,7 +62494,7 @@
       <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
         </is>
       </c>
       <c r="X395" t="n">
@@ -62598,41 +62592,41 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS I</t>
+          <t>DANFARI I</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19/43/11/002</t>
+          <t>19/43/12/002</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b223</t>
+          <t>6a35c3f587b1768452f7b16d</t>
         </is>
       </c>
       <c r="L396" t="n">
-        <v>64731</v>
+        <v>64740</v>
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr">
         <is>
-          <t>1781977113305</t>
+          <t>1781976901500</t>
         </is>
       </c>
       <c r="O396" t="n">
@@ -62657,7 +62651,7 @@
       <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
         </is>
       </c>
       <c r="X396" t="n">
@@ -62755,41 +62749,41 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS II</t>
+          <t>DANFARI II</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>19/43/11/003</t>
+          <t>19/43/12/003</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21b</t>
+          <t>6a35c3f587b1768452f7b175</t>
         </is>
       </c>
       <c r="L397" t="n">
-        <v>64732</v>
+        <v>64741</v>
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr">
         <is>
-          <t>1781977075062</t>
+          <t>1781968309565</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -62814,7 +62808,7 @@
       <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
         </is>
       </c>
       <c r="X397" t="n">
@@ -62912,41 +62906,41 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>UNGUWAR ZURURU</t>
+          <t>DANTSAWA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>19/43/11/004</t>
+          <t>19/43/12/004</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b222</t>
+          <t>6a35c3f587b1768452f7b170</t>
         </is>
       </c>
       <c r="L398" t="n">
-        <v>64733</v>
+        <v>64742</v>
       </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr">
         <is>
-          <t>1781975346942</t>
+          <t>1781968186810</t>
         </is>
       </c>
       <c r="O398" t="n">
@@ -62971,7 +62965,7 @@
       <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
         </is>
       </c>
       <c r="X398" t="n">
@@ -63069,41 +63063,41 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>YANDADI I</t>
+          <t>HALADAWA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19/43/11/005</t>
+          <t>19/43/12/005</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b221</t>
+          <t>6a35c3f587b1768452f7b179</t>
         </is>
       </c>
       <c r="L399" t="n">
-        <v>64734</v>
+        <v>64743</v>
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr">
         <is>
-          <t>1781975887400</t>
+          <t>1781976861221</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -63128,7 +63122,7 @@
       <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
         </is>
       </c>
       <c r="X399" t="n">
@@ -63226,41 +63220,41 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>YANDADI II</t>
+          <t>HAYIN WAZO</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>19/43/11/006</t>
+          <t>19/43/12/006</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21e</t>
+          <t>6a35c3f587b1768452f7b16f</t>
         </is>
       </c>
       <c r="L400" t="n">
-        <v>64735</v>
+        <v>64744</v>
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr">
         <is>
-          <t>1782131641877</t>
+          <t>1781976900341</t>
         </is>
       </c>
       <c r="O400" t="n">
@@ -63285,7 +63279,7 @@
       <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
         </is>
       </c>
       <c r="X400" t="n">
@@ -63383,41 +63377,41 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>YADAUDU I</t>
+          <t>JILAWA</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19/43/11/007</t>
+          <t>19/43/12/007</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b220</t>
+          <t>6a35c3f587b1768452f7b174</t>
         </is>
       </c>
       <c r="L401" t="n">
-        <v>64736</v>
+        <v>64745</v>
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr">
         <is>
-          <t>1781989191145</t>
+          <t>1781968169241</t>
         </is>
       </c>
       <c r="O401" t="n">
@@ -63442,7 +63436,7 @@
       <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
         </is>
       </c>
       <c r="X401" t="n">
@@ -63540,41 +63534,41 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>YADAUDU II</t>
+          <t>KARGAWA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19/43/11/008</t>
+          <t>19/43/12/008</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21f</t>
+          <t>6a35c3f587b1768452f7b17a</t>
         </is>
       </c>
       <c r="L402" t="n">
-        <v>64737</v>
+        <v>64746</v>
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr">
         <is>
-          <t>1781976878903</t>
+          <t>1781976889527</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -63599,7 +63593,7 @@
       <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
         </is>
       </c>
       <c r="X402" t="n">
@@ -63697,41 +63691,41 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>ZANGO DANMARKE</t>
+          <t>MARAYAR ROGO</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19/43/11/009</t>
+          <t>19/43/12/009</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21d</t>
+          <t>6a35c3f587b1768452f7b178</t>
         </is>
       </c>
       <c r="L403" t="n">
-        <v>64738</v>
+        <v>64747</v>
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr">
         <is>
-          <t>1781976780359</t>
+          <t>1781976782857</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -63756,7 +63750,7 @@
       <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
         </is>
       </c>
       <c r="X403" t="n">
@@ -63854,41 +63848,41 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
+          <t>RIGAR GABAS</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19/43/11/010</t>
+          <t>19/43/12/010</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b224</t>
+          <t>6a35c3f587b1768452f7b177</t>
         </is>
       </c>
       <c r="L404" t="n">
-        <v>151220</v>
+        <v>64748</v>
       </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr">
         <is>
-          <t>1781977094685</t>
+          <t>1781968289759</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -63913,7 +63907,7 @@
       <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
         </is>
       </c>
       <c r="X404" t="n">
@@ -64011,41 +64005,41 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
+          <t>TANAGAR I</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19/43/11/011</t>
+          <t>19/43/12/011</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b225</t>
+          <t>6a35c3f587b1768452f7b173</t>
         </is>
       </c>
       <c r="L405" t="n">
-        <v>151221</v>
+        <v>64749</v>
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr">
         <is>
-          <t>1781976782683</t>
+          <t>1781976813571</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -64070,7 +64064,7 @@
       <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
         </is>
       </c>
       <c r="X405" t="n">
@@ -64183,26 +64177,26 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>CHARKA</t>
+          <t>TANAGAR II</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>19/43/12/001</t>
+          <t>19/43/12/012</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b171</t>
+          <t>6a35c3f587b1768452f7b172</t>
         </is>
       </c>
       <c r="L406" t="n">
-        <v>64739</v>
+        <v>64750</v>
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
-          <t>1781976872268</t>
+          <t>1781976798491</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -64227,7 +64221,7 @@
       <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
         </is>
       </c>
       <c r="X406" t="n">
@@ -64340,28 +64334,24 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>DANFARI I</t>
+          <t>WARKAI RUGAR YAMMA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>19/43/12/002</t>
+          <t>19/43/12/013</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16d</t>
+          <t>6a35c3f587b1768452f7b176</t>
         </is>
       </c>
       <c r="L407" t="n">
-        <v>64740</v>
+        <v>64751</v>
       </c>
       <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr">
-        <is>
-          <t>1781976901500</t>
-        </is>
-      </c>
+      <c r="N407" t="inlineStr"/>
       <c r="O407" t="n">
         <v>0</v>
       </c>
@@ -64382,11 +64372,7 @@
         <v>0</v>
       </c>
       <c r="V407" t="inlineStr"/>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
-        </is>
-      </c>
+      <c r="W407" t="inlineStr"/>
       <c r="X407" t="n">
         <v>0</v>
       </c>
@@ -64497,26 +64483,26 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>DANFARI II</t>
+          <t>YALMA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>19/43/12/003</t>
+          <t>19/43/12/014</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b175</t>
+          <t>6a35c3f587b1768452f7b16e</t>
         </is>
       </c>
       <c r="L408" t="n">
-        <v>64741</v>
+        <v>64752</v>
       </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="inlineStr">
         <is>
-          <t>1781968309565</t>
+          <t>1781976792595</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -64541,7 +64527,7 @@
       <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
         </is>
       </c>
       <c r="X408" t="n">
@@ -64654,26 +64640,26 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DANTSAWA</t>
+          <t>TANAGAR III (TANAGAR VETERINARY)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19/43/12/004</t>
+          <t>19/43/12/015</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b170</t>
+          <t>6a35c3f587b1768452f7b17b</t>
         </is>
       </c>
       <c r="L409" t="n">
-        <v>64742</v>
+        <v>151222</v>
       </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr">
         <is>
-          <t>1781968186810</t>
+          <t>1781976850366</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -64698,7 +64684,7 @@
       <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
         </is>
       </c>
       <c r="X409" t="n">
@@ -64796,41 +64782,41 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>HALADAWA</t>
+          <t>DUSHE I</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19/43/12/005</t>
+          <t>19/43/13/001</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b179</t>
+          <t>6a35c3f487b1768452f7b098</t>
         </is>
       </c>
       <c r="L410" t="n">
-        <v>64743</v>
+        <v>64753</v>
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr">
         <is>
-          <t>1781976861221</t>
+          <t>1781976869394</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -64855,7 +64841,7 @@
       <c r="V410" t="inlineStr"/>
       <c r="W410" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
         </is>
       </c>
       <c r="X410" t="n">
@@ -64953,41 +64939,41 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>HAYIN WAZO</t>
+          <t>DUSHE II</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>19/43/12/006</t>
+          <t>19/43/13/002</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16f</t>
+          <t>6a35c3f487b1768452f7b09b</t>
         </is>
       </c>
       <c r="L411" t="n">
-        <v>64744</v>
+        <v>64754</v>
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr">
         <is>
-          <t>1781976900341</t>
+          <t>1781974086141</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -65012,7 +64998,7 @@
       <c r="V411" t="inlineStr"/>
       <c r="W411" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
         </is>
       </c>
       <c r="X411" t="n">
@@ -65110,41 +65096,41 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>JILAWA</t>
+          <t>JALAWA I</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19/43/12/007</t>
+          <t>19/43/13/003</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b174</t>
+          <t>6a35c3f487b1768452f7b09c</t>
         </is>
       </c>
       <c r="L412" t="n">
-        <v>64745</v>
+        <v>64755</v>
       </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr">
         <is>
-          <t>1781968169241</t>
+          <t>1781976938520</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -65169,7 +65155,7 @@
       <c r="V412" t="inlineStr"/>
       <c r="W412" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
         </is>
       </c>
       <c r="X412" t="n">
@@ -65267,41 +65253,41 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>KARGAWA</t>
+          <t>JALAWA II</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19/43/12/008</t>
+          <t>19/43/13/004</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17a</t>
+          <t>6a35c3f487b1768452f7b09a</t>
         </is>
       </c>
       <c r="L413" t="n">
-        <v>64746</v>
+        <v>64756</v>
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr">
         <is>
-          <t>1781976889527</t>
+          <t>1781977012376</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -65326,7 +65312,7 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
         </is>
       </c>
       <c r="X413" t="n">
@@ -65424,41 +65410,41 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>MARAYAR ROGO</t>
+          <t>WARAWA I</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19/43/12/009</t>
+          <t>19/43/13/005</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b178</t>
+          <t>6a35c3f487b1768452f7b099</t>
         </is>
       </c>
       <c r="L414" t="n">
-        <v>64747</v>
+        <v>64757</v>
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr">
         <is>
-          <t>1781976782857</t>
+          <t>1781977113973</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -65483,7 +65469,7 @@
       <c r="V414" t="inlineStr"/>
       <c r="W414" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
         </is>
       </c>
       <c r="X414" t="n">
@@ -65581,41 +65567,41 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>RIGAR GABAS</t>
+          <t>WARAWA II</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>19/43/12/010</t>
+          <t>19/43/13/006</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b177</t>
+          <t>6a35c3f487b1768452f7b09d</t>
         </is>
       </c>
       <c r="L415" t="n">
-        <v>64748</v>
+        <v>64758</v>
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr">
         <is>
-          <t>1781968289759</t>
+          <t>1781976876830</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -65640,7 +65626,7 @@
       <c r="V415" t="inlineStr"/>
       <c r="W415" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
         </is>
       </c>
       <c r="X415" t="n">
@@ -65738,41 +65724,41 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>TANAGAR I</t>
+          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19/43/12/011</t>
+          <t>19/43/13/007</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b173</t>
+          <t>6a35c3f487b1768452f7b09f</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>64749</v>
+        <v>151223</v>
       </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr">
         <is>
-          <t>1781976813571</t>
+          <t>1781976882480</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -65797,7 +65783,7 @@
       <c r="V416" t="inlineStr"/>
       <c r="W416" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
         </is>
       </c>
       <c r="X416" t="n">
@@ -65895,66 +65881,72 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>TANAGAR II</t>
+          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>19/43/12/012</t>
+          <t>19/43/13/008</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b172</t>
+          <t>6a35c3f487b1768452f7b0a0</t>
         </is>
       </c>
       <c r="L417" t="n">
-        <v>64750</v>
-      </c>
-      <c r="M417" t="inlineStr"/>
+        <v>151224</v>
+      </c>
+      <c r="M417" t="n">
+        <v>1781968214959</v>
+      </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>1781976798491</t>
+          <t>1781968212953</t>
         </is>
       </c>
       <c r="O417" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P417" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q417" t="n">
-        <v>0</v>
-      </c>
-      <c r="R417" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>6a36ad5552b6362accb5c7d0</t>
+        </is>
+      </c>
       <c r="S417" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T417" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="U417" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V417" t="inlineStr"/>
       <c r="W417" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
         </is>
       </c>
       <c r="X417" t="n">
@@ -65973,7 +65965,7 @@
         <v>0</v>
       </c>
       <c r="AC417" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD417" t="n">
         <v>0</v>
@@ -66052,39 +66044,43 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>WARKAI RUGAR YAMMA</t>
+          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19/43/12/013</t>
+          <t>19/43/13/009</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b176</t>
+          <t>6a35c3f487b1768452f7b09e</t>
         </is>
       </c>
       <c r="L418" t="n">
-        <v>64751</v>
+        <v>151225</v>
       </c>
       <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>1781968282375</t>
+        </is>
+      </c>
       <c r="O418" t="n">
         <v>0</v>
       </c>
@@ -66105,7 +66101,11 @@
         <v>0</v>
       </c>
       <c r="V418" t="inlineStr"/>
-      <c r="W418" t="inlineStr"/>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
+        </is>
+      </c>
       <c r="X418" t="n">
         <v>0</v>
       </c>
@@ -66201,41 +66201,41 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>YALMA</t>
+          <t>GUMAKA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19/43/12/014</t>
+          <t>19/43/14/001</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16e</t>
+          <t>6a35c3f587b1768452f7b17e</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>64752</v>
+        <v>64759</v>
       </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
         <is>
-          <t>1781976792595</t>
+          <t>1781975166154</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -66260,7 +66260,7 @@
       <c r="V419" t="inlineStr"/>
       <c r="W419" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
         </is>
       </c>
       <c r="X419" t="n">
@@ -66358,41 +66358,41 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>TANAGAR III (TANAGAR VETERINARY)</t>
+          <t>KANWA</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19/43/12/015</t>
+          <t>19/43/14/002</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17b</t>
+          <t>6a35c3f587b1768452f7b17c</t>
         </is>
       </c>
       <c r="L420" t="n">
-        <v>151222</v>
+        <v>64760</v>
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
         <is>
-          <t>1781976850366</t>
+          <t>1781974985005</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -66417,7 +66417,7 @@
       <c r="V420" t="inlineStr"/>
       <c r="W420" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
         </is>
       </c>
       <c r="X420" t="n">
@@ -66515,41 +66515,41 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>DUSHE I</t>
+          <t>POLICE ACADEMY</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19/43/13/001</t>
+          <t>19/43/14/003</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b098</t>
+          <t>6a35c3f587b1768452f7b17d</t>
         </is>
       </c>
       <c r="L421" t="n">
-        <v>64753</v>
+        <v>64761</v>
       </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
         <is>
-          <t>1781976869394</t>
+          <t>1781975165502</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -66574,7 +66574,7 @@
       <c r="V421" t="inlineStr"/>
       <c r="W421" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
         </is>
       </c>
       <c r="X421" t="n">
@@ -66672,41 +66672,41 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>DUSHE II</t>
+          <t>'YANDALLA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>19/43/13/002</t>
+          <t>19/43/14/004</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09b</t>
+          <t>6a35c3f587b1768452f7b17f</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>64754</v>
+        <v>64762</v>
       </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
         <is>
-          <t>1781974086141</t>
+          <t>1781975169663</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -66731,7 +66731,7 @@
       <c r="V422" t="inlineStr"/>
       <c r="W422" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
         </is>
       </c>
       <c r="X422" t="n">
@@ -66829,41 +66829,41 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>JALAWA I</t>
+          <t>'YANDALLA II</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>19/43/13/003</t>
+          <t>19/43/14/005</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09c</t>
+          <t>6a35c3f587b1768452f7b180</t>
         </is>
       </c>
       <c r="L423" t="n">
-        <v>64755</v>
+        <v>64763</v>
       </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr">
         <is>
-          <t>1781976938520</t>
+          <t>1781968201933</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -66888,7 +66888,7 @@
       <c r="V423" t="inlineStr"/>
       <c r="W423" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
         </is>
       </c>
       <c r="X423" t="n">
@@ -66986,41 +66986,41 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>JALAWA II</t>
+          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>19/43/13/004</t>
+          <t>19/43/14/006</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09a</t>
+          <t>6a35c3f587b1768452f7b183</t>
         </is>
       </c>
       <c r="L424" t="n">
-        <v>64756</v>
+        <v>151226</v>
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr">
         <is>
-          <t>1781977012376</t>
+          <t>1781968195719</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -67045,7 +67045,7 @@
       <c r="V424" t="inlineStr"/>
       <c r="W424" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
         </is>
       </c>
       <c r="X424" t="n">
@@ -67143,41 +67143,41 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>WARAWA I</t>
+          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>19/43/13/005</t>
+          <t>19/43/14/007</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b099</t>
+          <t>6a35c3f587b1768452f7b182</t>
         </is>
       </c>
       <c r="L425" t="n">
-        <v>64757</v>
+        <v>151227</v>
       </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr">
         <is>
-          <t>1781977113973</t>
+          <t>1781974982952</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -67202,7 +67202,7 @@
       <c r="V425" t="inlineStr"/>
       <c r="W425" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
         </is>
       </c>
       <c r="X425" t="n">
@@ -67300,41 +67300,41 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>WARAWA II</t>
+          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>19/43/13/006</t>
+          <t>19/43/14/008</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09d</t>
+          <t>6a35c3f587b1768452f7b181</t>
         </is>
       </c>
       <c r="L426" t="n">
-        <v>64758</v>
+        <v>151228</v>
       </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
-          <t>1781976876830</t>
+          <t>1781968682952</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -67359,7 +67359,7 @@
       <c r="V426" t="inlineStr"/>
       <c r="W426" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
         </is>
       </c>
       <c r="X426" t="n">
@@ -67457,41 +67457,41 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
+          <t>ALIMAWA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>19/43/13/007</t>
+          <t>19/43/15/001</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09f</t>
+          <t>6a35c3f587b1768452f7b1fd</t>
         </is>
       </c>
       <c r="L427" t="n">
-        <v>151223</v>
+        <v>64764</v>
       </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr">
         <is>
-          <t>1781976882480</t>
+          <t>1781968165832</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -67516,7 +67516,7 @@
       <c r="V427" t="inlineStr"/>
       <c r="W427" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
         </is>
       </c>
       <c r="X427" t="n">
@@ -67614,72 +67614,66 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
+          <t>BUROMAWA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>19/43/13/008</t>
+          <t>19/43/15/002</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b0a0</t>
+          <t>6a35c3f587b1768452f7b1fc</t>
         </is>
       </c>
       <c r="L428" t="n">
-        <v>151224</v>
-      </c>
-      <c r="M428" t="n">
-        <v>1781968214959</v>
-      </c>
+        <v>64765</v>
+      </c>
+      <c r="M428" t="inlineStr"/>
       <c r="N428" t="inlineStr">
         <is>
-          <t>1781968212953</t>
+          <t>1781974266039</t>
         </is>
       </c>
       <c r="O428" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P428" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q428" t="n">
-        <v>3</v>
-      </c>
-      <c r="R428" t="inlineStr">
-        <is>
-          <t>6a36ad5552b6362accb5c7d0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R428" t="inlineStr"/>
       <c r="S428" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T428" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="U428" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V428" t="inlineStr"/>
       <c r="W428" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
         </is>
       </c>
       <c r="X428" t="n">
@@ -67698,7 +67692,7 @@
         <v>0</v>
       </c>
       <c r="AC428" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD428" t="n">
         <v>0</v>
@@ -67777,41 +67771,41 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
+          <t>GIWARAN ALITINI I</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>19/43/13/009</t>
+          <t>19/43/15/003</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09e</t>
+          <t>6a35c3f587b1768452f7b1fe</t>
         </is>
       </c>
       <c r="L429" t="n">
-        <v>151225</v>
+        <v>64766</v>
       </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr">
         <is>
-          <t>1781968282375</t>
+          <t>1781976840577</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -67836,7 +67830,7 @@
       <c r="V429" t="inlineStr"/>
       <c r="W429" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
         </is>
       </c>
       <c r="X429" t="n">
@@ -67934,41 +67928,41 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>GUMAKA</t>
+          <t>GIWARAN ALITINI II</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>19/43/14/001</t>
+          <t>19/43/15/004</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17e</t>
+          <t>6a35c3f587b1768452f7b1fb</t>
         </is>
       </c>
       <c r="L430" t="n">
-        <v>64759</v>
+        <v>64767</v>
       </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr">
         <is>
-          <t>1781975166154</t>
+          <t>1781968281024</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -67993,7 +67987,7 @@
       <c r="V430" t="inlineStr"/>
       <c r="W430" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
         </is>
       </c>
       <c r="X430" t="n">
@@ -68091,41 +68085,41 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>KANWA</t>
+          <t>GIWARAN JIJIYAWA I</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>19/43/14/002</t>
+          <t>19/43/15/005</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17c</t>
+          <t>6a35c3f587b1768452f7b1ff</t>
         </is>
       </c>
       <c r="L431" t="n">
-        <v>64760</v>
+        <v>64768</v>
       </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr">
         <is>
-          <t>1781974985005</t>
+          <t>1781974266070</t>
         </is>
       </c>
       <c r="O431" t="n">
@@ -68150,7 +68144,7 @@
       <c r="V431" t="inlineStr"/>
       <c r="W431" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
         </is>
       </c>
       <c r="X431" t="n">
@@ -68248,41 +68242,41 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>POLICE ACADEMY</t>
+          <t>GIWARAN JIJIYAWA II</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>19/43/14/003</t>
+          <t>19/43/15/006</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17d</t>
+          <t>6a35c3f587b1768452f7b200</t>
         </is>
       </c>
       <c r="L432" t="n">
-        <v>64761</v>
+        <v>64769</v>
       </c>
       <c r="M432" t="inlineStr"/>
       <c r="N432" t="inlineStr">
         <is>
-          <t>1781975165502</t>
+          <t>1781974447124</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -68307,7 +68301,7 @@
       <c r="V432" t="inlineStr"/>
       <c r="W432" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
         </is>
       </c>
       <c r="X432" t="n">
@@ -68405,41 +68399,41 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>'YANDALLA</t>
+          <t>'YANGIZO I</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>19/43/14/004</t>
+          <t>19/43/15/007</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17f</t>
+          <t>6a35c3f587b1768452f7b1f8</t>
         </is>
       </c>
       <c r="L433" t="n">
-        <v>64762</v>
+        <v>64770</v>
       </c>
       <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr">
         <is>
-          <t>1781975169663</t>
+          <t>1781974628327</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -68464,7 +68458,7 @@
       <c r="V433" t="inlineStr"/>
       <c r="W433" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
         </is>
       </c>
       <c r="X433" t="n">
@@ -68562,41 +68556,41 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>'YANDALLA II</t>
+          <t>'YANGIZO II</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>19/43/14/005</t>
+          <t>19/43/15/008</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b180</t>
+          <t>6a35c3f587b1768452f7b1f9</t>
         </is>
       </c>
       <c r="L434" t="n">
-        <v>64763</v>
+        <v>64771</v>
       </c>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr">
         <is>
-          <t>1781968201933</t>
+          <t>1781974630372</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -68621,7 +68615,7 @@
       <c r="V434" t="inlineStr"/>
       <c r="W434" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
         </is>
       </c>
       <c r="X434" t="n">
@@ -68719,41 +68713,41 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
+          <t>'YANGIZO III</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>19/43/14/006</t>
+          <t>19/43/15/009</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b183</t>
+          <t>6a35c3f587b1768452f7b1fa</t>
         </is>
       </c>
       <c r="L435" t="n">
-        <v>151226</v>
+        <v>64772</v>
       </c>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr">
         <is>
-          <t>1781968195719</t>
+          <t>1781968246493</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -68778,7 +68772,7 @@
       <c r="V435" t="inlineStr"/>
       <c r="W435" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
         </is>
       </c>
       <c r="X435" t="n">
@@ -68876,41 +68870,41 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf38f77bb3acad0a012</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
+          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>19/43/14/007</t>
+          <t>19/43/15/010</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b182</t>
+          <t>6a35c3f587b1768452f7b201</t>
         </is>
       </c>
       <c r="L436" t="n">
-        <v>151227</v>
+        <v>151229</v>
       </c>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr">
         <is>
-          <t>1781974982952</t>
+          <t>1781974627113</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -68935,7 +68929,7 @@
       <c r="V436" t="inlineStr"/>
       <c r="W436" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
         </is>
       </c>
       <c r="X436" t="n">
@@ -69002,1733 +68996,6 @@
         <v>0</v>
       </c>
       <c r="AS436" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>YAN DALLA</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
-        </is>
-      </c>
-      <c r="I437" t="inlineStr">
-        <is>
-          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
-        </is>
-      </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>19/43/14/008</t>
-        </is>
-      </c>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b181</t>
-        </is>
-      </c>
-      <c r="L437" t="n">
-        <v>151228</v>
-      </c>
-      <c r="M437" t="inlineStr"/>
-      <c r="N437" t="inlineStr">
-        <is>
-          <t>1781968682952</t>
-        </is>
-      </c>
-      <c r="O437" t="n">
-        <v>0</v>
-      </c>
-      <c r="P437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
-      <c r="R437" t="inlineStr"/>
-      <c r="S437" t="n">
-        <v>0</v>
-      </c>
-      <c r="T437" t="n">
-        <v>0</v>
-      </c>
-      <c r="U437" t="n">
-        <v>0</v>
-      </c>
-      <c r="V437" t="inlineStr"/>
-      <c r="W437" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
-        </is>
-      </c>
-      <c r="X437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y437" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR437" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS437" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>ALIMAWA</t>
-        </is>
-      </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>19/43/15/001</t>
-        </is>
-      </c>
-      <c r="K438" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fd</t>
-        </is>
-      </c>
-      <c r="L438" t="n">
-        <v>64764</v>
-      </c>
-      <c r="M438" t="inlineStr"/>
-      <c r="N438" t="inlineStr">
-        <is>
-          <t>1781968165832</t>
-        </is>
-      </c>
-      <c r="O438" t="n">
-        <v>0</v>
-      </c>
-      <c r="P438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
-      <c r="R438" t="inlineStr"/>
-      <c r="S438" t="n">
-        <v>0</v>
-      </c>
-      <c r="T438" t="n">
-        <v>0</v>
-      </c>
-      <c r="U438" t="n">
-        <v>0</v>
-      </c>
-      <c r="V438" t="inlineStr"/>
-      <c r="W438" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
-        </is>
-      </c>
-      <c r="X438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y438" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR438" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS438" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I439" t="inlineStr">
-        <is>
-          <t>BUROMAWA</t>
-        </is>
-      </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>19/43/15/002</t>
-        </is>
-      </c>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fc</t>
-        </is>
-      </c>
-      <c r="L439" t="n">
-        <v>64765</v>
-      </c>
-      <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>1781974266039</t>
-        </is>
-      </c>
-      <c r="O439" t="n">
-        <v>0</v>
-      </c>
-      <c r="P439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q439" t="n">
-        <v>0</v>
-      </c>
-      <c r="R439" t="inlineStr"/>
-      <c r="S439" t="n">
-        <v>0</v>
-      </c>
-      <c r="T439" t="n">
-        <v>0</v>
-      </c>
-      <c r="U439" t="n">
-        <v>0</v>
-      </c>
-      <c r="V439" t="inlineStr"/>
-      <c r="W439" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
-        </is>
-      </c>
-      <c r="X439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y439" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR439" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS439" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>GIWARAN ALITINI I</t>
-        </is>
-      </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>19/43/15/003</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fe</t>
-        </is>
-      </c>
-      <c r="L440" t="n">
-        <v>64766</v>
-      </c>
-      <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr">
-        <is>
-          <t>1781976840577</t>
-        </is>
-      </c>
-      <c r="O440" t="n">
-        <v>0</v>
-      </c>
-      <c r="P440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
-      <c r="R440" t="inlineStr"/>
-      <c r="S440" t="n">
-        <v>0</v>
-      </c>
-      <c r="T440" t="n">
-        <v>0</v>
-      </c>
-      <c r="U440" t="n">
-        <v>0</v>
-      </c>
-      <c r="V440" t="inlineStr"/>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
-        </is>
-      </c>
-      <c r="X440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y440" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR440" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS440" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>GIWARAN ALITINI II</t>
-        </is>
-      </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>19/43/15/004</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fb</t>
-        </is>
-      </c>
-      <c r="L441" t="n">
-        <v>64767</v>
-      </c>
-      <c r="M441" t="inlineStr"/>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>1781968281024</t>
-        </is>
-      </c>
-      <c r="O441" t="n">
-        <v>0</v>
-      </c>
-      <c r="P441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
-      <c r="R441" t="inlineStr"/>
-      <c r="S441" t="n">
-        <v>0</v>
-      </c>
-      <c r="T441" t="n">
-        <v>0</v>
-      </c>
-      <c r="U441" t="n">
-        <v>0</v>
-      </c>
-      <c r="V441" t="inlineStr"/>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
-        </is>
-      </c>
-      <c r="X441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y441" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR441" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS441" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>GIWARAN JIJIYAWA I</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>19/43/15/005</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1ff</t>
-        </is>
-      </c>
-      <c r="L442" t="n">
-        <v>64768</v>
-      </c>
-      <c r="M442" t="inlineStr"/>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>1781974266070</t>
-        </is>
-      </c>
-      <c r="O442" t="n">
-        <v>0</v>
-      </c>
-      <c r="P442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
-      <c r="R442" t="inlineStr"/>
-      <c r="S442" t="n">
-        <v>0</v>
-      </c>
-      <c r="T442" t="n">
-        <v>0</v>
-      </c>
-      <c r="U442" t="n">
-        <v>0</v>
-      </c>
-      <c r="V442" t="inlineStr"/>
-      <c r="W442" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
-        </is>
-      </c>
-      <c r="X442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y442" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR442" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS442" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>GIWARAN JIJIYAWA II</t>
-        </is>
-      </c>
-      <c r="J443" t="inlineStr">
-        <is>
-          <t>19/43/15/006</t>
-        </is>
-      </c>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b200</t>
-        </is>
-      </c>
-      <c r="L443" t="n">
-        <v>64769</v>
-      </c>
-      <c r="M443" t="inlineStr"/>
-      <c r="N443" t="inlineStr">
-        <is>
-          <t>1781974447124</t>
-        </is>
-      </c>
-      <c r="O443" t="n">
-        <v>0</v>
-      </c>
-      <c r="P443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q443" t="n">
-        <v>0</v>
-      </c>
-      <c r="R443" t="inlineStr"/>
-      <c r="S443" t="n">
-        <v>0</v>
-      </c>
-      <c r="T443" t="n">
-        <v>0</v>
-      </c>
-      <c r="U443" t="n">
-        <v>0</v>
-      </c>
-      <c r="V443" t="inlineStr"/>
-      <c r="W443" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
-        </is>
-      </c>
-      <c r="X443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y443" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR443" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS443" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I444" t="inlineStr">
-        <is>
-          <t>'YANGIZO I</t>
-        </is>
-      </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>19/43/15/007</t>
-        </is>
-      </c>
-      <c r="K444" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1f8</t>
-        </is>
-      </c>
-      <c r="L444" t="n">
-        <v>64770</v>
-      </c>
-      <c r="M444" t="inlineStr"/>
-      <c r="N444" t="inlineStr">
-        <is>
-          <t>1781974628327</t>
-        </is>
-      </c>
-      <c r="O444" t="n">
-        <v>0</v>
-      </c>
-      <c r="P444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q444" t="n">
-        <v>0</v>
-      </c>
-      <c r="R444" t="inlineStr"/>
-      <c r="S444" t="n">
-        <v>0</v>
-      </c>
-      <c r="T444" t="n">
-        <v>0</v>
-      </c>
-      <c r="U444" t="n">
-        <v>0</v>
-      </c>
-      <c r="V444" t="inlineStr"/>
-      <c r="W444" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
-        </is>
-      </c>
-      <c r="X444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y444" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR444" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS444" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>'YANGIZO II</t>
-        </is>
-      </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>19/43/15/008</t>
-        </is>
-      </c>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1f9</t>
-        </is>
-      </c>
-      <c r="L445" t="n">
-        <v>64771</v>
-      </c>
-      <c r="M445" t="inlineStr"/>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>1781974630372</t>
-        </is>
-      </c>
-      <c r="O445" t="n">
-        <v>0</v>
-      </c>
-      <c r="P445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
-      <c r="R445" t="inlineStr"/>
-      <c r="S445" t="n">
-        <v>0</v>
-      </c>
-      <c r="T445" t="n">
-        <v>0</v>
-      </c>
-      <c r="U445" t="n">
-        <v>0</v>
-      </c>
-      <c r="V445" t="inlineStr"/>
-      <c r="W445" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
-        </is>
-      </c>
-      <c r="X445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y445" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR445" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS445" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>'YANGIZO III</t>
-        </is>
-      </c>
-      <c r="J446" t="inlineStr">
-        <is>
-          <t>19/43/15/009</t>
-        </is>
-      </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b1fa</t>
-        </is>
-      </c>
-      <c r="L446" t="n">
-        <v>64772</v>
-      </c>
-      <c r="M446" t="inlineStr"/>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>1781968246493</t>
-        </is>
-      </c>
-      <c r="O446" t="n">
-        <v>0</v>
-      </c>
-      <c r="P446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
-      <c r="R446" t="inlineStr"/>
-      <c r="S446" t="n">
-        <v>0</v>
-      </c>
-      <c r="T446" t="n">
-        <v>0</v>
-      </c>
-      <c r="U446" t="n">
-        <v>0</v>
-      </c>
-      <c r="V446" t="inlineStr"/>
-      <c r="W446" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
-        </is>
-      </c>
-      <c r="X446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y446" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR446" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS446" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>6a35c3e587b1768452f7b027</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>2026-06-19T23:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
-        </is>
-      </c>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
-        </is>
-      </c>
-      <c r="J447" t="inlineStr">
-        <is>
-          <t>19/43/15/010</t>
-        </is>
-      </c>
-      <c r="K447" t="inlineStr">
-        <is>
-          <t>6a35c3f587b1768452f7b201</t>
-        </is>
-      </c>
-      <c r="L447" t="n">
-        <v>151229</v>
-      </c>
-      <c r="M447" t="inlineStr"/>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>1781974627113</t>
-        </is>
-      </c>
-      <c r="O447" t="n">
-        <v>0</v>
-      </c>
-      <c r="P447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
-      <c r="R447" t="inlineStr"/>
-      <c r="S447" t="n">
-        <v>0</v>
-      </c>
-      <c r="T447" t="n">
-        <v>0</v>
-      </c>
-      <c r="U447" t="n">
-        <v>0</v>
-      </c>
-      <c r="V447" t="inlineStr"/>
-      <c r="W447" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
-        </is>
-      </c>
-      <c r="X447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y447" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR447" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS447" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70743,7 +69010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73461,26 +71728,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KATARKAWA</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -73498,7 +71765,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -73549,10 +71816,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>100</v>
@@ -73571,7 +71838,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -73659,10 +71926,10 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
         <v>100</v>
@@ -73681,7 +71948,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -73769,13 +72036,13 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28">
@@ -73791,26 +72058,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -73828,7 +72095,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -73879,13 +72146,13 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -73901,26 +72168,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -73938,7 +72205,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -73989,10 +72256,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH29" t="n">
         <v>100</v>
@@ -74011,7 +72278,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>YANGIZO</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -74099,122 +72366,12 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Kano</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>WARAWA</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>YANGIZO</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH31" t="n">
         <v>100</v>
       </c>
     </row>
@@ -74516,22 +72673,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3131</v>
+        <v>2896</v>
       </c>
       <c r="D3" t="n">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="G3" t="n">
-        <v>3089</v>
+        <v>2854</v>
       </c>
       <c r="H3" t="n">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -74549,7 +72706,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -74600,13 +72757,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="AF3" t="n">
         <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>99.3</v>
+        <v>107.6</v>
       </c>
     </row>
   </sheetData>
@@ -74797,22 +72954,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7311</v>
+        <v>7076</v>
       </c>
       <c r="C2" t="n">
-        <v>984</v>
+        <v>951</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>965</v>
+        <v>934</v>
       </c>
       <c r="F2" t="n">
-        <v>7269</v>
+        <v>7034</v>
       </c>
       <c r="G2" t="n">
-        <v>958</v>
+        <v>927</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -74830,7 +72987,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>949</v>
+        <v>918</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -74881,16 +73038,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AE2" t="n">
         <v>445</v>
       </c>
       <c r="AF2" t="n">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AG2" t="n">
-        <v>99.8</v>
+        <v>102.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/Kano/results.xlsx
+++ b/output/Kano/results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS436"/>
+  <dimension ref="A1:AS447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59138,41 +59138,41 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>GANAKAKUN I</t>
+          <t>DANHAWAGIWA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>19/43/10/001</t>
+          <t>19/43/09/001</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cf</t>
+          <t>6a35c3f587b1768452f7b213</t>
         </is>
       </c>
       <c r="L374" t="n">
-        <v>64722</v>
+        <v>64714</v>
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr">
         <is>
-          <t>1781968221436</t>
+          <t>1781970484687</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -59197,7 +59197,7 @@
       <c r="V374" t="inlineStr"/>
       <c r="W374" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64624/70cd1307-d7d8-4a4d-8f5c-53964dbc4cd9.jpg</t>
         </is>
       </c>
       <c r="X374" t="n">
@@ -59295,41 +59295,41 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>GANAKAKUN II</t>
+          <t>GISHIRI WUYA I</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>19/43/10/002</t>
+          <t>19/43/09/002</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ce</t>
+          <t>6a35c3f587b1768452f7b215</t>
         </is>
       </c>
       <c r="L375" t="n">
-        <v>64723</v>
+        <v>64715</v>
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr">
         <is>
-          <t>1781968244797</t>
+          <t>1781970664668</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -59354,7 +59354,7 @@
       <c r="V375" t="inlineStr"/>
       <c r="W375" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64625/1df8c5ea-4859-4f83-89aa-d0c6aefc4e2a.jpg</t>
         </is>
       </c>
       <c r="X375" t="n">
@@ -59452,66 +59452,72 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>MADARIN MABA I</t>
+          <t>GISHIRI WUYA II</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>19/43/10/003</t>
+          <t>19/43/09/003</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d3</t>
+          <t>6a35c3f587b1768452f7b217</t>
         </is>
       </c>
       <c r="L376" t="n">
-        <v>64724</v>
-      </c>
-      <c r="M376" t="inlineStr"/>
+        <v>64716</v>
+      </c>
+      <c r="M376" t="n">
+        <v>1781969584429</v>
+      </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>1781968265095</t>
+          <t>1781969583795</t>
         </is>
       </c>
       <c r="O376" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="P376" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q376" t="n">
         <v>0</v>
       </c>
-      <c r="R376" t="inlineStr"/>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>6a36b2af52b6362accb5cc50</t>
+        </is>
+      </c>
       <c r="S376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="T376" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="U376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64626/b615548b-a67c-49b5-8408-3ff1ecddeb6d.jpg</t>
         </is>
       </c>
       <c r="X376" t="n">
@@ -59530,7 +59536,7 @@
         <v>0</v>
       </c>
       <c r="AC376" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD376" t="n">
         <v>0</v>
@@ -59609,41 +59615,41 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>MADARIN MABA II</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>19/43/10/004</t>
+          <t>19/43/09/004</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d0</t>
+          <t>6a35c3f587b1768452f7b210</t>
         </is>
       </c>
       <c r="L377" t="n">
-        <v>64725</v>
+        <v>64717</v>
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr">
         <is>
-          <t>1781971564529</t>
+          <t>1781976885564</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -59668,7 +59674,7 @@
       <c r="V377" t="inlineStr"/>
       <c r="W377" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64627/8e305834-fd28-46da-98c8-7eaf22d37821.jpg</t>
         </is>
       </c>
       <c r="X377" t="n">
@@ -59766,41 +59772,41 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>MADARIN MABA III</t>
+          <t>KINCHAU</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>19/43/10/005</t>
+          <t>19/43/09/005</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d2</t>
+          <t>6a35c3f587b1768452f7b212</t>
         </is>
       </c>
       <c r="L378" t="n">
-        <v>64726</v>
+        <v>64718</v>
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr">
         <is>
-          <t>1781971929292</t>
+          <t>1781976801113</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -59825,7 +59831,7 @@
       <c r="V378" t="inlineStr"/>
       <c r="W378" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64628/a75abbbf-9dae-4fbd-9025-73135eab4236.jpg</t>
         </is>
       </c>
       <c r="X378" t="n">
@@ -59923,41 +59929,41 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>MARAYAR WUTA</t>
+          <t>NAIRA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>19/43/10/006</t>
+          <t>19/43/09/006</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cd</t>
+          <t>6a35c3f587b1768452f7b214</t>
         </is>
       </c>
       <c r="L379" t="n">
-        <v>64727</v>
+        <v>64719</v>
       </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr">
         <is>
-          <t>1781971930377</t>
+          <t>1781976797855</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -59982,7 +59988,7 @@
       <c r="V379" t="inlineStr"/>
       <c r="W379" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64629/1a870077-7f2f-4827-b3c0-82b15fd5388d.jpg</t>
         </is>
       </c>
       <c r="X379" t="n">
@@ -60080,41 +60086,41 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>SABON GARIN NASARA</t>
+          <t>TURBA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>19/43/10/007</t>
+          <t>19/43/09/007</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1cc</t>
+          <t>6a35c3f587b1768452f7b211</t>
         </is>
       </c>
       <c r="L380" t="n">
-        <v>64728</v>
+        <v>64720</v>
       </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr">
         <is>
-          <t>1781971922925</t>
+          <t>1781970126235</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -60139,7 +60145,7 @@
       <c r="V380" t="inlineStr"/>
       <c r="W380" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64630/87bf41a6-80ef-4848-aa12-c1b266c40130.jpg</t>
         </is>
       </c>
       <c r="X380" t="n">
@@ -60237,41 +60243,41 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>TALAWA</t>
+          <t>WALAGIGI</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>19/43/10/008</t>
+          <t>19/43/09/008</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d1</t>
+          <t>6a35c3f587b1768452f7b216</t>
         </is>
       </c>
       <c r="L381" t="n">
-        <v>64729</v>
+        <v>64721</v>
       </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr">
         <is>
-          <t>1781968262106</t>
+          <t>1781973924024</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -60296,7 +60302,7 @@
       <c r="V381" t="inlineStr"/>
       <c r="W381" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/64631/7fd4d2b1-fc11-41e9-b238-faacf20264bc.jpg</t>
         </is>
       </c>
       <c r="X381" t="n">
@@ -60394,41 +60400,41 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>DANHAWAN GIWA II (KATARKAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>19/43/10/009</t>
+          <t>19/43/09/009</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d5</t>
+          <t>6a35c3f587b1768452f7b219</t>
         </is>
       </c>
       <c r="L382" t="n">
-        <v>151218</v>
+        <v>151215</v>
       </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr">
         <is>
-          <t>1781972103434</t>
+          <t>1781976919845</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -60453,7 +60459,7 @@
       <c r="V382" t="inlineStr"/>
       <c r="W382" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646502/b691bc55-9619-4cac-9086-625a1b6733e7.jpg</t>
         </is>
       </c>
       <c r="X382" t="n">
@@ -60551,41 +60557,41 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00d</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
+          <t>KATARKAWA GARI (NURUL HUDA ISLAMIYYA KATARKAWA)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>19/43/10/010</t>
+          <t>19/43/09/010</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1d4</t>
+          <t>6a35c3f587b1768452f7b218</t>
         </is>
       </c>
       <c r="L383" t="n">
-        <v>151219</v>
+        <v>151216</v>
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr">
         <is>
-          <t>1781972285399</t>
+          <t>1781973731518</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -60610,7 +60616,7 @@
       <c r="V383" t="inlineStr"/>
       <c r="W383" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646503/2b611837-2b29-42a8-9058-9e3d68f8b5c9.jpg</t>
         </is>
       </c>
       <c r="X383" t="n">
@@ -60708,41 +60714,41 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00c</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>FARTAWA</t>
+          <t>KINCHAU II (KINCHAU PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>19/43/11/001</t>
+          <t>19/43/09/011</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21c</t>
+          <t>6a35c3f587b1768452f7b21a</t>
         </is>
       </c>
       <c r="L384" t="n">
-        <v>64730</v>
+        <v>151217</v>
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr">
         <is>
-          <t>1781977074928</t>
+          <t>1781977138945</t>
         </is>
       </c>
       <c r="O384" t="n">
@@ -60767,7 +60773,7 @@
       <c r="V384" t="inlineStr"/>
       <c r="W384" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4724/646504/7f254219-3e51-4120-bd54-f94180177cd2.jpg</t>
         </is>
       </c>
       <c r="X384" t="n">
@@ -60865,41 +60871,41 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS I</t>
+          <t>GANAKAKUN I</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>19/43/11/002</t>
+          <t>19/43/10/001</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b223</t>
+          <t>6a35c3f587b1768452f7b1cf</t>
         </is>
       </c>
       <c r="L385" t="n">
-        <v>64731</v>
+        <v>64722</v>
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr">
         <is>
-          <t>1781977113305</t>
+          <t>1781968221436</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -60924,7 +60930,7 @@
       <c r="V385" t="inlineStr"/>
       <c r="W385" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64632/3b62561b-655d-4fe3-b355-e53260514cc0.jpg</t>
         </is>
       </c>
       <c r="X385" t="n">
@@ -61022,41 +61028,41 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS II</t>
+          <t>GANAKAKUN II</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>19/43/11/003</t>
+          <t>19/43/10/002</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21b</t>
+          <t>6a35c3f587b1768452f7b1ce</t>
         </is>
       </c>
       <c r="L386" t="n">
-        <v>64732</v>
+        <v>64723</v>
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr">
         <is>
-          <t>1781977075062</t>
+          <t>1781968244797</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -61081,7 +61087,7 @@
       <c r="V386" t="inlineStr"/>
       <c r="W386" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64633/5c2df62a-9143-47a7-8460-9a8646619f15.jpg</t>
         </is>
       </c>
       <c r="X386" t="n">
@@ -61179,41 +61185,41 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>UNGUWAR ZURURU</t>
+          <t>MADARIN MABA I</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>19/43/11/004</t>
+          <t>19/43/10/003</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b222</t>
+          <t>6a35c3f587b1768452f7b1d3</t>
         </is>
       </c>
       <c r="L387" t="n">
-        <v>64733</v>
+        <v>64724</v>
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr">
         <is>
-          <t>1781975346942</t>
+          <t>1781968265095</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -61238,7 +61244,7 @@
       <c r="V387" t="inlineStr"/>
       <c r="W387" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64634/e8a9cb61-181f-4d87-b70f-449e75a5e2ae.jpg</t>
         </is>
       </c>
       <c r="X387" t="n">
@@ -61336,41 +61342,41 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>YANDADI I</t>
+          <t>MADARIN MABA II</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>19/43/11/005</t>
+          <t>19/43/10/004</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b221</t>
+          <t>6a35c3f587b1768452f7b1d0</t>
         </is>
       </c>
       <c r="L388" t="n">
-        <v>64734</v>
+        <v>64725</v>
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr">
         <is>
-          <t>1781975887400</t>
+          <t>1781971564529</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -61395,7 +61401,7 @@
       <c r="V388" t="inlineStr"/>
       <c r="W388" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64635/54551ac3-8f0f-4845-bbd7-aa46752921ee.jpg</t>
         </is>
       </c>
       <c r="X388" t="n">
@@ -61493,41 +61499,41 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>YANDADI II</t>
+          <t>MADARIN MABA III</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>19/43/11/006</t>
+          <t>19/43/10/005</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21e</t>
+          <t>6a35c3f587b1768452f7b1d2</t>
         </is>
       </c>
       <c r="L389" t="n">
-        <v>64735</v>
+        <v>64726</v>
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr">
         <is>
-          <t>1782131641877</t>
+          <t>1781971929292</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -61552,7 +61558,7 @@
       <c r="V389" t="inlineStr"/>
       <c r="W389" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64636/8d5b87db-edd5-421c-8864-e4b6d0ea9484.jpg</t>
         </is>
       </c>
       <c r="X389" t="n">
@@ -61650,41 +61656,41 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>YADAUDU I</t>
+          <t>MARAYAR WUTA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>19/43/11/007</t>
+          <t>19/43/10/006</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b220</t>
+          <t>6a35c3f587b1768452f7b1cd</t>
         </is>
       </c>
       <c r="L390" t="n">
-        <v>64736</v>
+        <v>64727</v>
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr">
         <is>
-          <t>1781989191145</t>
+          <t>1781971930377</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -61709,7 +61715,7 @@
       <c r="V390" t="inlineStr"/>
       <c r="W390" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64637/050779bd-644f-4a5b-b732-89dc6d56c670.jpg</t>
         </is>
       </c>
       <c r="X390" t="n">
@@ -61807,41 +61813,41 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>YADAUDU II</t>
+          <t>SABON GARIN NASARA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>19/43/11/008</t>
+          <t>19/43/10/007</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21f</t>
+          <t>6a35c3f587b1768452f7b1cc</t>
         </is>
       </c>
       <c r="L391" t="n">
-        <v>64737</v>
+        <v>64728</v>
       </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr">
         <is>
-          <t>1781976878903</t>
+          <t>1781971922925</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -61866,7 +61872,7 @@
       <c r="V391" t="inlineStr"/>
       <c r="W391" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64638/a55339a4-2327-4cf1-9695-cc8c17e2c930.jpg</t>
         </is>
       </c>
       <c r="X391" t="n">
@@ -61964,41 +61970,41 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>ZANGO DANMARKE</t>
+          <t>TALAWA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>19/43/11/009</t>
+          <t>19/43/10/008</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b21d</t>
+          <t>6a35c3f587b1768452f7b1d1</t>
         </is>
       </c>
       <c r="L392" t="n">
-        <v>64738</v>
+        <v>64729</v>
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr">
         <is>
-          <t>1781976780359</t>
+          <t>1781968262106</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -62023,7 +62029,7 @@
       <c r="V392" t="inlineStr"/>
       <c r="W392" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/64639/8f5fcc71-7a9d-4c8a-8093-6fd37923fde9.jpg</t>
         </is>
       </c>
       <c r="X392" t="n">
@@ -62121,41 +62127,41 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
+          <t>MADARIN MATA IV (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>19/43/11/010</t>
+          <t>19/43/10/009</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b224</t>
+          <t>6a35c3f587b1768452f7b1d5</t>
         </is>
       </c>
       <c r="L393" t="n">
-        <v>151220</v>
+        <v>151218</v>
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr">
         <is>
-          <t>1781977094685</t>
+          <t>1781972103434</t>
         </is>
       </c>
       <c r="O393" t="n">
@@ -62180,7 +62186,7 @@
       <c r="V393" t="inlineStr"/>
       <c r="W393" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646505/cf6c98ff-500f-45ec-8dd2-01115ab808d2.jpg</t>
         </is>
       </c>
       <c r="X393" t="n">
@@ -62278,41 +62284,41 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00e</t>
+          <t>5f0f3cf28f77bb3acad0a00d</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
+          <t>MADARIN MATA V (MADARIN MATA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>19/43/11/011</t>
+          <t>19/43/10/010</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b225</t>
+          <t>6a35c3f587b1768452f7b1d4</t>
         </is>
       </c>
       <c r="L394" t="n">
-        <v>151221</v>
+        <v>151219</v>
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr">
         <is>
-          <t>1781976782683</t>
+          <t>1781972285399</t>
         </is>
       </c>
       <c r="O394" t="n">
@@ -62337,7 +62343,7 @@
       <c r="V394" t="inlineStr"/>
       <c r="W394" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4725/646506/3aab3f6c-045d-4151-b266-7cbecfe080e9.jpg</t>
         </is>
       </c>
       <c r="X394" t="n">
@@ -62435,41 +62441,41 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>CHARKA</t>
+          <t>FARTAWA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>19/43/12/001</t>
+          <t>19/43/11/001</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b171</t>
+          <t>6a35c3f587b1768452f7b21c</t>
         </is>
       </c>
       <c r="L395" t="n">
-        <v>64739</v>
+        <v>64730</v>
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr">
         <is>
-          <t>1781976872268</t>
+          <t>1781977074928</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -62494,7 +62500,7 @@
       <c r="V395" t="inlineStr"/>
       <c r="W395" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64640/e348add5-8b87-4ad5-9921-77bdb90d0f83.jpg</t>
         </is>
       </c>
       <c r="X395" t="n">
@@ -62592,41 +62598,41 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>DANFARI I</t>
+          <t>TAMBURAWAR GABAS I</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>19/43/12/002</t>
+          <t>19/43/11/002</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16d</t>
+          <t>6a35c3f587b1768452f7b223</t>
         </is>
       </c>
       <c r="L396" t="n">
-        <v>64740</v>
+        <v>64731</v>
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr">
         <is>
-          <t>1781976901500</t>
+          <t>1781977113305</t>
         </is>
       </c>
       <c r="O396" t="n">
@@ -62651,7 +62657,7 @@
       <c r="V396" t="inlineStr"/>
       <c r="W396" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64641/a27d5955-80bb-4f4c-afe6-86f0815cf3f7.jpg</t>
         </is>
       </c>
       <c r="X396" t="n">
@@ -62749,41 +62755,41 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>DANFARI II</t>
+          <t>TAMBURAWAR GABAS II</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>19/43/12/003</t>
+          <t>19/43/11/003</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b175</t>
+          <t>6a35c3f587b1768452f7b21b</t>
         </is>
       </c>
       <c r="L397" t="n">
-        <v>64741</v>
+        <v>64732</v>
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr">
         <is>
-          <t>1781968309565</t>
+          <t>1781977075062</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -62808,7 +62814,7 @@
       <c r="V397" t="inlineStr"/>
       <c r="W397" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64642/125b94db-9702-4749-868a-b9168d139802.jpg</t>
         </is>
       </c>
       <c r="X397" t="n">
@@ -62906,41 +62912,41 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>DANTSAWA</t>
+          <t>UNGUWAR ZURURU</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>19/43/12/004</t>
+          <t>19/43/11/004</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b170</t>
+          <t>6a35c3f587b1768452f7b222</t>
         </is>
       </c>
       <c r="L398" t="n">
-        <v>64742</v>
+        <v>64733</v>
       </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr">
         <is>
-          <t>1781968186810</t>
+          <t>1781975346942</t>
         </is>
       </c>
       <c r="O398" t="n">
@@ -62965,7 +62971,7 @@
       <c r="V398" t="inlineStr"/>
       <c r="W398" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64643/49a417c9-faaa-4c0c-bca7-f4831e278e42.jpg</t>
         </is>
       </c>
       <c r="X398" t="n">
@@ -63063,41 +63069,41 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>HALADAWA</t>
+          <t>YANDADI I</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>19/43/12/005</t>
+          <t>19/43/11/005</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b179</t>
+          <t>6a35c3f587b1768452f7b221</t>
         </is>
       </c>
       <c r="L399" t="n">
-        <v>64743</v>
+        <v>64734</v>
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr">
         <is>
-          <t>1781976861221</t>
+          <t>1781975887400</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -63122,7 +63128,7 @@
       <c r="V399" t="inlineStr"/>
       <c r="W399" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64644/ae094b1c-861f-466e-94a5-a73591f7351b.jpg</t>
         </is>
       </c>
       <c r="X399" t="n">
@@ -63220,41 +63226,41 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>HAYIN WAZO</t>
+          <t>YANDADI II</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>19/43/12/006</t>
+          <t>19/43/11/006</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16f</t>
+          <t>6a35c3f587b1768452f7b21e</t>
         </is>
       </c>
       <c r="L400" t="n">
-        <v>64744</v>
+        <v>64735</v>
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr">
         <is>
-          <t>1781976900341</t>
+          <t>1782131641877</t>
         </is>
       </c>
       <c r="O400" t="n">
@@ -63279,7 +63285,7 @@
       <c r="V400" t="inlineStr"/>
       <c r="W400" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64645/fd403a17-caa8-4daf-b3a8-29301e69a60e.jpg</t>
         </is>
       </c>
       <c r="X400" t="n">
@@ -63377,41 +63383,41 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>JILAWA</t>
+          <t>YADAUDU I</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>19/43/12/007</t>
+          <t>19/43/11/007</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b174</t>
+          <t>6a35c3f587b1768452f7b220</t>
         </is>
       </c>
       <c r="L401" t="n">
-        <v>64745</v>
+        <v>64736</v>
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr">
         <is>
-          <t>1781968169241</t>
+          <t>1781989191145</t>
         </is>
       </c>
       <c r="O401" t="n">
@@ -63436,7 +63442,7 @@
       <c r="V401" t="inlineStr"/>
       <c r="W401" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64646/d3c1b354-6508-4598-a45d-79f021e3a887.jpg</t>
         </is>
       </c>
       <c r="X401" t="n">
@@ -63534,41 +63540,41 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>KARGAWA</t>
+          <t>YADAUDU II</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>19/43/12/008</t>
+          <t>19/43/11/008</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17a</t>
+          <t>6a35c3f587b1768452f7b21f</t>
         </is>
       </c>
       <c r="L402" t="n">
-        <v>64746</v>
+        <v>64737</v>
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr">
         <is>
-          <t>1781976889527</t>
+          <t>1781976878903</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -63593,7 +63599,7 @@
       <c r="V402" t="inlineStr"/>
       <c r="W402" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64647/7f37ae57-784e-4f88-aa63-4a5cd2b65464.jpg</t>
         </is>
       </c>
       <c r="X402" t="n">
@@ -63691,41 +63697,41 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>MARAYAR ROGO</t>
+          <t>ZANGO DANMARKE</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>19/43/12/009</t>
+          <t>19/43/11/009</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b178</t>
+          <t>6a35c3f587b1768452f7b21d</t>
         </is>
       </c>
       <c r="L403" t="n">
-        <v>64747</v>
+        <v>64738</v>
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr">
         <is>
-          <t>1781976782857</t>
+          <t>1781976780359</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -63750,7 +63756,7 @@
       <c r="V403" t="inlineStr"/>
       <c r="W403" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/64648/ad13ca4f-07a2-42e6-8151-45e35b7d6d49.jpg</t>
         </is>
       </c>
       <c r="X403" t="n">
@@ -63848,41 +63854,41 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>RIGAR GABAS</t>
+          <t>FARTAWA II (FARTAWA ISLAMIYYA SCHOOL)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>19/43/12/010</t>
+          <t>19/43/11/010</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b177</t>
+          <t>6a35c3f587b1768452f7b224</t>
         </is>
       </c>
       <c r="L404" t="n">
-        <v>64748</v>
+        <v>151220</v>
       </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr">
         <is>
-          <t>1781968289759</t>
+          <t>1781977094685</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -63907,7 +63913,7 @@
       <c r="V404" t="inlineStr"/>
       <c r="W404" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646507/7a68173f-0286-4c60-b02c-5c14a811e46a.jpg</t>
         </is>
       </c>
       <c r="X404" t="n">
@@ -64005,41 +64011,41 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a00f</t>
+          <t>5f0f3cf28f77bb3acad0a00e</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>TANAGAR I</t>
+          <t>YANSHUNI (YANSHUNI PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>19/43/12/011</t>
+          <t>19/43/11/011</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b173</t>
+          <t>6a35c3f587b1768452f7b225</t>
         </is>
       </c>
       <c r="L405" t="n">
-        <v>64749</v>
+        <v>151221</v>
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr">
         <is>
-          <t>1781976813571</t>
+          <t>1781976782683</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -64064,7 +64070,7 @@
       <c r="V405" t="inlineStr"/>
       <c r="W405" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4726/646508/2d648d0d-65a7-4a6a-9bf4-7cc6145000bc.jpg</t>
         </is>
       </c>
       <c r="X405" t="n">
@@ -64177,26 +64183,26 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>TANAGAR II</t>
+          <t>CHARKA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>19/43/12/012</t>
+          <t>19/43/12/001</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b172</t>
+          <t>6a35c3f587b1768452f7b171</t>
         </is>
       </c>
       <c r="L406" t="n">
-        <v>64750</v>
+        <v>64739</v>
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr">
         <is>
-          <t>1781976798491</t>
+          <t>1781976872268</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -64221,7 +64227,7 @@
       <c r="V406" t="inlineStr"/>
       <c r="W406" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64649/e57583cb-ff04-4433-8128-6b32362fca31.jpg</t>
         </is>
       </c>
       <c r="X406" t="n">
@@ -64334,24 +64340,28 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>WARKAI RUGAR YAMMA</t>
+          <t>DANFARI I</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>19/43/12/013</t>
+          <t>19/43/12/002</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b176</t>
+          <t>6a35c3f587b1768452f7b16d</t>
         </is>
       </c>
       <c r="L407" t="n">
-        <v>64751</v>
+        <v>64740</v>
       </c>
       <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>1781976901500</t>
+        </is>
+      </c>
       <c r="O407" t="n">
         <v>0</v>
       </c>
@@ -64372,7 +64382,11 @@
         <v>0</v>
       </c>
       <c r="V407" t="inlineStr"/>
-      <c r="W407" t="inlineStr"/>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64650/da56eccc-1e33-4e87-9e6f-496ea6c8903d.jpg</t>
+        </is>
+      </c>
       <c r="X407" t="n">
         <v>0</v>
       </c>
@@ -64483,26 +64497,26 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>YALMA</t>
+          <t>DANFARI II</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>19/43/12/014</t>
+          <t>19/43/12/003</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b16e</t>
+          <t>6a35c3f587b1768452f7b175</t>
         </is>
       </c>
       <c r="L408" t="n">
-        <v>64752</v>
+        <v>64741</v>
       </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="inlineStr">
         <is>
-          <t>1781976792595</t>
+          <t>1781968309565</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -64527,7 +64541,7 @@
       <c r="V408" t="inlineStr"/>
       <c r="W408" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64651/ad158432-bf2a-409a-835a-458a1fb5cf12.jpg</t>
         </is>
       </c>
       <c r="X408" t="n">
@@ -64640,26 +64654,26 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>TANAGAR III (TANAGAR VETERINARY)</t>
+          <t>DANTSAWA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>19/43/12/015</t>
+          <t>19/43/12/004</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17b</t>
+          <t>6a35c3f587b1768452f7b170</t>
         </is>
       </c>
       <c r="L409" t="n">
-        <v>151222</v>
+        <v>64742</v>
       </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr">
         <is>
-          <t>1781976850366</t>
+          <t>1781968186810</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -64684,7 +64698,7 @@
       <c r="V409" t="inlineStr"/>
       <c r="W409" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64652/2bf1186f-3094-4fe2-9d57-1026897b8e13.jpg</t>
         </is>
       </c>
       <c r="X409" t="n">
@@ -64782,41 +64796,41 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>DUSHE I</t>
+          <t>HALADAWA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>19/43/13/001</t>
+          <t>19/43/12/005</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b098</t>
+          <t>6a35c3f587b1768452f7b179</t>
         </is>
       </c>
       <c r="L410" t="n">
-        <v>64753</v>
+        <v>64743</v>
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr">
         <is>
-          <t>1781976869394</t>
+          <t>1781976861221</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -64841,7 +64855,7 @@
       <c r="V410" t="inlineStr"/>
       <c r="W410" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64653/710fc86b-1e37-4ef6-997d-987936018c33.jpg</t>
         </is>
       </c>
       <c r="X410" t="n">
@@ -64939,41 +64953,41 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>DUSHE II</t>
+          <t>HAYIN WAZO</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>19/43/13/002</t>
+          <t>19/43/12/006</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09b</t>
+          <t>6a35c3f587b1768452f7b16f</t>
         </is>
       </c>
       <c r="L411" t="n">
-        <v>64754</v>
+        <v>64744</v>
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr">
         <is>
-          <t>1781974086141</t>
+          <t>1781976900341</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -64998,7 +65012,7 @@
       <c r="V411" t="inlineStr"/>
       <c r="W411" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64654/b970ac74-a0cc-45cb-a487-62549326eddf.jpg</t>
         </is>
       </c>
       <c r="X411" t="n">
@@ -65096,41 +65110,41 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>JALAWA I</t>
+          <t>JILAWA</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>19/43/13/003</t>
+          <t>19/43/12/007</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09c</t>
+          <t>6a35c3f587b1768452f7b174</t>
         </is>
       </c>
       <c r="L412" t="n">
-        <v>64755</v>
+        <v>64745</v>
       </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr">
         <is>
-          <t>1781976938520</t>
+          <t>1781968169241</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -65155,7 +65169,7 @@
       <c r="V412" t="inlineStr"/>
       <c r="W412" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64655/6dd1050b-6cf9-4c36-b88e-bc14b6c10a7a.jpg</t>
         </is>
       </c>
       <c r="X412" t="n">
@@ -65253,41 +65267,41 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>JALAWA II</t>
+          <t>KARGAWA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>19/43/13/004</t>
+          <t>19/43/12/008</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09a</t>
+          <t>6a35c3f587b1768452f7b17a</t>
         </is>
       </c>
       <c r="L413" t="n">
-        <v>64756</v>
+        <v>64746</v>
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr">
         <is>
-          <t>1781977012376</t>
+          <t>1781976889527</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -65312,7 +65326,7 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64656/7f42a7df-6eb8-43e6-a127-e5f4e35c20ca.jpg</t>
         </is>
       </c>
       <c r="X413" t="n">
@@ -65410,41 +65424,41 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>WARAWA I</t>
+          <t>MARAYAR ROGO</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>19/43/13/005</t>
+          <t>19/43/12/009</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b099</t>
+          <t>6a35c3f587b1768452f7b178</t>
         </is>
       </c>
       <c r="L414" t="n">
-        <v>64757</v>
+        <v>64747</v>
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr">
         <is>
-          <t>1781977113973</t>
+          <t>1781976782857</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -65469,7 +65483,7 @@
       <c r="V414" t="inlineStr"/>
       <c r="W414" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64657/39842f3c-42e7-40da-8a4c-48e3dfade0bd.jpg</t>
         </is>
       </c>
       <c r="X414" t="n">
@@ -65567,41 +65581,41 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>WARAWA II</t>
+          <t>RIGAR GABAS</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>19/43/13/006</t>
+          <t>19/43/12/010</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09d</t>
+          <t>6a35c3f587b1768452f7b177</t>
         </is>
       </c>
       <c r="L415" t="n">
-        <v>64758</v>
+        <v>64748</v>
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr">
         <is>
-          <t>1781976876830</t>
+          <t>1781968289759</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -65626,7 +65640,7 @@
       <c r="V415" t="inlineStr"/>
       <c r="W415" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64658/6d7a2500-1b01-4e40-b04d-77f2296bcf68.jpg</t>
         </is>
       </c>
       <c r="X415" t="n">
@@ -65724,41 +65738,41 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
+          <t>TANAGAR I</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>19/43/13/007</t>
+          <t>19/43/12/011</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09f</t>
+          <t>6a35c3f587b1768452f7b173</t>
         </is>
       </c>
       <c r="L416" t="n">
-        <v>151223</v>
+        <v>64749</v>
       </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr">
         <is>
-          <t>1781976882480</t>
+          <t>1781976813571</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -65783,7 +65797,7 @@
       <c r="V416" t="inlineStr"/>
       <c r="W416" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64659/b18f3030-0cf9-42fe-8cf6-af12f198a7c6.jpg</t>
         </is>
       </c>
       <c r="X416" t="n">
@@ -65881,72 +65895,66 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
+          <t>TANAGAR II</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>19/43/13/008</t>
+          <t>19/43/12/012</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b0a0</t>
+          <t>6a35c3f587b1768452f7b172</t>
         </is>
       </c>
       <c r="L417" t="n">
-        <v>151224</v>
-      </c>
-      <c r="M417" t="n">
-        <v>1781968214959</v>
-      </c>
+        <v>64750</v>
+      </c>
+      <c r="M417" t="inlineStr"/>
       <c r="N417" t="inlineStr">
         <is>
-          <t>1781968212953</t>
+          <t>1781976798491</t>
         </is>
       </c>
       <c r="O417" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P417" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q417" t="n">
-        <v>3</v>
-      </c>
-      <c r="R417" t="inlineStr">
-        <is>
-          <t>6a36ad5552b6362accb5c7d0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R417" t="inlineStr"/>
       <c r="S417" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="T417" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="U417" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V417" t="inlineStr"/>
       <c r="W417" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64660/515230de-58ce-40bd-a47f-a7b24a9e6bb1.jpg</t>
         </is>
       </c>
       <c r="X417" t="n">
@@ -65965,7 +65973,7 @@
         <v>0</v>
       </c>
       <c r="AC417" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD417" t="n">
         <v>0</v>
@@ -66044,43 +66052,39 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>5f0f3cf28f77bb3acad0a010</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
+          <t>WARKAI RUGAR YAMMA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>19/43/13/009</t>
+          <t>19/43/12/013</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>6a35c3f487b1768452f7b09e</t>
+          <t>6a35c3f587b1768452f7b176</t>
         </is>
       </c>
       <c r="L418" t="n">
-        <v>151225</v>
+        <v>64751</v>
       </c>
       <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr">
-        <is>
-          <t>1781968282375</t>
-        </is>
-      </c>
+      <c r="N418" t="inlineStr"/>
       <c r="O418" t="n">
         <v>0</v>
       </c>
@@ -66101,11 +66105,7 @@
         <v>0</v>
       </c>
       <c r="V418" t="inlineStr"/>
-      <c r="W418" t="inlineStr">
-        <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
-        </is>
-      </c>
+      <c r="W418" t="inlineStr"/>
       <c r="X418" t="n">
         <v>0</v>
       </c>
@@ -66201,41 +66201,41 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>GUMAKA</t>
+          <t>YALMA</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>19/43/14/001</t>
+          <t>19/43/12/014</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17e</t>
+          <t>6a35c3f587b1768452f7b16e</t>
         </is>
       </c>
       <c r="L419" t="n">
-        <v>64759</v>
+        <v>64752</v>
       </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr">
         <is>
-          <t>1781975166154</t>
+          <t>1781976792595</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -66260,7 +66260,7 @@
       <c r="V419" t="inlineStr"/>
       <c r="W419" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/64662/4342eb83-c9a3-4def-8474-5b727cd2c781.jpg</t>
         </is>
       </c>
       <c r="X419" t="n">
@@ -66358,41 +66358,41 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a00f</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>KANWA</t>
+          <t>TANAGAR III (TANAGAR VETERINARY)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>19/43/14/002</t>
+          <t>19/43/12/015</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17c</t>
+          <t>6a35c3f587b1768452f7b17b</t>
         </is>
       </c>
       <c r="L420" t="n">
-        <v>64760</v>
+        <v>151222</v>
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr">
         <is>
-          <t>1781974985005</t>
+          <t>1781976850366</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -66417,7 +66417,7 @@
       <c r="V420" t="inlineStr"/>
       <c r="W420" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4727/646509/56225ec0-5ea6-4e37-9567-bf12fb35bc51.jpg</t>
         </is>
       </c>
       <c r="X420" t="n">
@@ -66515,41 +66515,41 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>POLICE ACADEMY</t>
+          <t>DUSHE I</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>19/43/14/003</t>
+          <t>19/43/13/001</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17d</t>
+          <t>6a35c3f487b1768452f7b098</t>
         </is>
       </c>
       <c r="L421" t="n">
-        <v>64761</v>
+        <v>64753</v>
       </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr">
         <is>
-          <t>1781975165502</t>
+          <t>1781976869394</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -66574,7 +66574,7 @@
       <c r="V421" t="inlineStr"/>
       <c r="W421" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64663/09708a35-e00e-46b0-9a92-4c258d1b2114.jpg</t>
         </is>
       </c>
       <c r="X421" t="n">
@@ -66672,41 +66672,41 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>'YANDALLA</t>
+          <t>DUSHE II</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>19/43/14/004</t>
+          <t>19/43/13/002</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b17f</t>
+          <t>6a35c3f487b1768452f7b09b</t>
         </is>
       </c>
       <c r="L422" t="n">
-        <v>64762</v>
+        <v>64754</v>
       </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr">
         <is>
-          <t>1781975169663</t>
+          <t>1781974086141</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -66731,7 +66731,7 @@
       <c r="V422" t="inlineStr"/>
       <c r="W422" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64664/1c93ce1b-22f4-4579-b53e-9aa04552bd31.jpg</t>
         </is>
       </c>
       <c r="X422" t="n">
@@ -66829,41 +66829,41 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>'YANDALLA II</t>
+          <t>JALAWA I</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>19/43/14/005</t>
+          <t>19/43/13/003</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b180</t>
+          <t>6a35c3f487b1768452f7b09c</t>
         </is>
       </c>
       <c r="L423" t="n">
-        <v>64763</v>
+        <v>64755</v>
       </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr">
         <is>
-          <t>1781968201933</t>
+          <t>1781976938520</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -66888,7 +66888,7 @@
       <c r="V423" t="inlineStr"/>
       <c r="W423" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64665/13ed887f-79c4-4583-9b15-357eb73958be.jpg</t>
         </is>
       </c>
       <c r="X423" t="n">
@@ -66986,41 +66986,41 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
+          <t>JALAWA II</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>19/43/14/006</t>
+          <t>19/43/13/004</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b183</t>
+          <t>6a35c3f487b1768452f7b09a</t>
         </is>
       </c>
       <c r="L424" t="n">
-        <v>151226</v>
+        <v>64756</v>
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr">
         <is>
-          <t>1781968195719</t>
+          <t>1781977012376</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -67045,7 +67045,7 @@
       <c r="V424" t="inlineStr"/>
       <c r="W424" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64666/6d43421c-1472-4d56-8885-964991ba89d8.jpg</t>
         </is>
       </c>
       <c r="X424" t="n">
@@ -67143,41 +67143,41 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
+          <t>WARAWA I</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>19/43/14/007</t>
+          <t>19/43/13/005</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b182</t>
+          <t>6a35c3f487b1768452f7b099</t>
         </is>
       </c>
       <c r="L425" t="n">
-        <v>151227</v>
+        <v>64757</v>
       </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr">
         <is>
-          <t>1781974982952</t>
+          <t>1781977113973</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -67202,7 +67202,7 @@
       <c r="V425" t="inlineStr"/>
       <c r="W425" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64667/391c01c3-9a86-4aa5-aeca-c9d35761c9e8.jpg</t>
         </is>
       </c>
       <c r="X425" t="n">
@@ -67300,41 +67300,41 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a011</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
+          <t>WARAWA II</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>19/43/14/008</t>
+          <t>19/43/13/006</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b181</t>
+          <t>6a35c3f487b1768452f7b09d</t>
         </is>
       </c>
       <c r="L426" t="n">
-        <v>151228</v>
+        <v>64758</v>
       </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr">
         <is>
-          <t>1781968682952</t>
+          <t>1781976876830</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -67359,7 +67359,7 @@
       <c r="V426" t="inlineStr"/>
       <c r="W426" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/64668/2ea97eb4-f44c-44f3-b6a6-62469812dc43.jpg</t>
         </is>
       </c>
       <c r="X426" t="n">
@@ -67457,41 +67457,41 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>ALIMAWA</t>
+          <t>JALAWA III (JALAWA ISLAMIYYA)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>19/43/15/001</t>
+          <t>19/43/13/007</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fd</t>
+          <t>6a35c3f487b1768452f7b09f</t>
         </is>
       </c>
       <c r="L427" t="n">
-        <v>64764</v>
+        <v>151223</v>
       </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr">
         <is>
-          <t>1781968165832</t>
+          <t>1781976882480</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -67516,7 +67516,7 @@
       <c r="V427" t="inlineStr"/>
       <c r="W427" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646510/9830f289-574e-4fc8-a7e8-0272cabe9a50.jpg</t>
         </is>
       </c>
       <c r="X427" t="n">
@@ -67614,66 +67614,72 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>BUROMAWA</t>
+          <t>WARAWA III (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>19/43/15/002</t>
+          <t>19/43/13/008</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fc</t>
+          <t>6a35c3f487b1768452f7b0a0</t>
         </is>
       </c>
       <c r="L428" t="n">
-        <v>64765</v>
-      </c>
-      <c r="M428" t="inlineStr"/>
+        <v>151224</v>
+      </c>
+      <c r="M428" t="n">
+        <v>1781968214959</v>
+      </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>1781974266039</t>
+          <t>1781968212953</t>
         </is>
       </c>
       <c r="O428" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P428" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q428" t="n">
-        <v>0</v>
-      </c>
-      <c r="R428" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>6a36ad5552b6362accb5c7d0</t>
+        </is>
+      </c>
       <c r="S428" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T428" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="U428" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="V428" t="inlineStr"/>
       <c r="W428" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646511/147b1669-b9f5-4f53-8a7e-1009c8a2a166.jpg</t>
         </is>
       </c>
       <c r="X428" t="n">
@@ -67692,7 +67698,7 @@
         <v>0</v>
       </c>
       <c r="AC428" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AD428" t="n">
         <v>0</v>
@@ -67771,41 +67777,41 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf28f77bb3acad0a010</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>GIWARAN ALITINI I</t>
+          <t>WARAWA IV (WARAWA PRIMARY SCHOOL)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>19/43/15/003</t>
+          <t>19/43/13/009</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fe</t>
+          <t>6a35c3f487b1768452f7b09e</t>
         </is>
       </c>
       <c r="L429" t="n">
-        <v>64766</v>
+        <v>151225</v>
       </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr">
         <is>
-          <t>1781976840577</t>
+          <t>1781968282375</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -67830,7 +67836,7 @@
       <c r="V429" t="inlineStr"/>
       <c r="W429" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4728/646512/49874ef3-9722-4373-82cd-71c4b06f9a5b.jpg</t>
         </is>
       </c>
       <c r="X429" t="n">
@@ -67928,41 +67934,41 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>GIWARAN ALITINI II</t>
+          <t>GUMAKA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>19/43/15/004</t>
+          <t>19/43/14/001</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fb</t>
+          <t>6a35c3f587b1768452f7b17e</t>
         </is>
       </c>
       <c r="L430" t="n">
-        <v>64767</v>
+        <v>64759</v>
       </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr">
         <is>
-          <t>1781968281024</t>
+          <t>1781975166154</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -67987,7 +67993,7 @@
       <c r="V430" t="inlineStr"/>
       <c r="W430" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64669/cec77346-71f5-4fa9-b3ce-6d6950643853.jpg</t>
         </is>
       </c>
       <c r="X430" t="n">
@@ -68085,41 +68091,41 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>GIWARAN JIJIYAWA I</t>
+          <t>KANWA</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>19/43/15/005</t>
+          <t>19/43/14/002</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1ff</t>
+          <t>6a35c3f587b1768452f7b17c</t>
         </is>
       </c>
       <c r="L431" t="n">
-        <v>64768</v>
+        <v>64760</v>
       </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr">
         <is>
-          <t>1781974266070</t>
+          <t>1781974985005</t>
         </is>
       </c>
       <c r="O431" t="n">
@@ -68144,7 +68150,7 @@
       <c r="V431" t="inlineStr"/>
       <c r="W431" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64670/42cde8e5-f1e0-43a3-804e-1cc558a3f723.jpg</t>
         </is>
       </c>
       <c r="X431" t="n">
@@ -68242,41 +68248,41 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>GIWARAN JIJIYAWA II</t>
+          <t>POLICE ACADEMY</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>19/43/15/006</t>
+          <t>19/43/14/003</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b200</t>
+          <t>6a35c3f587b1768452f7b17d</t>
         </is>
       </c>
       <c r="L432" t="n">
-        <v>64769</v>
+        <v>64761</v>
       </c>
       <c r="M432" t="inlineStr"/>
       <c r="N432" t="inlineStr">
         <is>
-          <t>1781974447124</t>
+          <t>1781975165502</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -68301,7 +68307,7 @@
       <c r="V432" t="inlineStr"/>
       <c r="W432" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64671/c413c988-26a5-459a-a22d-a8ca5f852427.jpg</t>
         </is>
       </c>
       <c r="X432" t="n">
@@ -68399,41 +68405,41 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>'YANGIZO I</t>
+          <t>'YANDALLA</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>19/43/15/007</t>
+          <t>19/43/14/004</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1f8</t>
+          <t>6a35c3f587b1768452f7b17f</t>
         </is>
       </c>
       <c r="L433" t="n">
-        <v>64770</v>
+        <v>64762</v>
       </c>
       <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr">
         <is>
-          <t>1781974628327</t>
+          <t>1781975169663</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -68458,7 +68464,7 @@
       <c r="V433" t="inlineStr"/>
       <c r="W433" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64672/48c4cc56-fda3-49e8-804d-a99d94f5ca51.jpg</t>
         </is>
       </c>
       <c r="X433" t="n">
@@ -68556,41 +68562,41 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>'YANGIZO II</t>
+          <t>'YANDALLA II</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>19/43/15/008</t>
+          <t>19/43/14/005</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1f9</t>
+          <t>6a35c3f587b1768452f7b180</t>
         </is>
       </c>
       <c r="L434" t="n">
-        <v>64771</v>
+        <v>64763</v>
       </c>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr">
         <is>
-          <t>1781974630372</t>
+          <t>1781968201933</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -68615,7 +68621,7 @@
       <c r="V434" t="inlineStr"/>
       <c r="W434" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/64673/ceae24ae-ba96-4971-af26-dcfd8f5a87ba.jpg</t>
         </is>
       </c>
       <c r="X434" t="n">
@@ -68713,41 +68719,41 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>'YANGIZO III</t>
+          <t>'YAN DALLA III NURUL HUDA ISLAMIYYA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>19/43/15/009</t>
+          <t>19/43/14/006</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b1fa</t>
+          <t>6a35c3f587b1768452f7b183</t>
         </is>
       </c>
       <c r="L435" t="n">
-        <v>64772</v>
+        <v>151226</v>
       </c>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr">
         <is>
-          <t>1781968246493</t>
+          <t>1781968195719</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -68772,7 +68778,7 @@
       <c r="V435" t="inlineStr"/>
       <c r="W435" t="inlineStr">
         <is>
-          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646513/be631c2d-7835-4165-8de0-97cc43b4d0b9.jpg</t>
         </is>
       </c>
       <c r="X435" t="n">
@@ -68870,41 +68876,41 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>YANGIZO</t>
+          <t>YAN DALLA</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>5f0f3cf38f77bb3acad0a012</t>
+          <t>5f0f3cf38f77bb3acad0a011</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
+          <t>'YAN DALLA IV ('YAN DALLA PRI SCH.)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>19/43/15/010</t>
+          <t>19/43/14/007</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>6a35c3f587b1768452f7b201</t>
+          <t>6a35c3f587b1768452f7b182</t>
         </is>
       </c>
       <c r="L436" t="n">
-        <v>151229</v>
+        <v>151227</v>
       </c>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr">
         <is>
-          <t>1781974627113</t>
+          <t>1781974982952</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -68929,73 +68935,1800 @@
       <c r="V436" t="inlineStr"/>
       <c r="W436" t="inlineStr">
         <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646514/bb0fa014-b367-41a7-b8f0-dab2c523a540.jpg</t>
+        </is>
+      </c>
+      <c r="X436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>YAN DALLA</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a011</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>'YAN DALLA FULANI ('YAN DALLA FULANI ISLAMIYYA)</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>19/43/14/008</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b181</t>
+        </is>
+      </c>
+      <c r="L437" t="n">
+        <v>151228</v>
+      </c>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>1781968682952</t>
+        </is>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="P437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="inlineStr"/>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="n">
+        <v>0</v>
+      </c>
+      <c r="U437" t="n">
+        <v>0</v>
+      </c>
+      <c r="V437" t="inlineStr"/>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4729/646515/0cbf7c86-3310-49af-a47c-99415eb37b9d.jpg</t>
+        </is>
+      </c>
+      <c r="X437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>ALIMAWA</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>19/43/15/001</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fd</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>64764</v>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>1781968165832</t>
+        </is>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+      <c r="P438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>0</v>
+      </c>
+      <c r="R438" t="inlineStr"/>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="n">
+        <v>0</v>
+      </c>
+      <c r="U438" t="n">
+        <v>0</v>
+      </c>
+      <c r="V438" t="inlineStr"/>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64674/175b2f35-ff42-4220-8b55-e6185009a354.jpg</t>
+        </is>
+      </c>
+      <c r="X438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>BUROMAWA</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>19/43/15/002</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fc</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>64765</v>
+      </c>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>1781974266039</t>
+        </is>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="P439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="inlineStr"/>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="n">
+        <v>0</v>
+      </c>
+      <c r="V439" t="inlineStr"/>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64675/c080c04b-3dcf-4f18-a636-9c1e29e33e9b.jpg</t>
+        </is>
+      </c>
+      <c r="X439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>GIWARAN ALITINI I</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>19/43/15/003</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fe</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>64766</v>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>1781976840577</t>
+        </is>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+      <c r="P440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>0</v>
+      </c>
+      <c r="R440" t="inlineStr"/>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="n">
+        <v>0</v>
+      </c>
+      <c r="U440" t="n">
+        <v>0</v>
+      </c>
+      <c r="V440" t="inlineStr"/>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64676/de74165f-fbc5-4cc7-8a13-9d1faa9d3397.jpg</t>
+        </is>
+      </c>
+      <c r="X440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>GIWARAN ALITINI II</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>19/43/15/004</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fb</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>64767</v>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>1781968281024</t>
+        </is>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="P441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" t="inlineStr"/>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="n">
+        <v>0</v>
+      </c>
+      <c r="V441" t="inlineStr"/>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64677/296f0ca9-ea7d-4043-9a71-b70da57e2eac.jpg</t>
+        </is>
+      </c>
+      <c r="X441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>GIWARAN JIJIYAWA I</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>19/43/15/005</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1ff</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>64768</v>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>1781974266070</t>
+        </is>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="P442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="inlineStr"/>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="n">
+        <v>0</v>
+      </c>
+      <c r="V442" t="inlineStr"/>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64678/57a0b365-235c-46f5-8e1d-7a6785359c5e.jpg</t>
+        </is>
+      </c>
+      <c r="X442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>GIWARAN JIJIYAWA II</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>19/43/15/006</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b200</t>
+        </is>
+      </c>
+      <c r="L443" t="n">
+        <v>64769</v>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>1781974447124</t>
+        </is>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="P443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>0</v>
+      </c>
+      <c r="R443" t="inlineStr"/>
+      <c r="S443" t="n">
+        <v>0</v>
+      </c>
+      <c r="T443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="n">
+        <v>0</v>
+      </c>
+      <c r="V443" t="inlineStr"/>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64679/5b0e1ed0-9516-410b-8420-efafdc8a4266.jpg</t>
+        </is>
+      </c>
+      <c r="X443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>'YANGIZO I</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>19/43/15/007</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1f8</t>
+        </is>
+      </c>
+      <c r="L444" t="n">
+        <v>64770</v>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>1781974628327</t>
+        </is>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="P444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>0</v>
+      </c>
+      <c r="R444" t="inlineStr"/>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="n">
+        <v>0</v>
+      </c>
+      <c r="U444" t="n">
+        <v>0</v>
+      </c>
+      <c r="V444" t="inlineStr"/>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64680/fdf8717e-7fdf-4759-bdf4-67bcd20030a1.jpg</t>
+        </is>
+      </c>
+      <c r="X444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>'YANGIZO II</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>19/43/15/008</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1f9</t>
+        </is>
+      </c>
+      <c r="L445" t="n">
+        <v>64771</v>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>1781974630372</t>
+        </is>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>0</v>
+      </c>
+      <c r="R445" t="inlineStr"/>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="n">
+        <v>0</v>
+      </c>
+      <c r="V445" t="inlineStr"/>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64681/47783bab-a75e-4ab2-a6d9-c154eca2e745.jpg</t>
+        </is>
+      </c>
+      <c r="X445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>'YANGIZO III</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>19/43/15/009</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b1fa</t>
+        </is>
+      </c>
+      <c r="L446" t="n">
+        <v>64772</v>
+      </c>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>1781968246493</t>
+        </is>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="P446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="inlineStr"/>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="n">
+        <v>0</v>
+      </c>
+      <c r="U446" t="n">
+        <v>0</v>
+      </c>
+      <c r="V446" t="inlineStr"/>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/64682/6b04a818-22c5-4824-a5b8-fe549672bdec.jpg</t>
+        </is>
+      </c>
+      <c r="X446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>6a35c3e587b1768452f7b027</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>House of Representatives election - 2026-06-20 - dawakin kudu/warawa</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-06-19T23:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>YANGIZO</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>5f0f3cf38f77bb3acad0a012</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>GIWARAN BAGINAWA (GIWARAN BAGINAWA PRIMARY SCHOOL)</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>19/43/15/010</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>6a35c3f587b1768452f7b201</t>
+        </is>
+      </c>
+      <c r="L447" t="n">
+        <v>151229</v>
+      </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>1781974627113</t>
+        </is>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="P447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>0</v>
+      </c>
+      <c r="R447" t="inlineStr"/>
+      <c r="S447" t="n">
+        <v>0</v>
+      </c>
+      <c r="T447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="n">
+        <v>0</v>
+      </c>
+      <c r="V447" t="inlineStr"/>
+      <c r="W447" t="inlineStr">
+        <is>
           <t>https://inc-s3-cache.incportals.com/cached/express/results/2992/20/412/4730/646516/066acd00-5fa0-4076-909b-7e86563f62e7.jpg</t>
         </is>
       </c>
-      <c r="X436" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y436" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR436" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS436" t="n">
+      <c r="X447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS447" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69010,7 +70743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH30"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71728,26 +73461,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MADARI MATA</t>
+          <t>KATARKAWA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -71765,7 +73498,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -71816,10 +73549,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>100</v>
@@ -71838,7 +73571,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TAMBURAWAR GABAS</t>
+          <t>MADARI MATA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -71926,10 +73659,10 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
         <v>100</v>
@@ -71948,7 +73681,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TANGAR</t>
+          <t>TAMBURAWAR GABAS</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -72036,13 +73769,13 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -72058,26 +73791,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WARAWA</t>
+          <t>TANGAR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -72095,7 +73828,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -72146,13 +73879,13 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AG28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="29">
@@ -72168,26 +73901,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YAN DALLA</t>
+          <t>WARAWA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -72205,7 +73938,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -72256,10 +73989,10 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH29" t="n">
         <v>100</v>
@@ -72278,100 +74011,210 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>YAN DALLA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WARAWA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>YANGIZO</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
         <v>10</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG31" t="n">
         <v>10</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH31" t="n">
         <v>100</v>
       </c>
     </row>
@@ -72673,22 +74516,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2896</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>483</v>
+        <v>516</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>482</v>
+        <v>513</v>
       </c>
       <c r="G3" t="n">
-        <v>2854</v>
+        <v>3089</v>
       </c>
       <c r="H3" t="n">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -72706,7 +74549,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -72757,13 +74600,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AF3" t="n">
         <v>142</v>
       </c>
       <c r="AG3" t="n">
-        <v>107.6</v>
+        <v>99.3</v>
       </c>
     </row>
   </sheetData>
@@ -72954,22 +74797,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7076</v>
+        <v>7311</v>
       </c>
       <c r="C2" t="n">
-        <v>951</v>
+        <v>984</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>934</v>
+        <v>965</v>
       </c>
       <c r="F2" t="n">
-        <v>7034</v>
+        <v>7269</v>
       </c>
       <c r="G2" t="n">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -72987,7 +74830,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>918</v>
+        <v>949</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -73038,16 +74881,16 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AE2" t="n">
         <v>445</v>
       </c>
       <c r="AF2" t="n">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AG2" t="n">
-        <v>102.3</v>
+        <v>99.8</v>
       </c>
     </row>
   </sheetData>
